--- a/DRUG DISEASE.xlsx
+++ b/DRUG DISEASE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT Room\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A6AF305-0B8F-47BF-BA7B-946AEBFB3725}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E83F5C6B-DC6B-4440-996C-30AC0CECEC85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2670" yWindow="195" windowWidth="17595" windowHeight="12780" xr2:uid="{3244C3E9-4DF0-4247-BD4E-75BB2D6BE0CE}"/>
+    <workbookView xWindow="825" yWindow="0" windowWidth="17595" windowHeight="12780" xr2:uid="{3244C3E9-4DF0-4247-BD4E-75BB2D6BE0CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="839" uniqueCount="338">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="374">
   <si>
     <t>ชื่อยา</t>
   </si>
@@ -1058,12 +1058,120 @@
   <si>
     <t>หูอื้อ</t>
   </si>
+  <si>
+    <t>COUMADIN 3 MG (HAD)</t>
+  </si>
+  <si>
+    <t>I634</t>
+  </si>
+  <si>
+    <t>N185</t>
+  </si>
+  <si>
+    <t>ZENTEL  200 MG  (ALBENDAZOLE)  TAB</t>
+  </si>
+  <si>
+    <t>D721</t>
+  </si>
+  <si>
+    <t>R1049</t>
+  </si>
+  <si>
+    <t>E782</t>
+  </si>
+  <si>
+    <t>CLOXACILLIN 500 MG</t>
+  </si>
+  <si>
+    <t>CALAMINE LOTION 60 ML</t>
+  </si>
+  <si>
+    <t>CPM 10  MG INJECTION</t>
+  </si>
+  <si>
+    <t>L42</t>
+  </si>
+  <si>
+    <t>SENOKOT   </t>
+  </si>
+  <si>
+    <t>MOM  240 ML</t>
+  </si>
+  <si>
+    <t>K590</t>
+  </si>
+  <si>
+    <t>AUGMENTIN 1 G (L)</t>
+  </si>
+  <si>
+    <t>TYLENOL 500 MG  TAB.</t>
+  </si>
+  <si>
+    <t>K610</t>
+  </si>
+  <si>
+    <t>J029</t>
+  </si>
+  <si>
+    <t>OPSIL  TEARS  10 ML</t>
+  </si>
+  <si>
+    <t>H041</t>
+  </si>
+  <si>
+    <t>DUPHALAC (per ML)</t>
+  </si>
+  <si>
+    <t>HISTA - OPH EYE DROP</t>
+  </si>
+  <si>
+    <t>CIPROFLOXACIN  500 MG  TAB.</t>
+  </si>
+  <si>
+    <t>H055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">เศษเหล็กเข้าตาข้างซ้าย มีซ้าย มีอาการ ปวดเคือง เป็นมา 1 วัน  </t>
+  </si>
+  <si>
+    <t>L040</t>
+  </si>
+  <si>
+    <t>ปวดคอ</t>
+  </si>
+  <si>
+    <t>DMPA 150 MG (DEPO-PROVERA)</t>
+  </si>
+  <si>
+    <t>Z304</t>
+  </si>
+  <si>
+    <t>L010</t>
+  </si>
+  <si>
+    <t>KETOCONAZOLE 2%  5 G</t>
+  </si>
+  <si>
+    <t>L219</t>
+  </si>
+  <si>
+    <t>K580</t>
+  </si>
+  <si>
+    <t>D568</t>
+  </si>
+  <si>
+    <t>QUININE 300 MG</t>
+  </si>
+  <si>
+    <t>M793</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="16"/>
       <color theme="1"/>
@@ -1076,6 +1184,13 @@
       <name val="BrowalliaUPC"/>
       <family val="2"/>
       <charset val="222"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="BrowalliaUPC"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1098,7 +1213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1106,6 +1221,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
@@ -1420,7 +1536,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36EC5C3C-1E59-4742-8E49-52DA351D6E49}">
-  <dimension ref="A1:D383"/>
+  <dimension ref="A1:D439"/>
   <sheetFormatPr defaultColWidth="17.5" defaultRowHeight="22.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="27.25" customWidth="1"/>
@@ -4713,6 +4829,466 @@
         <v>100</v>
       </c>
     </row>
+    <row r="384" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A384" s="1" t="s">
+        <v>338</v>
+      </c>
+      <c r="D384" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="385" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A385" t="s">
+        <v>255</v>
+      </c>
+      <c r="D385" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="386" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+      <c r="A386" s="1" t="s">
+        <v>161</v>
+      </c>
+      <c r="D386" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+      <c r="A387" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="D387" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="388" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A388" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D388" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+      <c r="A389" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="D389" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="390" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A390" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D390" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="391" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A391" t="s">
+        <v>258</v>
+      </c>
+      <c r="D391" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="392" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A392" t="s">
+        <v>345</v>
+      </c>
+      <c r="D392" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A393" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="D393" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="394" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A394" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D394" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="395" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A395" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="D395" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+      <c r="A396" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D396" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="397" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A397" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D397" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A398" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="D398" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="399" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A399" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D399" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="400" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A400" s="1" t="s">
+        <v>349</v>
+      </c>
+      <c r="D400" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="401" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A401" s="1" t="s">
+        <v>350</v>
+      </c>
+      <c r="D401" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A402" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="D402" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="403" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A403" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D403" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="404" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A404" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="D404" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="405" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+      <c r="A405" s="1" t="s">
+        <v>314</v>
+      </c>
+      <c r="D405" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="406" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A406" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D406" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A407" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D407" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="408" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A408" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="D408" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="409" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A409" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D409" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="410" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A410" t="s">
+        <v>356</v>
+      </c>
+      <c r="D410" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A411" t="s">
+        <v>358</v>
+      </c>
+      <c r="D411" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A412" s="1" t="s">
+        <v>359</v>
+      </c>
+      <c r="D412" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A413" t="s">
+        <v>360</v>
+      </c>
+      <c r="D413" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="414" spans="1:4" ht="23.25" x14ac:dyDescent="0.5">
+      <c r="A414" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B414" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="D414" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="415" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A415" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B415" t="s">
+        <v>362</v>
+      </c>
+      <c r="D415" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="416" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A416" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B416" t="s">
+        <v>362</v>
+      </c>
+      <c r="D416" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="417" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A417" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D417" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="418" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A418" s="1" t="s">
+        <v>283</v>
+      </c>
+      <c r="D418" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+      <c r="A419" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="D419" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="420" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A420" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="D420" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="421" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A421" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D421" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A422" t="s">
+        <v>244</v>
+      </c>
+      <c r="D422" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+      <c r="A423" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B423" t="s">
+        <v>364</v>
+      </c>
+      <c r="D423" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A424" t="s">
+        <v>365</v>
+      </c>
+      <c r="D424" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="425" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A425" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D425" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="426" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A426" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D426" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="427" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A427" s="1" t="s">
+        <v>267</v>
+      </c>
+      <c r="D427" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="428" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A428" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="D428" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="429" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A429" s="1" t="s">
+        <v>270</v>
+      </c>
+      <c r="D429" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="430" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A430" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D430" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="431" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A431" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D431" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="432" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A432" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D432" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="433" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A433" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D433" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="434" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A434" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D434" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="435" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A435" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D435" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="436" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A436" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="D436" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="437" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A437" s="1" t="s">
+        <v>255</v>
+      </c>
+      <c r="D437" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="438" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A438" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="D438" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="439" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A439" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D439" t="s">
+        <v>373</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DRUG DISEASE.xlsx
+++ b/DRUG DISEASE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT Room\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E83F5C6B-DC6B-4440-996C-30AC0CECEC85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8274506C-90E0-4CA8-BC9B-E5356521A2E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="825" yWindow="0" windowWidth="17595" windowHeight="12780" xr2:uid="{3244C3E9-4DF0-4247-BD4E-75BB2D6BE0CE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{3244C3E9-4DF0-4247-BD4E-75BB2D6BE0CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="955" uniqueCount="374">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="366">
   <si>
     <t>ชื่อยา</t>
   </si>
@@ -801,37 +801,13 @@
     <t>M4796</t>
   </si>
   <si>
-    <t>SODAMINT</t>
-  </si>
-  <si>
-    <t>CHALK CAP 350 MG</t>
-  </si>
-  <si>
-    <t>MINOXIDIL  5 MG</t>
-  </si>
-  <si>
     <t>FBC TAB (FERROPRO)</t>
   </si>
   <si>
     <t>FOLIC ACID 5 MG</t>
   </si>
   <si>
-    <t>CARVEDILOL 6.25 TAB</t>
-  </si>
-  <si>
     <t>LOPID 600 MG</t>
-  </si>
-  <si>
-    <t>ONE- ALPHA  0.25 MCG.</t>
-  </si>
-  <si>
-    <t>VITAMIN C 500 MG 2 ML INJ.</t>
-  </si>
-  <si>
-    <t>OXYGEN  CANNULA</t>
-  </si>
-  <si>
-    <t>D569,E782,I120,N185</t>
   </si>
   <si>
     <t>BRICANYL 2.5 MG</t>
@@ -1536,7 +1512,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36EC5C3C-1E59-4742-8E49-52DA351D6E49}">
-  <dimension ref="A1:D439"/>
+  <dimension ref="A1:D427"/>
   <sheetFormatPr defaultColWidth="17.5" defaultRowHeight="22.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="27.25" customWidth="1"/>
@@ -1922,7 +1898,7 @@
         <v>38</v>
       </c>
       <c r="D47" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.45">
@@ -1930,7 +1906,7 @@
         <v>37</v>
       </c>
       <c r="D48" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.45">
@@ -1938,7 +1914,7 @@
         <v>54</v>
       </c>
       <c r="D49" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.45">
@@ -2399,15 +2375,15 @@
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A107" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="D107">
-        <v>9929</v>
+        <v>95</v>
+      </c>
+      <c r="D107" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A108" s="1" t="s">
-        <v>95</v>
+        <v>42</v>
       </c>
       <c r="D108" t="s">
         <v>96</v>
@@ -2415,7 +2391,7 @@
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A109" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D109" t="s">
         <v>96</v>
@@ -2423,7 +2399,7 @@
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A110" s="1" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
       <c r="D110" t="s">
         <v>96</v>
@@ -2431,15 +2407,15 @@
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A111" s="1" t="s">
-        <v>102</v>
+        <v>34</v>
       </c>
       <c r="D111" t="s">
-        <v>96</v>
+        <v>50</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A112" s="1" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="D112" t="s">
         <v>50</v>
@@ -2447,7 +2423,7 @@
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A113" s="1" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="D113" t="s">
         <v>50</v>
@@ -2455,39 +2431,39 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A114" s="1" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A115" s="1" t="s">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="D115" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:4" ht="45" x14ac:dyDescent="0.45">
       <c r="A116" s="1" t="s">
-        <v>66</v>
+        <v>114</v>
       </c>
       <c r="D116" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A117" s="1" t="s">
-        <v>114</v>
+        <v>38</v>
       </c>
       <c r="D117" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A118" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D118" t="s">
         <v>116</v>
@@ -2495,10 +2471,10 @@
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A119" s="1" t="s">
-        <v>37</v>
+        <v>117</v>
       </c>
       <c r="D119" t="s">
-        <v>116</v>
+        <v>12</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.45">
@@ -2506,20 +2482,20 @@
         <v>117</v>
       </c>
       <c r="D120" t="s">
-        <v>12</v>
+        <v>118</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A121" s="1" t="s">
-        <v>117</v>
+        <v>45</v>
       </c>
       <c r="D121" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A122" s="1" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="D122" t="s">
         <v>120</v>
@@ -2527,7 +2503,7 @@
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A123" s="1" t="s">
-        <v>119</v>
+        <v>43</v>
       </c>
       <c r="D123" t="s">
         <v>120</v>
@@ -2535,15 +2511,15 @@
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A124" s="1" t="s">
-        <v>43</v>
+        <v>121</v>
       </c>
       <c r="D124" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A125" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D125" t="s">
         <v>124</v>
@@ -2551,7 +2527,7 @@
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A126" s="1" t="s">
-        <v>122</v>
+        <v>47</v>
       </c>
       <c r="D126" t="s">
         <v>124</v>
@@ -2559,7 +2535,7 @@
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A127" s="1" t="s">
-        <v>47</v>
+        <v>123</v>
       </c>
       <c r="D127" t="s">
         <v>124</v>
@@ -2567,55 +2543,55 @@
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A128" s="1" t="s">
-        <v>123</v>
+        <v>21</v>
       </c>
       <c r="D128" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A129" s="1" t="s">
-        <v>21</v>
+    <row r="129" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+      <c r="A129" s="2" t="s">
+        <v>127</v>
       </c>
       <c r="D129" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4" ht="45" x14ac:dyDescent="0.45">
-      <c r="A130" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A130" t="s">
+        <v>126</v>
       </c>
       <c r="D130" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A131" t="s">
-        <v>126</v>
+      <c r="A131" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="D131" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A132" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D132" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A133" s="1" t="s">
-        <v>130</v>
+        <v>38</v>
       </c>
       <c r="D133" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A134" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D134" t="s">
         <v>132</v>
@@ -2623,7 +2599,7 @@
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A135" s="1" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="D135" t="s">
         <v>132</v>
@@ -2631,55 +2607,55 @@
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A136" s="1" t="s">
-        <v>54</v>
+        <v>133</v>
       </c>
       <c r="D136" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A137" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D137" t="s">
-        <v>134</v>
+        <v>80</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A138" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="D138" t="s">
-        <v>80</v>
+        <v>137</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A139" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D139" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A140" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D140" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A141" s="1" t="s">
-        <v>140</v>
+        <v>20</v>
       </c>
       <c r="D141" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A142" s="1" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D142" t="s">
         <v>142</v>
@@ -2687,7 +2663,7 @@
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A143" s="1" t="s">
-        <v>38</v>
+        <v>135</v>
       </c>
       <c r="D143" t="s">
         <v>142</v>
@@ -2695,15 +2671,15 @@
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A144" s="1" t="s">
-        <v>135</v>
+        <v>8</v>
       </c>
       <c r="D144" t="s">
-        <v>142</v>
+        <v>78</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A145" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D145" t="s">
         <v>78</v>
@@ -2711,15 +2687,15 @@
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A146" s="1" t="s">
-        <v>9</v>
+        <v>42</v>
       </c>
       <c r="D146" t="s">
-        <v>78</v>
+        <v>143</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A147" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D147" t="s">
         <v>143</v>
@@ -2727,7 +2703,7 @@
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A148" s="1" t="s">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="D148" t="s">
         <v>143</v>
@@ -2735,15 +2711,15 @@
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A149" s="1" t="s">
-        <v>94</v>
+        <v>144</v>
       </c>
       <c r="D149" t="s">
-        <v>143</v>
+        <v>96</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A150" s="1" t="s">
-        <v>144</v>
+        <v>95</v>
       </c>
       <c r="D150" t="s">
         <v>96</v>
@@ -2751,7 +2727,7 @@
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A151" s="1" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="D151" t="s">
         <v>96</v>
@@ -2759,15 +2735,15 @@
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A152" s="1" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D152" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
     </row>
     <row r="153" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A153" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D153" t="s">
         <v>112</v>
@@ -2775,23 +2751,23 @@
     </row>
     <row r="154" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A154" s="1" t="s">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="D154" t="s">
-        <v>112</v>
+        <v>12</v>
       </c>
     </row>
     <row r="155" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A155" s="1" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="D155" t="s">
-        <v>12</v>
+        <v>147</v>
       </c>
     </row>
     <row r="156" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A156" s="1" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="D156" t="s">
         <v>147</v>
@@ -2799,74 +2775,77 @@
     </row>
     <row r="157" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A157" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="D157" t="s">
-        <v>147</v>
+        <v>129</v>
       </c>
     </row>
     <row r="158" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A158" s="1" t="s">
-        <v>148</v>
+        <v>73</v>
       </c>
       <c r="D158" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
     </row>
     <row r="159" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A159" s="1" t="s">
-        <v>73</v>
+        <v>150</v>
       </c>
       <c r="D159" t="s">
-        <v>149</v>
+        <v>85</v>
       </c>
     </row>
     <row r="160" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A160" s="1" t="s">
-        <v>150</v>
+      <c r="A160" t="s">
+        <v>151</v>
       </c>
       <c r="D160" t="s">
-        <v>85</v>
+        <v>152</v>
       </c>
     </row>
     <row r="161" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A161" t="s">
-        <v>151</v>
+      <c r="A161" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="D161" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="162" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A162" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D162" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="163" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A163" s="1" t="s">
-        <v>154</v>
+      <c r="A163" t="s">
+        <v>9</v>
+      </c>
+      <c r="B163" t="s">
+        <v>157</v>
       </c>
       <c r="D163" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="164" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A164" t="s">
-        <v>9</v>
+      <c r="A164" s="1" t="s">
+        <v>158</v>
       </c>
       <c r="B164" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D164" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="165" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A165" s="1" t="s">
-        <v>158</v>
+        <v>47</v>
       </c>
       <c r="B165" t="s">
         <v>160</v>
@@ -2875,20 +2854,20 @@
         <v>159</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:4" ht="45" x14ac:dyDescent="0.45">
       <c r="A166" s="1" t="s">
-        <v>47</v>
+        <v>161</v>
       </c>
       <c r="B166" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D166" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A167" s="1" t="s">
-        <v>161</v>
+        <v>43</v>
       </c>
       <c r="B167" t="s">
         <v>163</v>
@@ -2899,7 +2878,7 @@
     </row>
     <row r="168" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A168" s="1" t="s">
-        <v>43</v>
+        <v>101</v>
       </c>
       <c r="B168" t="s">
         <v>163</v>
@@ -2910,7 +2889,7 @@
     </row>
     <row r="169" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A169" s="1" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="B169" t="s">
         <v>163</v>
@@ -2921,18 +2900,18 @@
     </row>
     <row r="170" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A170" s="1" t="s">
-        <v>95</v>
+        <v>47</v>
       </c>
       <c r="B170" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D170" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
     </row>
     <row r="171" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A171" s="1" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="B171" t="s">
         <v>164</v>
@@ -2941,53 +2920,53 @@
         <v>165</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:4" ht="45" x14ac:dyDescent="0.45">
       <c r="A172" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B172" t="s">
-        <v>164</v>
+        <v>63</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>166</v>
       </c>
       <c r="D172" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A173" s="1" t="s">
-        <v>63</v>
+        <v>110</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>166</v>
       </c>
       <c r="D173" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
     </row>
     <row r="174" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A174" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="B174" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B174" t="s">
         <v>166</v>
       </c>
       <c r="D174" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
     </row>
     <row r="175" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A175" s="1" t="s">
-        <v>54</v>
+        <v>167</v>
       </c>
       <c r="B175" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D175" t="s">
-        <v>326</v>
+        <v>56</v>
       </c>
     </row>
     <row r="176" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A176" s="1" t="s">
-        <v>167</v>
+        <v>21</v>
       </c>
       <c r="B176" t="s">
         <v>168</v>
@@ -2998,7 +2977,7 @@
     </row>
     <row r="177" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A177" s="1" t="s">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="B177" t="s">
         <v>168</v>
@@ -3009,7 +2988,7 @@
     </row>
     <row r="178" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A178" s="1" t="s">
-        <v>48</v>
+        <v>138</v>
       </c>
       <c r="B178" t="s">
         <v>168</v>
@@ -3020,18 +2999,18 @@
     </row>
     <row r="179" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A179" s="1" t="s">
-        <v>138</v>
+        <v>169</v>
       </c>
       <c r="B179" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D179" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
     </row>
     <row r="180" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A180" s="1" t="s">
-        <v>169</v>
+        <v>43</v>
       </c>
       <c r="B180" t="s">
         <v>170</v>
@@ -3042,18 +3021,18 @@
     </row>
     <row r="181" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A181" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B181" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D181" t="s">
-        <v>74</v>
+        <v>50</v>
       </c>
     </row>
     <row r="182" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A182" s="1" t="s">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="B182" t="s">
         <v>171</v>
@@ -3064,7 +3043,7 @@
     </row>
     <row r="183" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A183" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B183" t="s">
         <v>171</v>
@@ -3075,7 +3054,7 @@
     </row>
     <row r="184" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A184" s="1" t="s">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="B184" t="s">
         <v>171</v>
@@ -3086,48 +3065,48 @@
     </row>
     <row r="185" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A185" s="1" t="s">
-        <v>21</v>
+        <v>172</v>
       </c>
       <c r="B185" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D185" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="186" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A186" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B186" t="s">
-        <v>173</v>
+        <v>107</v>
       </c>
       <c r="D186" t="s">
-        <v>41</v>
+        <v>174</v>
       </c>
     </row>
     <row r="187" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A187" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D187" t="s">
-        <v>174</v>
+        <v>75</v>
+      </c>
+      <c r="B187" t="s">
+        <v>176</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="188" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A188" s="1" t="s">
-        <v>75</v>
+        <v>146</v>
       </c>
       <c r="B188" t="s">
-        <v>176</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
+      </c>
+      <c r="D188" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="189" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A189" s="1" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="B189" t="s">
         <v>177</v>
@@ -3138,7 +3117,7 @@
     </row>
     <row r="190" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A190" s="1" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B190" t="s">
         <v>177</v>
@@ -3149,18 +3128,18 @@
     </row>
     <row r="191" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A191" s="1" t="s">
-        <v>128</v>
+        <v>178</v>
       </c>
       <c r="B191" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D191" t="s">
-        <v>129</v>
+        <v>180</v>
       </c>
     </row>
     <row r="192" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A192" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B192" t="s">
         <v>181</v>
@@ -3171,7 +3150,7 @@
     </row>
     <row r="193" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A193" s="1" t="s">
-        <v>179</v>
+        <v>37</v>
       </c>
       <c r="B193" t="s">
         <v>181</v>
@@ -3182,18 +3161,18 @@
     </row>
     <row r="194" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A194" s="1" t="s">
-        <v>37</v>
+        <v>182</v>
       </c>
       <c r="B194" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="D194" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.45">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" ht="45" x14ac:dyDescent="0.45">
       <c r="A195" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B195" t="s">
         <v>185</v>
@@ -3202,9 +3181,9 @@
         <v>80</v>
       </c>
     </row>
-    <row r="196" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A196" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B196" t="s">
         <v>185</v>
@@ -3215,7 +3194,7 @@
     </row>
     <row r="197" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A197" s="1" t="s">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="B197" t="s">
         <v>185</v>
@@ -3226,62 +3205,62 @@
     </row>
     <row r="198" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A198" s="1" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="B198" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D198" t="s">
-        <v>80</v>
+        <v>317</v>
       </c>
     </row>
     <row r="199" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A199" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B199" t="s">
         <v>186</v>
       </c>
       <c r="D199" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
     </row>
     <row r="200" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A200" s="1" t="s">
-        <v>37</v>
+        <v>54</v>
       </c>
       <c r="B200" t="s">
         <v>186</v>
       </c>
       <c r="D200" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
     </row>
     <row r="201" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A201" s="1" t="s">
-        <v>54</v>
+        <v>8</v>
       </c>
       <c r="B201" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D201" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.45">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="202" spans="1:4" ht="45" x14ac:dyDescent="0.45">
       <c r="A202" s="1" t="s">
-        <v>8</v>
+        <v>188</v>
       </c>
       <c r="B202" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="D202" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A203" s="1" t="s">
-        <v>188</v>
+        <v>138</v>
       </c>
       <c r="B203" t="s">
         <v>190</v>
@@ -3292,7 +3271,7 @@
     </row>
     <row r="204" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A204" s="1" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="B204" t="s">
         <v>190</v>
@@ -3303,7 +3282,7 @@
     </row>
     <row r="205" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A205" s="1" t="s">
-        <v>146</v>
+        <v>128</v>
       </c>
       <c r="B205" t="s">
         <v>190</v>
@@ -3314,18 +3293,18 @@
     </row>
     <row r="206" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A206" s="1" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="B206" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D206" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="207" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A207" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B207" t="s">
         <v>192</v>
@@ -3336,29 +3315,29 @@
     </row>
     <row r="208" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A208" s="1" t="s">
-        <v>111</v>
+        <v>55</v>
       </c>
       <c r="B208" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D208" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A209" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B209" t="s">
-        <v>193</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="209" spans="1:4" ht="90" x14ac:dyDescent="0.45">
+      <c r="A209" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="B209" s="2" t="s">
+        <v>194</v>
       </c>
       <c r="D209" t="s">
-        <v>77</v>
+        <v>198</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="90" x14ac:dyDescent="0.45">
-      <c r="A210" s="2" t="s">
-        <v>195</v>
+      <c r="A210" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="B210" s="2" t="s">
         <v>194</v>
@@ -3369,7 +3348,7 @@
     </row>
     <row r="211" spans="1:4" ht="90" x14ac:dyDescent="0.45">
       <c r="A211" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B211" s="2" t="s">
         <v>194</v>
@@ -3378,20 +3357,20 @@
         <v>198</v>
       </c>
     </row>
-    <row r="212" spans="1:4" ht="90" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:4" ht="45" x14ac:dyDescent="0.45">
       <c r="A212" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B212" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="D212" t="s">
-        <v>198</v>
+        <v>200</v>
+      </c>
+      <c r="B212" t="s">
+        <v>199</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="45" x14ac:dyDescent="0.45">
       <c r="A213" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B213" t="s">
         <v>199</v>
@@ -3402,7 +3381,7 @@
     </row>
     <row r="214" spans="1:4" ht="45" x14ac:dyDescent="0.45">
       <c r="A214" s="1" t="s">
-        <v>201</v>
+        <v>9</v>
       </c>
       <c r="B214" t="s">
         <v>199</v>
@@ -3413,21 +3392,21 @@
     </row>
     <row r="215" spans="1:4" ht="45" x14ac:dyDescent="0.45">
       <c r="A215" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B215" t="s">
-        <v>199</v>
-      </c>
-      <c r="D215" s="2" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+      <c r="B215" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D215" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="216" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A216" s="1" t="s">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D216" t="s">
         <v>206</v>
@@ -3435,29 +3414,29 @@
     </row>
     <row r="217" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A217" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B217" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B217" t="s">
         <v>205</v>
       </c>
       <c r="D217" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:4" ht="45" x14ac:dyDescent="0.45">
       <c r="A218" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="B218" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D218" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="219" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="219" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A219" s="1" t="s">
-        <v>207</v>
+        <v>55</v>
       </c>
       <c r="B219" t="s">
         <v>208</v>
@@ -3468,7 +3447,7 @@
     </row>
     <row r="220" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A220" s="1" t="s">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="B220" t="s">
         <v>208</v>
@@ -3479,29 +3458,29 @@
     </row>
     <row r="221" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A221" s="1" t="s">
-        <v>21</v>
+        <v>133</v>
       </c>
       <c r="B221" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D221" t="s">
-        <v>209</v>
+        <v>134</v>
       </c>
     </row>
     <row r="222" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A222" s="1" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="B222" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D222" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
     </row>
     <row r="223" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A223" s="1" t="s">
-        <v>121</v>
+        <v>211</v>
       </c>
       <c r="B223" t="s">
         <v>212</v>
@@ -3512,7 +3491,7 @@
     </row>
     <row r="224" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A224" s="1" t="s">
-        <v>211</v>
+        <v>123</v>
       </c>
       <c r="B224" t="s">
         <v>212</v>
@@ -3521,47 +3500,44 @@
         <v>124</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A225" s="1" t="s">
-        <v>123</v>
+    <row r="225" spans="1:4" ht="135" x14ac:dyDescent="0.45">
+      <c r="A225" s="2" t="s">
+        <v>213</v>
       </c>
       <c r="B225" t="s">
-        <v>212</v>
-      </c>
-      <c r="D225" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="226" spans="1:4" ht="135" x14ac:dyDescent="0.45">
-      <c r="A226" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="B226" t="s">
         <v>214</v>
       </c>
-      <c r="D226" s="2" t="s">
+      <c r="D225" s="2" t="s">
         <v>215</v>
+      </c>
+    </row>
+    <row r="226" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A226" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="D226" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="227" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A227" s="1" t="s">
-        <v>216</v>
+        <v>38</v>
       </c>
       <c r="D227" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="228" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A228" s="1" t="s">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="D228" t="s">
-        <v>218</v>
+        <v>74</v>
       </c>
     </row>
     <row r="229" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A229" s="1" t="s">
-        <v>73</v>
+        <v>219</v>
       </c>
       <c r="D229" t="s">
         <v>74</v>
@@ -3569,15 +3545,15 @@
     </row>
     <row r="230" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A230" s="1" t="s">
-        <v>219</v>
+        <v>73</v>
       </c>
       <c r="D230" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
     </row>
     <row r="231" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A231" s="1" t="s">
-        <v>73</v>
+        <v>21</v>
       </c>
       <c r="D231" t="s">
         <v>52</v>
@@ -3585,39 +3561,39 @@
     </row>
     <row r="232" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A232" s="1" t="s">
-        <v>21</v>
+        <v>86</v>
       </c>
       <c r="D232" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.45">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="233" spans="1:4" ht="45" x14ac:dyDescent="0.45">
       <c r="A233" s="1" t="s">
-        <v>86</v>
+        <v>220</v>
       </c>
       <c r="D233" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="234" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="234" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A234" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="D234" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
     </row>
     <row r="235" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A235" s="1" t="s">
-        <v>222</v>
+        <v>48</v>
       </c>
       <c r="D235" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
     </row>
     <row r="236" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A236" s="1" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="D236" t="s">
         <v>224</v>
@@ -3625,7 +3601,7 @@
     </row>
     <row r="237" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A237" s="1" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="D237" t="s">
         <v>224</v>
@@ -3633,45 +3609,45 @@
     </row>
     <row r="238" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A238" s="1" t="s">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="D238" t="s">
         <v>224</v>
       </c>
     </row>
     <row r="239" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A239" s="1" t="s">
-        <v>138</v>
+      <c r="A239" t="s">
+        <v>225</v>
+      </c>
+      <c r="B239" t="s">
+        <v>226</v>
       </c>
       <c r="D239" t="s">
-        <v>224</v>
+        <v>78</v>
       </c>
     </row>
     <row r="240" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A240" t="s">
-        <v>225</v>
+      <c r="A240" s="1" t="s">
+        <v>227</v>
       </c>
       <c r="B240" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="D240" t="s">
-        <v>78</v>
+        <v>5</v>
       </c>
     </row>
     <row r="241" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A241" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="B241" t="s">
-        <v>228</v>
+      <c r="A241" s="2" t="s">
+        <v>153</v>
       </c>
       <c r="D241" t="s">
-        <v>5</v>
+        <v>229</v>
       </c>
     </row>
     <row r="242" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A242" s="2" t="s">
-        <v>153</v>
+      <c r="A242" s="1" t="s">
+        <v>154</v>
       </c>
       <c r="D242" t="s">
         <v>229</v>
@@ -3679,95 +3655,95 @@
     </row>
     <row r="243" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A243" s="1" t="s">
-        <v>154</v>
+        <v>231</v>
       </c>
       <c r="D243" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
     </row>
     <row r="244" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A244" s="1" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D244" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
     </row>
     <row r="245" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A245" s="1" t="s">
-        <v>232</v>
+      <c r="A245" t="s">
+        <v>234</v>
       </c>
       <c r="D245" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="246" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A246" t="s">
-        <v>234</v>
+      <c r="A246" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="D246" t="s">
-        <v>233</v>
+        <v>68</v>
       </c>
     </row>
     <row r="247" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A247" s="1" t="s">
-        <v>235</v>
+      <c r="A247" t="s">
+        <v>236</v>
       </c>
       <c r="D247" t="s">
-        <v>68</v>
+        <v>237</v>
       </c>
     </row>
     <row r="248" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A248" t="s">
-        <v>236</v>
+      <c r="A248" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="D248" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="249" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A249" s="1" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D249" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
     </row>
     <row r="250" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A250" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D250" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A251" s="1" t="s">
-        <v>241</v>
+    <row r="251" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+      <c r="A251" s="2" t="s">
+        <v>244</v>
       </c>
       <c r="D251" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4" ht="45" x14ac:dyDescent="0.45">
-      <c r="A252" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
+      </c>
+    </row>
+    <row r="252" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A252" t="s">
+        <v>234</v>
       </c>
       <c r="D252" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
     </row>
     <row r="253" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A253" t="s">
-        <v>234</v>
+      <c r="A253" s="1" t="s">
+        <v>246</v>
       </c>
       <c r="D253" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="254" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A254" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D254" t="s">
         <v>249</v>
@@ -3775,7 +3751,7 @@
     </row>
     <row r="255" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A255" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="D255" t="s">
         <v>249</v>
@@ -3783,15 +3759,15 @@
     </row>
     <row r="256" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A256" s="1" t="s">
-        <v>248</v>
+        <v>47</v>
       </c>
       <c r="D256" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
     </row>
     <row r="257" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A257" s="1" t="s">
-        <v>47</v>
+        <v>110</v>
       </c>
       <c r="D257" t="s">
         <v>251</v>
@@ -3799,7 +3775,7 @@
     </row>
     <row r="258" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A258" s="1" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="D258" t="s">
         <v>251</v>
@@ -3807,7 +3783,7 @@
     </row>
     <row r="259" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A259" s="1" t="s">
-        <v>123</v>
+        <v>250</v>
       </c>
       <c r="D259" t="s">
         <v>251</v>
@@ -3815,527 +3791,527 @@
     </row>
     <row r="260" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A260" s="1" t="s">
-        <v>250</v>
+        <v>234</v>
       </c>
       <c r="D260" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
     </row>
     <row r="261" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A261" s="1" t="s">
-        <v>234</v>
+        <v>18</v>
       </c>
       <c r="D261" t="s">
-        <v>245</v>
+        <v>35</v>
       </c>
     </row>
     <row r="262" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A262" s="1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D262" t="s">
-        <v>262</v>
+        <v>35</v>
       </c>
     </row>
     <row r="263" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A263" s="1" t="s">
-        <v>253</v>
+        <v>47</v>
       </c>
       <c r="D263" t="s">
-        <v>262</v>
+        <v>35</v>
       </c>
     </row>
     <row r="264" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A264" s="1" t="s">
-        <v>254</v>
+        <v>48</v>
       </c>
       <c r="D264" t="s">
-        <v>262</v>
+        <v>35</v>
       </c>
     </row>
     <row r="265" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A265" s="1" t="s">
-        <v>255</v>
+        <v>21</v>
       </c>
       <c r="D265" t="s">
-        <v>262</v>
+        <v>35</v>
       </c>
     </row>
     <row r="266" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A266" s="1" t="s">
-        <v>256</v>
+        <v>111</v>
       </c>
       <c r="D266" t="s">
-        <v>262</v>
+        <v>191</v>
       </c>
     </row>
     <row r="267" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A267" s="1" t="s">
-        <v>257</v>
+        <v>21</v>
       </c>
       <c r="D267" t="s">
-        <v>262</v>
+        <v>191</v>
       </c>
     </row>
     <row r="268" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A268" s="1" t="s">
-        <v>101</v>
+        <v>256</v>
       </c>
       <c r="D268" t="s">
-        <v>262</v>
+        <v>191</v>
       </c>
     </row>
     <row r="269" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A269" s="1" t="s">
-        <v>258</v>
+        <v>45</v>
       </c>
       <c r="D269" t="s">
-        <v>262</v>
+        <v>46</v>
       </c>
     </row>
     <row r="270" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A270" s="1" t="s">
-        <v>259</v>
+        <v>73</v>
       </c>
       <c r="D270" t="s">
-        <v>262</v>
+        <v>46</v>
       </c>
     </row>
     <row r="271" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A271" s="1" t="s">
-        <v>260</v>
+        <v>43</v>
       </c>
       <c r="D271" t="s">
-        <v>262</v>
+        <v>46</v>
       </c>
     </row>
     <row r="272" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A272" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="D272" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="273" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A273" t="s">
+        <v>257</v>
+      </c>
+      <c r="D273" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="274" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A274" t="s">
+        <v>259</v>
+      </c>
+      <c r="D274" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="275" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A275" t="s">
+        <v>260</v>
+      </c>
+      <c r="D275" t="s">
         <v>261</v>
-      </c>
-      <c r="D272" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A273" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D273" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A274" s="1" t="s">
-        <v>263</v>
-      </c>
-      <c r="D274" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A275" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D275" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="276" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A276" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D276" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
     </row>
     <row r="277" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A277" s="1" t="s">
-        <v>21</v>
+        <v>262</v>
       </c>
       <c r="D277" t="s">
-        <v>35</v>
+        <v>53</v>
       </c>
     </row>
     <row r="278" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A278" s="1" t="s">
-        <v>111</v>
+        <v>263</v>
       </c>
       <c r="D278" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
     </row>
     <row r="279" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A279" s="1" t="s">
-        <v>21</v>
+        <v>101</v>
       </c>
       <c r="D279" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
     </row>
     <row r="280" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A280" s="1" t="s">
-        <v>264</v>
+        <v>110</v>
       </c>
       <c r="D280" t="s">
-        <v>191</v>
+        <v>53</v>
       </c>
     </row>
     <row r="281" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A281" s="1" t="s">
-        <v>45</v>
+        <v>21</v>
       </c>
       <c r="D281" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="282" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A282" s="1" t="s">
-        <v>73</v>
+      <c r="A282" t="s">
+        <v>264</v>
       </c>
       <c r="D282" t="s">
-        <v>46</v>
+        <v>265</v>
       </c>
     </row>
     <row r="283" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A283" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D283" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.45">
+        <v>266</v>
+      </c>
+      <c r="D283" s="1" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="284" spans="1:4" ht="45" x14ac:dyDescent="0.45">
       <c r="A284" s="1" t="s">
-        <v>227</v>
+        <v>23</v>
       </c>
       <c r="D284" t="s">
-        <v>46</v>
+        <v>268</v>
       </c>
     </row>
     <row r="285" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A285" t="s">
-        <v>265</v>
+      <c r="A285" s="1" t="s">
+        <v>38</v>
       </c>
       <c r="D285" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="286" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A286" t="s">
-        <v>267</v>
+      <c r="A286" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="D286" t="s">
-        <v>10</v>
+        <v>268</v>
       </c>
     </row>
     <row r="287" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A287" t="s">
-        <v>268</v>
+      <c r="A287" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="D287" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="288" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A288" s="1" t="s">
-        <v>47</v>
+        <v>269</v>
       </c>
       <c r="D288" t="s">
-        <v>53</v>
+        <v>270</v>
       </c>
     </row>
     <row r="289" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A289" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D289" t="s">
         <v>270</v>
       </c>
-      <c r="D289" t="s">
-        <v>53</v>
-      </c>
     </row>
     <row r="290" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A290" s="1" t="s">
+      <c r="A290" t="s">
         <v>271</v>
       </c>
       <c r="D290" t="s">
-        <v>53</v>
+        <v>239</v>
       </c>
     </row>
     <row r="291" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A291" s="1" t="s">
-        <v>101</v>
+        <v>272</v>
       </c>
       <c r="D291" t="s">
-        <v>53</v>
+        <v>273</v>
       </c>
     </row>
     <row r="292" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A292" s="1" t="s">
-        <v>110</v>
+      <c r="A292" t="s">
+        <v>121</v>
       </c>
       <c r="D292" t="s">
-        <v>53</v>
+        <v>274</v>
       </c>
     </row>
     <row r="293" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A293" s="1" t="s">
-        <v>21</v>
+        <v>275</v>
       </c>
       <c r="D293" t="s">
-        <v>53</v>
+        <v>278</v>
       </c>
     </row>
     <row r="294" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A294" t="s">
-        <v>272</v>
+      <c r="A294" s="1" t="s">
+        <v>276</v>
       </c>
       <c r="D294" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="295" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A295" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="D295" s="1" t="s">
-        <v>275</v>
+        <v>277</v>
+      </c>
+      <c r="D295" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="296" spans="1:4" ht="45" x14ac:dyDescent="0.45">
       <c r="A296" s="1" t="s">
-        <v>23</v>
+        <v>183</v>
       </c>
       <c r="D296" t="s">
-        <v>276</v>
+        <v>175</v>
       </c>
     </row>
     <row r="297" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A297" s="1" t="s">
-        <v>38</v>
+        <v>279</v>
       </c>
       <c r="D297" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="298" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A298" s="1" t="s">
-        <v>37</v>
+        <v>58</v>
       </c>
       <c r="D298" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="299" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A299" s="1" t="s">
-        <v>101</v>
+        <v>182</v>
       </c>
       <c r="D299" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="300" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A300" s="1" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="D300" t="s">
-        <v>278</v>
+        <v>67</v>
       </c>
     </row>
     <row r="301" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A301" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D301" t="s">
-        <v>278</v>
+        <v>67</v>
       </c>
     </row>
     <row r="302" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A302" t="s">
-        <v>279</v>
+      <c r="A302" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="D302" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.45">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="303" spans="1:4" ht="45" x14ac:dyDescent="0.45">
       <c r="A303" s="1" t="s">
-        <v>280</v>
+        <v>29</v>
       </c>
       <c r="D303" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A304" t="s">
-        <v>121</v>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="304" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+      <c r="A304" s="1" t="s">
+        <v>283</v>
       </c>
       <c r="D304" t="s">
-        <v>282</v>
+        <v>99</v>
       </c>
     </row>
     <row r="305" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A305" s="1" t="s">
-        <v>283</v>
+        <v>55</v>
       </c>
       <c r="D305" t="s">
-        <v>286</v>
+        <v>99</v>
       </c>
     </row>
     <row r="306" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A306" s="1" t="s">
-        <v>284</v>
+        <v>31</v>
       </c>
       <c r="D306" t="s">
-        <v>286</v>
+        <v>99</v>
       </c>
     </row>
     <row r="307" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A307" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D307" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="308" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="308" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A308" s="1" t="s">
-        <v>183</v>
+        <v>61</v>
       </c>
       <c r="D308" t="s">
-        <v>175</v>
+        <v>242</v>
       </c>
     </row>
     <row r="309" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A309" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="D309" t="s">
-        <v>288</v>
+        <v>242</v>
       </c>
     </row>
     <row r="310" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A310" s="1" t="s">
-        <v>58</v>
+        <v>241</v>
       </c>
       <c r="D310" t="s">
-        <v>288</v>
+        <v>242</v>
       </c>
     </row>
     <row r="311" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A311" s="1" t="s">
-        <v>182</v>
+        <v>269</v>
       </c>
       <c r="D311" t="s">
-        <v>289</v>
+        <v>242</v>
       </c>
     </row>
     <row r="312" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A312" s="1" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="D312" t="s">
-        <v>67</v>
+        <v>242</v>
       </c>
     </row>
     <row r="313" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A313" s="1" t="s">
-        <v>60</v>
+        <v>95</v>
       </c>
       <c r="D313" t="s">
-        <v>67</v>
+        <v>287</v>
       </c>
     </row>
     <row r="314" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A314" s="1" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="D314" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="315" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="315" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A315" s="1" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="D315" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="316" spans="1:4" ht="45" x14ac:dyDescent="0.45">
-      <c r="A316" s="1" t="s">
-        <v>291</v>
+        <v>287</v>
+      </c>
+    </row>
+    <row r="316" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A316" t="s">
+        <v>288</v>
       </c>
       <c r="D316" t="s">
-        <v>99</v>
+        <v>289</v>
       </c>
     </row>
     <row r="317" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A317" s="1" t="s">
-        <v>55</v>
+        <v>234</v>
       </c>
       <c r="D317" t="s">
-        <v>99</v>
+        <v>223</v>
       </c>
     </row>
     <row r="318" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A318" s="1" t="s">
-        <v>31</v>
+        <v>269</v>
       </c>
       <c r="D318" t="s">
-        <v>99</v>
+        <v>290</v>
       </c>
     </row>
     <row r="319" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A319" s="1" t="s">
-        <v>292</v>
+        <v>240</v>
       </c>
       <c r="D319" t="s">
-        <v>99</v>
+        <v>290</v>
       </c>
     </row>
     <row r="320" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A320" s="1" t="s">
-        <v>61</v>
+        <v>222</v>
       </c>
       <c r="D320" t="s">
-        <v>242</v>
+        <v>290</v>
       </c>
     </row>
     <row r="321" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A321" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D321" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="322" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A322" t="s">
+        <v>291</v>
+      </c>
+      <c r="D322" s="1" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="323" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A323" t="s">
         <v>293</v>
       </c>
-      <c r="D321" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="322" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A322" s="1" t="s">
-        <v>241</v>
-      </c>
-      <c r="D322" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="323" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A323" s="1" t="s">
-        <v>277</v>
-      </c>
       <c r="D323" t="s">
-        <v>242</v>
+        <v>294</v>
       </c>
     </row>
     <row r="324" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A324" s="1" t="s">
-        <v>294</v>
+        <v>26</v>
       </c>
       <c r="D324" t="s">
-        <v>242</v>
+        <v>295</v>
       </c>
     </row>
     <row r="325" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A325" s="1" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="D325" t="s">
         <v>295</v>
@@ -4343,214 +4319,214 @@
     </row>
     <row r="326" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A326" s="1" t="s">
-        <v>102</v>
+        <v>146</v>
       </c>
       <c r="D326" t="s">
-        <v>295</v>
+        <v>129</v>
       </c>
     </row>
     <row r="327" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A327" s="1" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="D327" t="s">
-        <v>295</v>
+        <v>129</v>
       </c>
     </row>
     <row r="328" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A328" t="s">
-        <v>296</v>
+      <c r="A328" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="D328" t="s">
-        <v>297</v>
+        <v>129</v>
       </c>
     </row>
     <row r="329" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A329" s="1" t="s">
-        <v>234</v>
+        <v>296</v>
       </c>
       <c r="D329" t="s">
-        <v>223</v>
+        <v>301</v>
       </c>
     </row>
     <row r="330" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A330" s="1" t="s">
-        <v>277</v>
+        <v>297</v>
       </c>
       <c r="D330" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="331" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A331" s="1" t="s">
-        <v>240</v>
+        <v>298</v>
       </c>
       <c r="D331" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="332" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A332" s="1" t="s">
-        <v>222</v>
+        <v>299</v>
       </c>
       <c r="D332" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="333" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A333" s="1" t="s">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="D333" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="334" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A334" t="s">
-        <v>299</v>
-      </c>
-      <c r="D334" s="1" t="s">
-        <v>300</v>
+      <c r="A334" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D334" t="s">
+        <v>319</v>
       </c>
     </row>
     <row r="335" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A335" t="s">
-        <v>301</v>
+      <c r="A335" s="1" t="s">
+        <v>49</v>
       </c>
       <c r="D335" t="s">
-        <v>302</v>
+        <v>99</v>
       </c>
     </row>
     <row r="336" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A336" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D336" t="s">
-        <v>303</v>
+        <v>99</v>
       </c>
     </row>
     <row r="337" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A337" s="1" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="D337" t="s">
-        <v>303</v>
+        <v>99</v>
       </c>
     </row>
     <row r="338" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A338" s="1" t="s">
-        <v>146</v>
+        <v>302</v>
       </c>
       <c r="D338" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
     </row>
     <row r="339" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A339" s="1" t="s">
-        <v>24</v>
+        <v>146</v>
       </c>
       <c r="D339" t="s">
-        <v>129</v>
+        <v>304</v>
       </c>
     </row>
     <row r="340" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A340" s="1" t="s">
-        <v>27</v>
+        <v>303</v>
       </c>
       <c r="D340" t="s">
-        <v>129</v>
+        <v>304</v>
       </c>
     </row>
     <row r="341" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A341" s="1" t="s">
-        <v>304</v>
+        <v>47</v>
       </c>
       <c r="D341" t="s">
-        <v>309</v>
+        <v>124</v>
       </c>
     </row>
     <row r="342" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A342" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D342" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="343" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A343" t="s">
+        <v>244</v>
+      </c>
+      <c r="D343" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="344" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A344" t="s">
         <v>305</v>
       </c>
-      <c r="D342" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="343" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A343" s="1" t="s">
+      <c r="D344" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="345" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+      <c r="A345" s="1" t="s">
         <v>306</v>
       </c>
-      <c r="D343" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="344" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A344" s="1" t="s">
+      <c r="D345" t="s">
         <v>307</v>
-      </c>
-      <c r="D344" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="345" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A345" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="D345" t="s">
-        <v>309</v>
       </c>
     </row>
     <row r="346" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A346" s="1" t="s">
-        <v>54</v>
+        <v>308</v>
       </c>
       <c r="D346" t="s">
-        <v>327</v>
+        <v>309</v>
       </c>
     </row>
     <row r="347" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A347" s="1" t="s">
-        <v>49</v>
+        <v>138</v>
       </c>
       <c r="D347" t="s">
-        <v>99</v>
+        <v>309</v>
       </c>
     </row>
     <row r="348" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A348" s="1" t="s">
-        <v>24</v>
+        <v>201</v>
       </c>
       <c r="D348" t="s">
-        <v>99</v>
+        <v>309</v>
       </c>
     </row>
     <row r="349" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A349" s="1" t="s">
-        <v>22</v>
+      <c r="A349" t="s">
+        <v>128</v>
       </c>
       <c r="D349" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="350" spans="1:4" x14ac:dyDescent="0.45">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="350" spans="1:4" ht="45" x14ac:dyDescent="0.45">
       <c r="A350" s="1" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D350" t="s">
-        <v>99</v>
+        <v>149</v>
       </c>
     </row>
     <row r="351" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A351" s="1" t="s">
-        <v>146</v>
+        <v>182</v>
       </c>
       <c r="D351" t="s">
-        <v>312</v>
+        <v>149</v>
       </c>
     </row>
     <row r="352" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A352" s="1" t="s">
+      <c r="A352" t="s">
         <v>311</v>
       </c>
       <c r="D352" t="s">
@@ -4559,319 +4535,319 @@
     </row>
     <row r="353" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A353" s="1" t="s">
-        <v>47</v>
+        <v>313</v>
+      </c>
+      <c r="B353" t="s">
+        <v>316</v>
       </c>
       <c r="D353" t="s">
-        <v>124</v>
+        <v>72</v>
       </c>
     </row>
     <row r="354" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A354" s="1" t="s">
-        <v>26</v>
+        <v>314</v>
+      </c>
+      <c r="B354" t="s">
+        <v>316</v>
       </c>
       <c r="D354" t="s">
-        <v>124</v>
+        <v>72</v>
       </c>
     </row>
     <row r="355" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A355" t="s">
-        <v>244</v>
+      <c r="A355" s="1" t="s">
+        <v>315</v>
+      </c>
+      <c r="B355" t="s">
+        <v>316</v>
       </c>
       <c r="D355" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="356" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A356" t="s">
-        <v>313</v>
+      <c r="A356" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="D356" t="s">
-        <v>77</v>
+        <v>320</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="45" x14ac:dyDescent="0.45">
       <c r="A357" s="1" t="s">
-        <v>314</v>
+        <v>63</v>
       </c>
       <c r="D357" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="358" spans="1:4" x14ac:dyDescent="0.45">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="358" spans="1:4" ht="45" x14ac:dyDescent="0.45">
       <c r="A358" s="1" t="s">
-        <v>316</v>
+        <v>63</v>
       </c>
       <c r="D358" t="s">
-        <v>317</v>
+        <v>115</v>
       </c>
     </row>
     <row r="359" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A359" s="1" t="s">
-        <v>138</v>
+        <v>321</v>
       </c>
       <c r="D359" t="s">
-        <v>317</v>
+        <v>115</v>
       </c>
     </row>
     <row r="360" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A360" s="1" t="s">
-        <v>201</v>
+        <v>38</v>
       </c>
       <c r="D360" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
     </row>
     <row r="361" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A361" t="s">
-        <v>128</v>
+      <c r="A361" s="1" t="s">
+        <v>37</v>
       </c>
       <c r="D361" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="362" spans="1:4" ht="45" x14ac:dyDescent="0.45">
-      <c r="A362" s="1" t="s">
-        <v>314</v>
+        <v>322</v>
+      </c>
+    </row>
+    <row r="362" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A362" t="s">
+        <v>323</v>
       </c>
       <c r="D362" t="s">
-        <v>149</v>
+        <v>324</v>
       </c>
     </row>
     <row r="363" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A363" s="1" t="s">
-        <v>182</v>
+      <c r="A363" t="s">
+        <v>323</v>
       </c>
       <c r="D363" t="s">
-        <v>149</v>
+        <v>325</v>
       </c>
     </row>
     <row r="364" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A364" t="s">
-        <v>319</v>
+      <c r="A364" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="D364" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
     </row>
     <row r="365" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A365" s="1" t="s">
-        <v>321</v>
-      </c>
-      <c r="B365" t="s">
-        <v>324</v>
+        <v>259</v>
       </c>
       <c r="D365" t="s">
-        <v>72</v>
+        <v>326</v>
       </c>
     </row>
     <row r="366" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A366" s="1" t="s">
-        <v>322</v>
-      </c>
-      <c r="B366" t="s">
-        <v>324</v>
+        <v>231</v>
       </c>
       <c r="D366" t="s">
-        <v>72</v>
+        <v>326</v>
       </c>
     </row>
     <row r="367" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A367" s="1" t="s">
-        <v>323</v>
+        <v>37</v>
       </c>
       <c r="B367" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="D367" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="368" spans="1:4" x14ac:dyDescent="0.45">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="368" spans="1:4" ht="45" x14ac:dyDescent="0.45">
       <c r="A368" s="1" t="s">
-        <v>37</v>
+        <v>63</v>
+      </c>
+      <c r="B368" t="s">
+        <v>328</v>
       </c>
       <c r="D368" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="369" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="369" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A369" s="1" t="s">
-        <v>63</v>
+        <v>18</v>
+      </c>
+      <c r="B369" t="s">
+        <v>329</v>
       </c>
       <c r="D369" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="370" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="370" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A370" s="1" t="s">
-        <v>63</v>
+        <v>26</v>
+      </c>
+      <c r="B370" t="s">
+        <v>329</v>
       </c>
       <c r="D370" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="371" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A371" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B371" t="s">
         <v>329</v>
       </c>
       <c r="D371" t="s">
-        <v>115</v>
+        <v>100</v>
       </c>
     </row>
     <row r="372" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A372" s="1" t="s">
-        <v>38</v>
+        <v>330</v>
       </c>
       <c r="D372" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
     </row>
     <row r="373" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A373" s="1" t="s">
-        <v>37</v>
+      <c r="A373" t="s">
+        <v>252</v>
       </c>
       <c r="D373" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="374" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A374" t="s">
-        <v>331</v>
+        <v>332</v>
+      </c>
+    </row>
+    <row r="374" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+      <c r="A374" s="1" t="s">
+        <v>161</v>
       </c>
       <c r="D374" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="375" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A375" t="s">
-        <v>331</v>
+        <v>96</v>
+      </c>
+    </row>
+    <row r="375" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+      <c r="A375" s="1" t="s">
+        <v>333</v>
       </c>
       <c r="D375" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="376" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A376" s="1" t="s">
-        <v>47</v>
+        <v>101</v>
       </c>
       <c r="D376" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="377" spans="1:4" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:4" ht="45" x14ac:dyDescent="0.45">
       <c r="A377" s="1" t="s">
-        <v>267</v>
+        <v>333</v>
       </c>
       <c r="D377" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="378" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A378" s="1" t="s">
-        <v>231</v>
+        <v>101</v>
       </c>
       <c r="D378" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="379" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A379" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B379" t="s">
+      <c r="A379" t="s">
+        <v>254</v>
+      </c>
+      <c r="D379" t="s">
         <v>336</v>
       </c>
-      <c r="D379" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="380" spans="1:4" ht="45" x14ac:dyDescent="0.45">
-      <c r="A380" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B380" t="s">
-        <v>336</v>
+    </row>
+    <row r="380" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A380" t="s">
+        <v>337</v>
       </c>
       <c r="D380" t="s">
-        <v>335</v>
+        <v>295</v>
       </c>
     </row>
     <row r="381" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A381" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B381" t="s">
-        <v>337</v>
+        <v>138</v>
       </c>
       <c r="D381" t="s">
-        <v>100</v>
+        <v>340</v>
       </c>
     </row>
     <row r="382" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A382" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B382" t="s">
-        <v>337</v>
+        <v>146</v>
       </c>
       <c r="D382" t="s">
-        <v>100</v>
+        <v>340</v>
       </c>
     </row>
     <row r="383" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A383" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B383" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D383" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="384" spans="1:4" x14ac:dyDescent="0.45">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="384" spans="1:4" ht="45" x14ac:dyDescent="0.45">
       <c r="A384" s="1" t="s">
-        <v>338</v>
+        <v>23</v>
       </c>
       <c r="D384" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="385" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A385" t="s">
-        <v>255</v>
+      <c r="A385" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="D385" t="s">
         <v>340</v>
       </c>
     </row>
-    <row r="386" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A386" s="1" t="s">
-        <v>161</v>
+        <v>339</v>
       </c>
       <c r="D386" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="387" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="387" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A387" s="1" t="s">
-        <v>341</v>
+        <v>200</v>
       </c>
       <c r="D387" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
     </row>
     <row r="388" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A388" s="1" t="s">
-        <v>101</v>
+        <v>341</v>
       </c>
       <c r="D388" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="389" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A389" s="1" t="s">
         <v>342</v>
-      </c>
-    </row>
-    <row r="389" spans="1:4" ht="45" x14ac:dyDescent="0.45">
-      <c r="A389" s="1" t="s">
-        <v>341</v>
       </c>
       <c r="D389" t="s">
         <v>343</v>
@@ -4879,159 +4855,168 @@
     </row>
     <row r="390" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A390" s="1" t="s">
-        <v>101</v>
+        <v>344</v>
       </c>
       <c r="D390" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="391" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A391" t="s">
-        <v>258</v>
+      <c r="A391" s="1" t="s">
+        <v>47</v>
       </c>
       <c r="D391" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="392" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A392" t="s">
+      <c r="A392" s="1" t="s">
         <v>345</v>
       </c>
       <c r="D392" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="393" spans="1:4" x14ac:dyDescent="0.45">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="393" spans="1:4" ht="45" x14ac:dyDescent="0.45">
       <c r="A393" s="1" t="s">
-        <v>138</v>
+        <v>306</v>
       </c>
       <c r="D393" t="s">
-        <v>348</v>
+        <v>74</v>
       </c>
     </row>
     <row r="394" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A394" s="1" t="s">
-        <v>146</v>
+        <v>18</v>
       </c>
       <c r="D394" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="395" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A395" s="1" t="s">
-        <v>346</v>
+        <v>26</v>
       </c>
       <c r="D395" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="396" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="396" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A396" s="1" t="s">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="D396" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="397" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A397" s="1" t="s">
-        <v>113</v>
+        <v>21</v>
       </c>
       <c r="D397" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="398" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A398" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="398" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A398" s="1" t="s">
-        <v>347</v>
-      </c>
       <c r="D398" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="399" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A399" s="1" t="s">
-        <v>200</v>
+      <c r="A399" t="s">
+        <v>350</v>
       </c>
       <c r="D399" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
     </row>
     <row r="400" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A400" s="1" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D400" t="s">
-        <v>351</v>
+        <v>175</v>
       </c>
     </row>
     <row r="401" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A401" s="1" t="s">
-        <v>350</v>
+      <c r="A401" t="s">
+        <v>352</v>
       </c>
       <c r="D401" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="402" spans="1:4" x14ac:dyDescent="0.45">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="402" spans="1:4" ht="23.25" x14ac:dyDescent="0.5">
       <c r="A402" s="1" t="s">
-        <v>352</v>
+        <v>136</v>
+      </c>
+      <c r="B402" s="3" t="s">
+        <v>354</v>
       </c>
       <c r="D402" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="403" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A403" s="1" t="s">
-        <v>47</v>
+        <v>184</v>
+      </c>
+      <c r="B403" t="s">
+        <v>354</v>
       </c>
       <c r="D403" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="404" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A404" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B404" t="s">
+        <v>354</v>
+      </c>
+      <c r="D404" t="s">
         <v>353</v>
       </c>
-      <c r="D404" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="405" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+    </row>
+    <row r="405" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A405" s="1" t="s">
-        <v>314</v>
+        <v>81</v>
       </c>
       <c r="D405" t="s">
-        <v>74</v>
+        <v>312</v>
       </c>
     </row>
     <row r="406" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A406" s="1" t="s">
-        <v>18</v>
+        <v>275</v>
       </c>
       <c r="D406" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="407" spans="1:4" x14ac:dyDescent="0.45">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="407" spans="1:4" ht="45" x14ac:dyDescent="0.45">
       <c r="A407" s="1" t="s">
-        <v>26</v>
+        <v>207</v>
       </c>
       <c r="D407" t="s">
-        <v>355</v>
+        <v>80</v>
       </c>
     </row>
     <row r="408" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A408" s="1" t="s">
-        <v>48</v>
+        <v>344</v>
       </c>
       <c r="D408" t="s">
-        <v>355</v>
+        <v>80</v>
       </c>
     </row>
     <row r="409" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A409" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="D409" t="s">
         <v>355</v>
@@ -5039,64 +5024,58 @@
     </row>
     <row r="410" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A410" t="s">
+        <v>244</v>
+      </c>
+      <c r="D410" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="411" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+      <c r="A411" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B411" t="s">
         <v>356</v>
       </c>
-      <c r="D410" t="s">
+      <c r="D411" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="412" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A412" t="s">
         <v>357</v>
       </c>
-    </row>
-    <row r="411" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A411" t="s">
+      <c r="D412" t="s">
         <v>358</v>
       </c>
-      <c r="D411" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="412" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A412" s="1" t="s">
+    </row>
+    <row r="413" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A413" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D413" t="s">
         <v>359</v>
       </c>
-      <c r="D412" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="413" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A413" t="s">
-        <v>360</v>
-      </c>
-      <c r="D413" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="414" spans="1:4" ht="23.25" x14ac:dyDescent="0.5">
+    </row>
+    <row r="414" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A414" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="B414" s="3" t="s">
-        <v>362</v>
+        <v>9</v>
       </c>
       <c r="D414" t="s">
-        <v>361</v>
+        <v>125</v>
       </c>
     </row>
     <row r="415" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A415" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="B415" t="s">
-        <v>362</v>
+        <v>259</v>
       </c>
       <c r="D415" t="s">
-        <v>361</v>
+        <v>125</v>
       </c>
     </row>
     <row r="416" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A416" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B416" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="D416" t="s">
         <v>361</v>
@@ -5104,189 +5083,90 @@
     </row>
     <row r="417" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A417" s="1" t="s">
-        <v>81</v>
+        <v>262</v>
       </c>
       <c r="D417" t="s">
-        <v>320</v>
+        <v>361</v>
       </c>
     </row>
     <row r="418" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A418" s="1" t="s">
-        <v>283</v>
+        <v>61</v>
       </c>
       <c r="D418" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="419" spans="1:4" ht="45" x14ac:dyDescent="0.45">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="419" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A419" s="1" t="s">
-        <v>207</v>
+        <v>73</v>
       </c>
       <c r="D419" t="s">
-        <v>80</v>
+        <v>362</v>
       </c>
     </row>
     <row r="420" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A420" s="1" t="s">
-        <v>352</v>
+        <v>43</v>
       </c>
       <c r="D420" t="s">
-        <v>80</v>
+        <v>362</v>
       </c>
     </row>
     <row r="421" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A421" s="1" t="s">
-        <v>18</v>
+        <v>227</v>
       </c>
       <c r="D421" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="422" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A422" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D422" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="423" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A423" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D423" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="424" spans="1:4" x14ac:dyDescent="0.45">
+      <c r="A424" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D424" t="s">
         <v>363</v>
-      </c>
-    </row>
-    <row r="422" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A422" t="s">
-        <v>244</v>
-      </c>
-      <c r="D422" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="423" spans="1:4" ht="45" x14ac:dyDescent="0.45">
-      <c r="A423" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B423" t="s">
-        <v>364</v>
-      </c>
-      <c r="D423" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="424" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A424" t="s">
-        <v>365</v>
-      </c>
-      <c r="D424" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="425" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A425" s="1" t="s">
-        <v>79</v>
+        <v>252</v>
       </c>
       <c r="D425" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
     </row>
     <row r="426" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A426" s="1" t="s">
-        <v>9</v>
+        <v>364</v>
       </c>
       <c r="D426" t="s">
-        <v>125</v>
+        <v>365</v>
       </c>
     </row>
     <row r="427" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A427" s="1" t="s">
-        <v>267</v>
+        <v>24</v>
       </c>
       <c r="D427" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="428" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A428" s="1" t="s">
-        <v>368</v>
-      </c>
-      <c r="D428" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="429" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A429" s="1" t="s">
-        <v>270</v>
-      </c>
-      <c r="D429" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="430" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A430" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="D430" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="431" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A431" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D431" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="432" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A432" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D432" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="433" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A433" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="D433" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="434" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A434" s="1" t="s">
-        <v>231</v>
-      </c>
-      <c r="D434" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="435" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A435" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="D435" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="436" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A436" s="1" t="s">
-        <v>256</v>
-      </c>
-      <c r="D436" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="437" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A437" s="1" t="s">
-        <v>255</v>
-      </c>
-      <c r="D437" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="438" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A438" s="1" t="s">
-        <v>372</v>
-      </c>
-      <c r="D438" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="439" spans="1:4" x14ac:dyDescent="0.45">
-      <c r="A439" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D439" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
     </row>
   </sheetData>

--- a/DRUG DISEASE.xlsx
+++ b/DRUG DISEASE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT Room\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00876FA9-A976-438D-BA54-42A754013B25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3093246-44F4-4B8C-ABD6-625F8D07DC0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{3244C3E9-4DF0-4247-BD4E-75BB2D6BE0CE}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="12210" windowHeight="12885" xr2:uid="{3244C3E9-4DF0-4247-BD4E-75BB2D6BE0CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="931" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="739">
   <si>
     <t>ชื่อยา</t>
   </si>
@@ -1138,6 +1138,1128 @@
   </si>
   <si>
     <t>M793</t>
+  </si>
+  <si>
+    <t>ORS</t>
+  </si>
+  <si>
+    <t>อหิวาตกโรค</t>
+  </si>
+  <si>
+    <t>A00</t>
+  </si>
+  <si>
+    <t>Doxycycline</t>
+  </si>
+  <si>
+    <t>Azithromycin</t>
+  </si>
+  <si>
+    <t>Ciprofloxacin</t>
+  </si>
+  <si>
+    <t>ไทฟอยด์</t>
+  </si>
+  <si>
+    <t>A01</t>
+  </si>
+  <si>
+    <t>Ceftriaxone</t>
+  </si>
+  <si>
+    <t>Metronidazole</t>
+  </si>
+  <si>
+    <t>A02</t>
+  </si>
+  <si>
+    <t>A03</t>
+  </si>
+  <si>
+    <t>ชิเกลโลซิส</t>
+  </si>
+  <si>
+    <t>A04</t>
+  </si>
+  <si>
+    <t>Vancomycin</t>
+  </si>
+  <si>
+    <t>A04.7</t>
+  </si>
+  <si>
+    <t>ลำไส้อักเสบ</t>
+  </si>
+  <si>
+    <t>อาหารเป็นพิษ</t>
+  </si>
+  <si>
+    <t>A05</t>
+  </si>
+  <si>
+    <t>Activated charcoal</t>
+  </si>
+  <si>
+    <t>บิดอะมีบา</t>
+  </si>
+  <si>
+    <t>A06</t>
+  </si>
+  <si>
+    <t>Tinidazole</t>
+  </si>
+  <si>
+    <t>Paromomycin</t>
+  </si>
+  <si>
+    <t>A07</t>
+  </si>
+  <si>
+    <t>Nitazoxanide</t>
+  </si>
+  <si>
+    <t>ท้องเสียไวรัส</t>
+  </si>
+  <si>
+    <t>A08</t>
+  </si>
+  <si>
+    <t>Zinc</t>
+  </si>
+  <si>
+    <t>ท้องเสียไม่ทราบสาเหตุ</t>
+  </si>
+  <si>
+    <t>A09</t>
+  </si>
+  <si>
+    <t>Paracetamol</t>
+  </si>
+  <si>
+    <t>A15</t>
+  </si>
+  <si>
+    <t>Isoniazid</t>
+  </si>
+  <si>
+    <t>วัณโรค</t>
+  </si>
+  <si>
+    <t>Rifampicin</t>
+  </si>
+  <si>
+    <t>Ethambutol</t>
+  </si>
+  <si>
+    <t>Pyrazinamide</t>
+  </si>
+  <si>
+    <t>Dapsone</t>
+  </si>
+  <si>
+    <t>โรคเรื้อน</t>
+  </si>
+  <si>
+    <t>A30</t>
+  </si>
+  <si>
+    <t>Clofazimine</t>
+  </si>
+  <si>
+    <t>Penicillin G</t>
+  </si>
+  <si>
+    <t>ซิฟิลิส</t>
+  </si>
+  <si>
+    <t>Benzathine penicillin</t>
+  </si>
+  <si>
+    <t>หนองใน</t>
+  </si>
+  <si>
+    <t>A54</t>
+  </si>
+  <si>
+    <t>หนองในเทียม</t>
+  </si>
+  <si>
+    <t>Trichomoniasis</t>
+  </si>
+  <si>
+    <t>A59</t>
+  </si>
+  <si>
+    <t>Acyclovir</t>
+  </si>
+  <si>
+    <t>Herpes simplex</t>
+  </si>
+  <si>
+    <t>A60</t>
+  </si>
+  <si>
+    <t>Valacyclovir</t>
+  </si>
+  <si>
+    <t>Oseltamivir</t>
+  </si>
+  <si>
+    <t>ไข้หวัดใหญ่</t>
+  </si>
+  <si>
+    <t>Zidovudine</t>
+  </si>
+  <si>
+    <t>HIV</t>
+  </si>
+  <si>
+    <t>B20</t>
+  </si>
+  <si>
+    <t>Tenofovir</t>
+  </si>
+  <si>
+    <t>Lamivudine</t>
+  </si>
+  <si>
+    <t>Efavirenz</t>
+  </si>
+  <si>
+    <t>Fluconazole</t>
+  </si>
+  <si>
+    <t>เชื้อรา Candida</t>
+  </si>
+  <si>
+    <t>B37</t>
+  </si>
+  <si>
+    <t>Clotrimazole</t>
+  </si>
+  <si>
+    <t>เชื้อรา</t>
+  </si>
+  <si>
+    <t>Terbinafine</t>
+  </si>
+  <si>
+    <t>B35</t>
+  </si>
+  <si>
+    <t>Amphotericin B</t>
+  </si>
+  <si>
+    <t>เชื้อรารุนแรง</t>
+  </si>
+  <si>
+    <t>Albendazole</t>
+  </si>
+  <si>
+    <t>พยาธิ</t>
+  </si>
+  <si>
+    <t>Mebendazole</t>
+  </si>
+  <si>
+    <t>Ivermectin</t>
+  </si>
+  <si>
+    <t>Praziquantel</t>
+  </si>
+  <si>
+    <t>พยาธิใบไม้</t>
+  </si>
+  <si>
+    <t>B65</t>
+  </si>
+  <si>
+    <t>ซัลโมเนลลา</t>
+  </si>
+  <si>
+    <t>ติดเชื้อ E. coli</t>
+  </si>
+  <si>
+    <t>ท้องเสียจากแบคทีเรีย</t>
+  </si>
+  <si>
+    <t>โปรโตซัว</t>
+  </si>
+  <si>
+    <t>Herpes</t>
+  </si>
+  <si>
+    <t>A50</t>
+  </si>
+  <si>
+    <t>A56</t>
+  </si>
+  <si>
+    <t>B40</t>
+  </si>
+  <si>
+    <t>Famciclovir</t>
+  </si>
+  <si>
+    <t>Ganciclovir</t>
+  </si>
+  <si>
+    <t>Valganciclovir</t>
+  </si>
+  <si>
+    <t>Zanamivir</t>
+  </si>
+  <si>
+    <t>Ribavirin</t>
+  </si>
+  <si>
+    <t>Interferon</t>
+  </si>
+  <si>
+    <t>Dolutegravir</t>
+  </si>
+  <si>
+    <t>Itraconazole</t>
+  </si>
+  <si>
+    <t>Ketoconazole</t>
+  </si>
+  <si>
+    <t>Nystatin</t>
+  </si>
+  <si>
+    <t>Griseofulvin</t>
+  </si>
+  <si>
+    <t>Diethylcarbamazine</t>
+  </si>
+  <si>
+    <t>Niclosamide</t>
+  </si>
+  <si>
+    <t>Pentamidine</t>
+  </si>
+  <si>
+    <t>Trimethoprim-sulfamethoxazole</t>
+  </si>
+  <si>
+    <t>Clindamycin</t>
+  </si>
+  <si>
+    <t>Atovaquone</t>
+  </si>
+  <si>
+    <t>Artemisinin</t>
+  </si>
+  <si>
+    <t>Chloroquine</t>
+  </si>
+  <si>
+    <t>Primaquine</t>
+  </si>
+  <si>
+    <t>Quinine</t>
+  </si>
+  <si>
+    <t>Cytomegalovirus</t>
+  </si>
+  <si>
+    <t>ไวรัส RSV</t>
+  </si>
+  <si>
+    <t>ไวรัสตับอักเสบ</t>
+  </si>
+  <si>
+    <t>เชื้อราผิวหนัง</t>
+  </si>
+  <si>
+    <t>พยาธิฟิลาเรีย</t>
+  </si>
+  <si>
+    <t>พยาธิตัวตืด</t>
+  </si>
+  <si>
+    <t>Pneumocystis</t>
+  </si>
+  <si>
+    <t>ติดเชื้อฉวยโอกาส</t>
+  </si>
+  <si>
+    <t>มาลาเรีย</t>
+  </si>
+  <si>
+    <t>B00</t>
+  </si>
+  <si>
+    <t>B25</t>
+  </si>
+  <si>
+    <t>J10</t>
+  </si>
+  <si>
+    <t>B97</t>
+  </si>
+  <si>
+    <t>B18</t>
+  </si>
+  <si>
+    <t>B74</t>
+  </si>
+  <si>
+    <t>B68</t>
+  </si>
+  <si>
+    <t>B50</t>
+  </si>
+  <si>
+    <t>B59</t>
+  </si>
+  <si>
+    <t>Cisplatin</t>
+  </si>
+  <si>
+    <t>Carboplatin</t>
+  </si>
+  <si>
+    <t>Paclitaxel</t>
+  </si>
+  <si>
+    <t>Docetaxel</t>
+  </si>
+  <si>
+    <t>5-Fluorouracil</t>
+  </si>
+  <si>
+    <t>Capecitabine</t>
+  </si>
+  <si>
+    <t>Doxorubicin</t>
+  </si>
+  <si>
+    <t>Epirubicin</t>
+  </si>
+  <si>
+    <t>Cyclophosphamide</t>
+  </si>
+  <si>
+    <t>Methotrexate</t>
+  </si>
+  <si>
+    <t>Imatinib</t>
+  </si>
+  <si>
+    <t>Trastuzumab</t>
+  </si>
+  <si>
+    <t>Tamoxifen</t>
+  </si>
+  <si>
+    <t>Letrozole</t>
+  </si>
+  <si>
+    <t>Anastrozole</t>
+  </si>
+  <si>
+    <t>Leuprolide</t>
+  </si>
+  <si>
+    <t>Bicalutamide</t>
+  </si>
+  <si>
+    <t>Flutamide</t>
+  </si>
+  <si>
+    <t>Rituximab</t>
+  </si>
+  <si>
+    <t>Bevacizumab</t>
+  </si>
+  <si>
+    <t>Sorafenib</t>
+  </si>
+  <si>
+    <t>Sunitinib</t>
+  </si>
+  <si>
+    <t>Etoposide</t>
+  </si>
+  <si>
+    <t>Vincristine</t>
+  </si>
+  <si>
+    <t>Vinblastine</t>
+  </si>
+  <si>
+    <t>Bleomycin</t>
+  </si>
+  <si>
+    <t>Gemcitabine</t>
+  </si>
+  <si>
+    <t>Oxaliplatin</t>
+  </si>
+  <si>
+    <t>Irinotecan</t>
+  </si>
+  <si>
+    <t>Pembrolizumab</t>
+  </si>
+  <si>
+    <t>Nivolumab</t>
+  </si>
+  <si>
+    <t>Atezolizumab</t>
+  </si>
+  <si>
+    <t>Durvalumab</t>
+  </si>
+  <si>
+    <t>Cetuximab</t>
+  </si>
+  <si>
+    <t>Panitumumab</t>
+  </si>
+  <si>
+    <t>Lapatinib</t>
+  </si>
+  <si>
+    <t>Everolimus</t>
+  </si>
+  <si>
+    <t>Temsirolimus</t>
+  </si>
+  <si>
+    <t>Dasatinib</t>
+  </si>
+  <si>
+    <t>Nilotinib</t>
+  </si>
+  <si>
+    <t>มะเร็งช่องปาก</t>
+  </si>
+  <si>
+    <t>มะเร็งเต้านม</t>
+  </si>
+  <si>
+    <t>มะเร็งลำไส้ใหญ่</t>
+  </si>
+  <si>
+    <t>มะเร็งต่อมน้ำเหลือง</t>
+  </si>
+  <si>
+    <t>มะเร็งเม็ดเลือด</t>
+  </si>
+  <si>
+    <t>มะเร็งเม็ดเลือดขาว</t>
+  </si>
+  <si>
+    <t>มะเร็งต่อมลูกหมาก</t>
+  </si>
+  <si>
+    <t>มะเร็งลำไส้</t>
+  </si>
+  <si>
+    <t>มะเร็งตับ</t>
+  </si>
+  <si>
+    <t>มะเร็งไต</t>
+  </si>
+  <si>
+    <t>มะเร็งปอด</t>
+  </si>
+  <si>
+    <t>มะเร็งอัณฑะ</t>
+  </si>
+  <si>
+    <t>มะเร็งตับอ่อน</t>
+  </si>
+  <si>
+    <t>C00</t>
+  </si>
+  <si>
+    <t>C50</t>
+  </si>
+  <si>
+    <t>C18</t>
+  </si>
+  <si>
+    <t>C82</t>
+  </si>
+  <si>
+    <t>C91</t>
+  </si>
+  <si>
+    <t>C92</t>
+  </si>
+  <si>
+    <t>C61</t>
+  </si>
+  <si>
+    <t>C22</t>
+  </si>
+  <si>
+    <t>C64</t>
+  </si>
+  <si>
+    <t>C34</t>
+  </si>
+  <si>
+    <t>C62</t>
+  </si>
+  <si>
+    <t>C25</t>
+  </si>
+  <si>
+    <t>Azathioprine</t>
+  </si>
+  <si>
+    <t>Prednisolone</t>
+  </si>
+  <si>
+    <t>Hydroxyurea</t>
+  </si>
+  <si>
+    <t>Erythropoietin</t>
+  </si>
+  <si>
+    <t>Ferrous sulfate</t>
+  </si>
+  <si>
+    <t>Folic acid</t>
+  </si>
+  <si>
+    <t>Vitamin B12</t>
+  </si>
+  <si>
+    <t>Deferoxamine</t>
+  </si>
+  <si>
+    <t>Desmopressin</t>
+  </si>
+  <si>
+    <t>Tranexamic acid</t>
+  </si>
+  <si>
+    <t>Warfarin</t>
+  </si>
+  <si>
+    <t>Heparin</t>
+  </si>
+  <si>
+    <t>Aspirin</t>
+  </si>
+  <si>
+    <t>Clopidogrel</t>
+  </si>
+  <si>
+    <t>Eltrombopag</t>
+  </si>
+  <si>
+    <t>Romiplostim</t>
+  </si>
+  <si>
+    <t>IVIG</t>
+  </si>
+  <si>
+    <t>Filgrastim</t>
+  </si>
+  <si>
+    <t>Pegfilgrastim</t>
+  </si>
+  <si>
+    <t>Mycophenolate mofetil</t>
+  </si>
+  <si>
+    <t>Tacrolimus</t>
+  </si>
+  <si>
+    <t>Cyclosporine</t>
+  </si>
+  <si>
+    <t>Hydroxychloroquine</t>
+  </si>
+  <si>
+    <t>Sulfasalazine</t>
+  </si>
+  <si>
+    <t>Allopurinol</t>
+  </si>
+  <si>
+    <t>Colchicine</t>
+  </si>
+  <si>
+    <t>Carcinoma in situ</t>
+  </si>
+  <si>
+    <t>Polycythemia vera</t>
+  </si>
+  <si>
+    <t>Myeloproliferative disorder</t>
+  </si>
+  <si>
+    <t>โลหิตจาง</t>
+  </si>
+  <si>
+    <t>โลหิตจางจากขาดธาตุเหล็ก</t>
+  </si>
+  <si>
+    <t>โลหิตจางจากขาด B12</t>
+  </si>
+  <si>
+    <t>ภาวะเหล็กเกิน</t>
+  </si>
+  <si>
+    <t>ฮีโมฟีเลีย</t>
+  </si>
+  <si>
+    <t>เลือดออกผิดปกติ</t>
+  </si>
+  <si>
+    <t>ลิ่มเลือดอุดตัน</t>
+  </si>
+  <si>
+    <t>เกล็ดเลือดเกาะตัว</t>
+  </si>
+  <si>
+    <t>เกล็ดเลือดต่ำ</t>
+  </si>
+  <si>
+    <t>โรคภูมิคุ้มกัน</t>
+  </si>
+  <si>
+    <t>ภูมิคุ้มกันบกพร่อง</t>
+  </si>
+  <si>
+    <t>เม็ดเลือดขาวต่ำ</t>
+  </si>
+  <si>
+    <t>ภูมิคุ้มกันผิดปกติ</t>
+  </si>
+  <si>
+    <t>SLE</t>
+  </si>
+  <si>
+    <t>ข้ออักเสบ</t>
+  </si>
+  <si>
+    <t>เก๊าท์</t>
+  </si>
+  <si>
+    <t>D00</t>
+  </si>
+  <si>
+    <t>D45</t>
+  </si>
+  <si>
+    <t>D47</t>
+  </si>
+  <si>
+    <t>D64</t>
+  </si>
+  <si>
+    <t>D50</t>
+  </si>
+  <si>
+    <t>D51</t>
+  </si>
+  <si>
+    <t>D75</t>
+  </si>
+  <si>
+    <t>D66</t>
+  </si>
+  <si>
+    <t>D69</t>
+  </si>
+  <si>
+    <t>D68</t>
+  </si>
+  <si>
+    <t>D89</t>
+  </si>
+  <si>
+    <t>D80</t>
+  </si>
+  <si>
+    <t>D70</t>
+  </si>
+  <si>
+    <t>Levofloxacin</t>
+  </si>
+  <si>
+    <t>Nitrofurantoin</t>
+  </si>
+  <si>
+    <t>Fosfomycin</t>
+  </si>
+  <si>
+    <t>Amoxicillin-clavulanate</t>
+  </si>
+  <si>
+    <t>Gentamicin</t>
+  </si>
+  <si>
+    <t>Tamsulosin</t>
+  </si>
+  <si>
+    <t>Finasteride</t>
+  </si>
+  <si>
+    <t>Dutasteride</t>
+  </si>
+  <si>
+    <t>Furosemide</t>
+  </si>
+  <si>
+    <t>Spironolactone</t>
+  </si>
+  <si>
+    <t>Hydrochlorothiazide</t>
+  </si>
+  <si>
+    <t>Calcium carbonate</t>
+  </si>
+  <si>
+    <t>Sevelamer</t>
+  </si>
+  <si>
+    <t>Sodium bicarbonate</t>
+  </si>
+  <si>
+    <t>Potassium citrate</t>
+  </si>
+  <si>
+    <t>Oxybutynin</t>
+  </si>
+  <si>
+    <t>Tolterodine</t>
+  </si>
+  <si>
+    <t>Mirabegron</t>
+  </si>
+  <si>
+    <t>Sildenafil</t>
+  </si>
+  <si>
+    <t>Tadalafil</t>
+  </si>
+  <si>
+    <t>Clomiphene</t>
+  </si>
+  <si>
+    <t>Medroxyprogesterone</t>
+  </si>
+  <si>
+    <t>Estradiol</t>
+  </si>
+  <si>
+    <t>Progesterone</t>
+  </si>
+  <si>
+    <t>ไตอักเสบเฉียบพลัน</t>
+  </si>
+  <si>
+    <t>ติดเชื้อทางเดินปัสสาวะ</t>
+  </si>
+  <si>
+    <t>กรวยไตอักเสบ</t>
+  </si>
+  <si>
+    <t>ต่อมลูกหมากโต</t>
+  </si>
+  <si>
+    <t>ไตวาย</t>
+  </si>
+  <si>
+    <t>ความดันจากไต</t>
+  </si>
+  <si>
+    <t>โลหิตจางจากไต</t>
+  </si>
+  <si>
+    <t>โรคไตเรื้อรัง</t>
+  </si>
+  <si>
+    <t>กรดเกินจากไต</t>
+  </si>
+  <si>
+    <t>นิ่วในไต</t>
+  </si>
+  <si>
+    <t>ปัสสาวะบ่อยกลางคืน</t>
+  </si>
+  <si>
+    <t>กระเพาะปัสสาวะไวเกิน</t>
+  </si>
+  <si>
+    <t>หย่อนสมรรถภาพ</t>
+  </si>
+  <si>
+    <t>มีบุตรยาก</t>
+  </si>
+  <si>
+    <t>ประจำเดือนผิดปกติ</t>
+  </si>
+  <si>
+    <t>ฮอร์โมนเพศต่ำ</t>
+  </si>
+  <si>
+    <t>N10</t>
+  </si>
+  <si>
+    <t>N39</t>
+  </si>
+  <si>
+    <t>N12</t>
+  </si>
+  <si>
+    <t>N17</t>
+  </si>
+  <si>
+    <t>N18</t>
+  </si>
+  <si>
+    <t>N25</t>
+  </si>
+  <si>
+    <t>N20</t>
+  </si>
+  <si>
+    <t>N32</t>
+  </si>
+  <si>
+    <t>N52</t>
+  </si>
+  <si>
+    <t>N46</t>
+  </si>
+  <si>
+    <t>N92</t>
+  </si>
+  <si>
+    <t>N95</t>
+  </si>
+  <si>
+    <t>Ibuprofen</t>
+  </si>
+  <si>
+    <t>Chlorpheniramine</t>
+  </si>
+  <si>
+    <t>Loratadine</t>
+  </si>
+  <si>
+    <t>Salbutamol</t>
+  </si>
+  <si>
+    <t>Budesonide</t>
+  </si>
+  <si>
+    <t>Formoterol</t>
+  </si>
+  <si>
+    <t>Montelukast</t>
+  </si>
+  <si>
+    <t>Amoxicillin</t>
+  </si>
+  <si>
+    <t>Dextromethorphan</t>
+  </si>
+  <si>
+    <t>Acetylcysteine</t>
+  </si>
+  <si>
+    <t>หวัด</t>
+  </si>
+  <si>
+    <t>ภูมิแพ้</t>
+  </si>
+  <si>
+    <t>หอบหืด</t>
+  </si>
+  <si>
+    <t>ติดเชื้อทางเดินหายใจ</t>
+  </si>
+  <si>
+    <t>ปอดอักเสบ</t>
+  </si>
+  <si>
+    <t>หอบกำเริบ</t>
+  </si>
+  <si>
+    <t>ไอ</t>
+  </si>
+  <si>
+    <t>เสมหะ</t>
+  </si>
+  <si>
+    <t>J30</t>
+  </si>
+  <si>
+    <t>J45</t>
+  </si>
+  <si>
+    <t>J06</t>
+  </si>
+  <si>
+    <t>J18</t>
+  </si>
+  <si>
+    <t>J46</t>
+  </si>
+  <si>
+    <t>R05</t>
+  </si>
+  <si>
+    <t>R09</t>
+  </si>
+  <si>
+    <t>Omeprazole</t>
+  </si>
+  <si>
+    <t>Esomeprazole</t>
+  </si>
+  <si>
+    <t>Pantoprazole</t>
+  </si>
+  <si>
+    <t>Ranitidine</t>
+  </si>
+  <si>
+    <t>Aluminium hydroxide</t>
+  </si>
+  <si>
+    <t>Magnesium hydroxide</t>
+  </si>
+  <si>
+    <t>Domperidone</t>
+  </si>
+  <si>
+    <t>Metoclopramide</t>
+  </si>
+  <si>
+    <t>Ondansetron</t>
+  </si>
+  <si>
+    <t>Simethicone</t>
+  </si>
+  <si>
+    <t>Loperamide</t>
+  </si>
+  <si>
+    <t>Clarithromycin</t>
+  </si>
+  <si>
+    <t>กรดไหลย้อน</t>
+  </si>
+  <si>
+    <t>แผลในกระเพาะ</t>
+  </si>
+  <si>
+    <t>แสบร้อนท้อง</t>
+  </si>
+  <si>
+    <t>อาเจียน</t>
+  </si>
+  <si>
+    <t>ท้องอืด</t>
+  </si>
+  <si>
+    <t>ท้องเสีย</t>
+  </si>
+  <si>
+    <t>ติดเชื้อในลำไส้</t>
+  </si>
+  <si>
+    <t>แผลกระเพาะ</t>
+  </si>
+  <si>
+    <t>K21</t>
+  </si>
+  <si>
+    <t>K25</t>
+  </si>
+  <si>
+    <t>R11</t>
+  </si>
+  <si>
+    <t>Hydrocortisone cream</t>
+  </si>
+  <si>
+    <t>Betamethasone</t>
+  </si>
+  <si>
+    <t>Clobetasol</t>
+  </si>
+  <si>
+    <t>Mupirocin</t>
+  </si>
+  <si>
+    <t>Fusidic acid</t>
+  </si>
+  <si>
+    <t>Acyclovir cream</t>
+  </si>
+  <si>
+    <t>Permethrin</t>
+  </si>
+  <si>
+    <t>Benzoyl peroxide</t>
+  </si>
+  <si>
+    <t>Isotretinoin</t>
+  </si>
+  <si>
+    <t>Adapalene</t>
+  </si>
+  <si>
+    <t>Cetirizine</t>
+  </si>
+  <si>
+    <t>ผื่นผิวหนัง</t>
+  </si>
+  <si>
+    <t>ผื่นแพ้</t>
+  </si>
+  <si>
+    <t>ผื่นอักเสบ</t>
+  </si>
+  <si>
+    <t>ติดเชื้อแบคทีเรีย</t>
+  </si>
+  <si>
+    <t>เริม</t>
+  </si>
+  <si>
+    <t>หิด</t>
+  </si>
+  <si>
+    <t>สิว</t>
+  </si>
+  <si>
+    <t>สิวรุนแรง</t>
+  </si>
+  <si>
+    <t>ลมพิษ</t>
+  </si>
+  <si>
+    <t>L20</t>
+  </si>
+  <si>
+    <t>L23</t>
+  </si>
+  <si>
+    <t>L30</t>
+  </si>
+  <si>
+    <t>L01</t>
+  </si>
+  <si>
+    <t>L70</t>
+  </si>
+  <si>
+    <t>L50</t>
   </si>
 </sst>
 </file>
@@ -1509,7 +2631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36EC5C3C-1E59-4742-8E49-52DA351D6E49}">
-  <dimension ref="A1:C427"/>
+  <dimension ref="A1:C670"/>
   <sheetFormatPr defaultColWidth="17.5" defaultRowHeight="22.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="27.25" customWidth="1"/>
@@ -5163,6 +6285,2679 @@
         <v>364</v>
       </c>
     </row>
+    <row r="428" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A428" t="s">
+        <v>365</v>
+      </c>
+      <c r="B428" t="s">
+        <v>366</v>
+      </c>
+      <c r="C428" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A429" t="s">
+        <v>368</v>
+      </c>
+      <c r="B429" t="s">
+        <v>366</v>
+      </c>
+      <c r="C429" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A430" t="s">
+        <v>369</v>
+      </c>
+      <c r="B430" t="s">
+        <v>366</v>
+      </c>
+      <c r="C430" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="431" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A431" t="s">
+        <v>370</v>
+      </c>
+      <c r="B431" t="s">
+        <v>371</v>
+      </c>
+      <c r="C431" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="432" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A432" t="s">
+        <v>373</v>
+      </c>
+      <c r="B432" t="s">
+        <v>371</v>
+      </c>
+      <c r="C432" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="433" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A433" t="s">
+        <v>369</v>
+      </c>
+      <c r="B433" t="s">
+        <v>371</v>
+      </c>
+      <c r="C433" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="434" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A434" t="s">
+        <v>374</v>
+      </c>
+      <c r="B434" t="s">
+        <v>443</v>
+      </c>
+      <c r="C434" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="435" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A435" t="s">
+        <v>370</v>
+      </c>
+      <c r="B435" t="s">
+        <v>443</v>
+      </c>
+      <c r="C435" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="436" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A436" t="s">
+        <v>373</v>
+      </c>
+      <c r="B436" t="s">
+        <v>443</v>
+      </c>
+      <c r="C436" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="437" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A437" t="s">
+        <v>374</v>
+      </c>
+      <c r="B437" t="s">
+        <v>377</v>
+      </c>
+      <c r="C437" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="438" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A438" t="s">
+        <v>370</v>
+      </c>
+      <c r="B438" t="s">
+        <v>377</v>
+      </c>
+      <c r="C438" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="439" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A439" t="s">
+        <v>369</v>
+      </c>
+      <c r="B439" t="s">
+        <v>377</v>
+      </c>
+      <c r="C439" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="440" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A440" t="s">
+        <v>374</v>
+      </c>
+      <c r="B440" t="s">
+        <v>444</v>
+      </c>
+      <c r="C440" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="441" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A441" t="s">
+        <v>370</v>
+      </c>
+      <c r="B441" t="s">
+        <v>444</v>
+      </c>
+      <c r="C441" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="442" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A442" t="s">
+        <v>365</v>
+      </c>
+      <c r="B442" t="s">
+        <v>445</v>
+      </c>
+      <c r="C442" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="443" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A443" t="s">
+        <v>379</v>
+      </c>
+      <c r="B443" t="s">
+        <v>381</v>
+      </c>
+      <c r="C443" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="444" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A444" t="s">
+        <v>374</v>
+      </c>
+      <c r="B444" t="s">
+        <v>381</v>
+      </c>
+      <c r="C444" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="445" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A445" t="s">
+        <v>365</v>
+      </c>
+      <c r="B445" t="s">
+        <v>382</v>
+      </c>
+      <c r="C445" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="446" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A446" t="s">
+        <v>384</v>
+      </c>
+      <c r="B446" t="s">
+        <v>382</v>
+      </c>
+      <c r="C446" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="447" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A447" t="s">
+        <v>370</v>
+      </c>
+      <c r="B447" t="s">
+        <v>382</v>
+      </c>
+      <c r="C447" t="s">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="448" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A448" t="s">
+        <v>374</v>
+      </c>
+      <c r="B448" t="s">
+        <v>385</v>
+      </c>
+      <c r="C448" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="449" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A449" t="s">
+        <v>387</v>
+      </c>
+      <c r="B449" t="s">
+        <v>385</v>
+      </c>
+      <c r="C449" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="450" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A450" t="s">
+        <v>388</v>
+      </c>
+      <c r="B450" t="s">
+        <v>385</v>
+      </c>
+      <c r="C450" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="451" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A451" t="s">
+        <v>374</v>
+      </c>
+      <c r="B451" t="s">
+        <v>446</v>
+      </c>
+      <c r="C451" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A452" t="s">
+        <v>390</v>
+      </c>
+      <c r="B452" t="s">
+        <v>446</v>
+      </c>
+      <c r="C452" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="453" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A453" t="s">
+        <v>365</v>
+      </c>
+      <c r="B453" t="s">
+        <v>391</v>
+      </c>
+      <c r="C453" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="454" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A454" t="s">
+        <v>393</v>
+      </c>
+      <c r="B454" t="s">
+        <v>391</v>
+      </c>
+      <c r="C454" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="455" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A455" t="s">
+        <v>365</v>
+      </c>
+      <c r="B455" t="s">
+        <v>394</v>
+      </c>
+      <c r="C455" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="456" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A456" t="s">
+        <v>398</v>
+      </c>
+      <c r="B456" t="s">
+        <v>399</v>
+      </c>
+      <c r="C456" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A457" t="s">
+        <v>400</v>
+      </c>
+      <c r="B457" t="s">
+        <v>399</v>
+      </c>
+      <c r="C457" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="458" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A458" t="s">
+        <v>401</v>
+      </c>
+      <c r="B458" t="s">
+        <v>399</v>
+      </c>
+      <c r="C458" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="459" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A459" t="s">
+        <v>402</v>
+      </c>
+      <c r="B459" t="s">
+        <v>399</v>
+      </c>
+      <c r="C459" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A460" t="s">
+        <v>403</v>
+      </c>
+      <c r="B460" t="s">
+        <v>404</v>
+      </c>
+      <c r="C460" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A461" t="s">
+        <v>400</v>
+      </c>
+      <c r="B461" t="s">
+        <v>404</v>
+      </c>
+      <c r="C461" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="462" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A462" t="s">
+        <v>406</v>
+      </c>
+      <c r="B462" t="s">
+        <v>404</v>
+      </c>
+      <c r="C462" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="463" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A463" t="s">
+        <v>407</v>
+      </c>
+      <c r="B463" t="s">
+        <v>408</v>
+      </c>
+      <c r="C463" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="464" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A464" t="s">
+        <v>409</v>
+      </c>
+      <c r="B464" t="s">
+        <v>408</v>
+      </c>
+      <c r="C464" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="465" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A465" t="s">
+        <v>368</v>
+      </c>
+      <c r="B465" t="s">
+        <v>408</v>
+      </c>
+      <c r="C465" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="466" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A466" t="s">
+        <v>373</v>
+      </c>
+      <c r="B466" t="s">
+        <v>410</v>
+      </c>
+      <c r="C466" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="467" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A467" t="s">
+        <v>369</v>
+      </c>
+      <c r="B467" t="s">
+        <v>410</v>
+      </c>
+      <c r="C467" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="468" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A468" t="s">
+        <v>368</v>
+      </c>
+      <c r="B468" t="s">
+        <v>412</v>
+      </c>
+      <c r="C468" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="469" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A469" t="s">
+        <v>369</v>
+      </c>
+      <c r="B469" t="s">
+        <v>412</v>
+      </c>
+      <c r="C469" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="470" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A470" t="s">
+        <v>374</v>
+      </c>
+      <c r="B470" t="s">
+        <v>413</v>
+      </c>
+      <c r="C470" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="471" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A471" t="s">
+        <v>387</v>
+      </c>
+      <c r="B471" t="s">
+        <v>413</v>
+      </c>
+      <c r="C471" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="472" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A472" t="s">
+        <v>415</v>
+      </c>
+      <c r="B472" t="s">
+        <v>447</v>
+      </c>
+      <c r="C472" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="473" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A473" t="s">
+        <v>418</v>
+      </c>
+      <c r="B473" t="s">
+        <v>447</v>
+      </c>
+      <c r="C473" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="474" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A474" t="s">
+        <v>421</v>
+      </c>
+      <c r="B474" t="s">
+        <v>422</v>
+      </c>
+      <c r="C474" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="475" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A475" t="s">
+        <v>424</v>
+      </c>
+      <c r="B475" t="s">
+        <v>422</v>
+      </c>
+      <c r="C475" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="476" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A476" t="s">
+        <v>425</v>
+      </c>
+      <c r="B476" t="s">
+        <v>422</v>
+      </c>
+      <c r="C476" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="477" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A477" t="s">
+        <v>426</v>
+      </c>
+      <c r="B477" t="s">
+        <v>422</v>
+      </c>
+      <c r="C477" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="478" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A478" t="s">
+        <v>427</v>
+      </c>
+      <c r="B478" t="s">
+        <v>431</v>
+      </c>
+      <c r="C478" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A479" t="s">
+        <v>430</v>
+      </c>
+      <c r="B479" t="s">
+        <v>431</v>
+      </c>
+      <c r="C479" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="480" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A480" t="s">
+        <v>432</v>
+      </c>
+      <c r="B480" t="s">
+        <v>431</v>
+      </c>
+      <c r="C480" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="481" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A481" t="s">
+        <v>434</v>
+      </c>
+      <c r="B481" t="s">
+        <v>435</v>
+      </c>
+      <c r="C481" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="482" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A482" t="s">
+        <v>436</v>
+      </c>
+      <c r="B482" t="s">
+        <v>437</v>
+      </c>
+      <c r="C482" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="483" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A483" t="s">
+        <v>438</v>
+      </c>
+      <c r="B483" t="s">
+        <v>437</v>
+      </c>
+      <c r="C483" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="484" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A484" t="s">
+        <v>439</v>
+      </c>
+      <c r="B484" t="s">
+        <v>437</v>
+      </c>
+      <c r="C484" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="485" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A485" t="s">
+        <v>440</v>
+      </c>
+      <c r="B485" t="s">
+        <v>441</v>
+      </c>
+      <c r="C485" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="486" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A486" t="s">
+        <v>415</v>
+      </c>
+      <c r="B486" t="s">
+        <v>416</v>
+      </c>
+      <c r="C486" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="487" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A487" t="s">
+        <v>418</v>
+      </c>
+      <c r="B487" t="s">
+        <v>416</v>
+      </c>
+      <c r="C487" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="488" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A488" t="s">
+        <v>451</v>
+      </c>
+      <c r="B488" t="s">
+        <v>416</v>
+      </c>
+      <c r="C488" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="489" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A489" t="s">
+        <v>452</v>
+      </c>
+      <c r="B489" t="s">
+        <v>472</v>
+      </c>
+      <c r="C489" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="490" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A490" t="s">
+        <v>453</v>
+      </c>
+      <c r="B490" t="s">
+        <v>472</v>
+      </c>
+      <c r="C490" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="491" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A491" t="s">
+        <v>419</v>
+      </c>
+      <c r="B491" t="s">
+        <v>420</v>
+      </c>
+      <c r="C491" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="492" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A492" t="s">
+        <v>454</v>
+      </c>
+      <c r="B492" t="s">
+        <v>420</v>
+      </c>
+      <c r="C492" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="493" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A493" t="s">
+        <v>455</v>
+      </c>
+      <c r="B493" t="s">
+        <v>473</v>
+      </c>
+      <c r="C493" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="494" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A494" t="s">
+        <v>456</v>
+      </c>
+      <c r="B494" t="s">
+        <v>474</v>
+      </c>
+      <c r="C494" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="495" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A495" t="s">
+        <v>421</v>
+      </c>
+      <c r="B495" t="s">
+        <v>422</v>
+      </c>
+      <c r="C495" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="496" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A496" t="s">
+        <v>424</v>
+      </c>
+      <c r="B496" t="s">
+        <v>422</v>
+      </c>
+      <c r="C496" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="497" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A497" t="s">
+        <v>425</v>
+      </c>
+      <c r="B497" t="s">
+        <v>422</v>
+      </c>
+      <c r="C497" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="498" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A498" t="s">
+        <v>426</v>
+      </c>
+      <c r="B498" t="s">
+        <v>422</v>
+      </c>
+      <c r="C498" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="499" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A499" t="s">
+        <v>457</v>
+      </c>
+      <c r="B499" t="s">
+        <v>422</v>
+      </c>
+      <c r="C499" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A500" t="s">
+        <v>427</v>
+      </c>
+      <c r="B500" t="s">
+        <v>428</v>
+      </c>
+      <c r="C500" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="501" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A501" t="s">
+        <v>458</v>
+      </c>
+      <c r="B501" t="s">
+        <v>431</v>
+      </c>
+      <c r="C501" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="502" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A502" t="s">
+        <v>459</v>
+      </c>
+      <c r="B502" t="s">
+        <v>431</v>
+      </c>
+      <c r="C502" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="503" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A503" t="s">
+        <v>430</v>
+      </c>
+      <c r="B503" t="s">
+        <v>475</v>
+      </c>
+      <c r="C503" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="504" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A504" t="s">
+        <v>432</v>
+      </c>
+      <c r="B504" t="s">
+        <v>475</v>
+      </c>
+      <c r="C504" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="505" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A505" t="s">
+        <v>434</v>
+      </c>
+      <c r="B505" t="s">
+        <v>435</v>
+      </c>
+      <c r="C505" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A506" t="s">
+        <v>460</v>
+      </c>
+      <c r="B506" t="s">
+        <v>428</v>
+      </c>
+      <c r="C506" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="507" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A507" t="s">
+        <v>461</v>
+      </c>
+      <c r="B507" t="s">
+        <v>475</v>
+      </c>
+      <c r="C507" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="508" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A508" t="s">
+        <v>436</v>
+      </c>
+      <c r="B508" t="s">
+        <v>437</v>
+      </c>
+      <c r="C508" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="509" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A509" t="s">
+        <v>438</v>
+      </c>
+      <c r="B509" t="s">
+        <v>437</v>
+      </c>
+      <c r="C509" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="510" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A510" t="s">
+        <v>439</v>
+      </c>
+      <c r="B510" t="s">
+        <v>437</v>
+      </c>
+      <c r="C510" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="511" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A511" t="s">
+        <v>440</v>
+      </c>
+      <c r="B511" t="s">
+        <v>441</v>
+      </c>
+      <c r="C511" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="512" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A512" t="s">
+        <v>462</v>
+      </c>
+      <c r="B512" t="s">
+        <v>476</v>
+      </c>
+      <c r="C512" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="513" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A513" t="s">
+        <v>463</v>
+      </c>
+      <c r="B513" t="s">
+        <v>477</v>
+      </c>
+      <c r="C513" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="514" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A514" t="s">
+        <v>374</v>
+      </c>
+      <c r="B514" t="s">
+        <v>446</v>
+      </c>
+      <c r="C514" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="515" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A515" t="s">
+        <v>387</v>
+      </c>
+      <c r="B515" t="s">
+        <v>446</v>
+      </c>
+      <c r="C515" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="516" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A516" t="s">
+        <v>390</v>
+      </c>
+      <c r="B516" t="s">
+        <v>446</v>
+      </c>
+      <c r="C516" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A517" t="s">
+        <v>464</v>
+      </c>
+      <c r="B517" t="s">
+        <v>478</v>
+      </c>
+      <c r="C517" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="518" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A518" t="s">
+        <v>465</v>
+      </c>
+      <c r="B518" t="s">
+        <v>478</v>
+      </c>
+      <c r="C518" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A519" t="s">
+        <v>403</v>
+      </c>
+      <c r="B519" t="s">
+        <v>479</v>
+      </c>
+      <c r="C519" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="520" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A520" t="s">
+        <v>466</v>
+      </c>
+      <c r="B520" t="s">
+        <v>479</v>
+      </c>
+      <c r="C520" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="521" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A521" t="s">
+        <v>467</v>
+      </c>
+      <c r="B521" t="s">
+        <v>446</v>
+      </c>
+      <c r="C521" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="522" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A522" t="s">
+        <v>468</v>
+      </c>
+      <c r="B522" t="s">
+        <v>480</v>
+      </c>
+      <c r="C522" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="523" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A523" t="s">
+        <v>469</v>
+      </c>
+      <c r="B523" t="s">
+        <v>480</v>
+      </c>
+      <c r="C523" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="524" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A524" t="s">
+        <v>470</v>
+      </c>
+      <c r="B524" t="s">
+        <v>480</v>
+      </c>
+      <c r="C524" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="525" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A525" t="s">
+        <v>471</v>
+      </c>
+      <c r="B525" t="s">
+        <v>480</v>
+      </c>
+      <c r="C525" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="526" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A526" t="s">
+        <v>490</v>
+      </c>
+      <c r="B526" t="s">
+        <v>530</v>
+      </c>
+      <c r="C526" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="527" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A527" t="s">
+        <v>491</v>
+      </c>
+      <c r="B527" t="s">
+        <v>530</v>
+      </c>
+      <c r="C527" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="528" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A528" t="s">
+        <v>492</v>
+      </c>
+      <c r="B528" t="s">
+        <v>531</v>
+      </c>
+      <c r="C528" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="529" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A529" t="s">
+        <v>493</v>
+      </c>
+      <c r="B529" t="s">
+        <v>531</v>
+      </c>
+      <c r="C529" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="530" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A530" t="s">
+        <v>494</v>
+      </c>
+      <c r="B530" t="s">
+        <v>532</v>
+      </c>
+      <c r="C530" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="531" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A531" t="s">
+        <v>495</v>
+      </c>
+      <c r="B531" t="s">
+        <v>532</v>
+      </c>
+      <c r="C531" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="532" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A532" t="s">
+        <v>496</v>
+      </c>
+      <c r="B532" t="s">
+        <v>531</v>
+      </c>
+      <c r="C532" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="533" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A533" t="s">
+        <v>497</v>
+      </c>
+      <c r="B533" t="s">
+        <v>531</v>
+      </c>
+      <c r="C533" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="534" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A534" t="s">
+        <v>498</v>
+      </c>
+      <c r="B534" t="s">
+        <v>533</v>
+      </c>
+      <c r="C534" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="535" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A535" t="s">
+        <v>499</v>
+      </c>
+      <c r="B535" t="s">
+        <v>534</v>
+      </c>
+      <c r="C535" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="536" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A536" t="s">
+        <v>500</v>
+      </c>
+      <c r="B536" t="s">
+        <v>535</v>
+      </c>
+      <c r="C536" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="537" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A537" t="s">
+        <v>501</v>
+      </c>
+      <c r="B537" t="s">
+        <v>531</v>
+      </c>
+      <c r="C537" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A538" t="s">
+        <v>502</v>
+      </c>
+      <c r="B538" t="s">
+        <v>531</v>
+      </c>
+      <c r="C538" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="539" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A539" t="s">
+        <v>503</v>
+      </c>
+      <c r="B539" t="s">
+        <v>531</v>
+      </c>
+      <c r="C539" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="540" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A540" t="s">
+        <v>504</v>
+      </c>
+      <c r="B540" t="s">
+        <v>531</v>
+      </c>
+      <c r="C540" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="541" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A541" t="s">
+        <v>505</v>
+      </c>
+      <c r="B541" t="s">
+        <v>536</v>
+      </c>
+      <c r="C541" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="542" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A542" t="s">
+        <v>506</v>
+      </c>
+      <c r="B542" t="s">
+        <v>536</v>
+      </c>
+      <c r="C542" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="543" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A543" t="s">
+        <v>507</v>
+      </c>
+      <c r="B543" t="s">
+        <v>536</v>
+      </c>
+      <c r="C543" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="544" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A544" t="s">
+        <v>508</v>
+      </c>
+      <c r="B544" t="s">
+        <v>533</v>
+      </c>
+      <c r="C544" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A545" t="s">
+        <v>509</v>
+      </c>
+      <c r="B545" t="s">
+        <v>537</v>
+      </c>
+      <c r="C545" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A546" t="s">
+        <v>510</v>
+      </c>
+      <c r="B546" t="s">
+        <v>538</v>
+      </c>
+      <c r="C546" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A547" t="s">
+        <v>511</v>
+      </c>
+      <c r="B547" t="s">
+        <v>539</v>
+      </c>
+      <c r="C547" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A548" t="s">
+        <v>512</v>
+      </c>
+      <c r="B548" t="s">
+        <v>540</v>
+      </c>
+      <c r="C548" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A549" t="s">
+        <v>513</v>
+      </c>
+      <c r="B549" t="s">
+        <v>534</v>
+      </c>
+      <c r="C549" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A550" t="s">
+        <v>514</v>
+      </c>
+      <c r="B550" t="s">
+        <v>533</v>
+      </c>
+      <c r="C550" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A551" t="s">
+        <v>515</v>
+      </c>
+      <c r="B551" t="s">
+        <v>541</v>
+      </c>
+      <c r="C551" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A552" t="s">
+        <v>516</v>
+      </c>
+      <c r="B552" t="s">
+        <v>542</v>
+      </c>
+      <c r="C552" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A553" t="s">
+        <v>517</v>
+      </c>
+      <c r="B553" t="s">
+        <v>537</v>
+      </c>
+      <c r="C553" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A554" t="s">
+        <v>518</v>
+      </c>
+      <c r="B554" t="s">
+        <v>537</v>
+      </c>
+      <c r="C554" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A555" t="s">
+        <v>519</v>
+      </c>
+      <c r="B555" t="s">
+        <v>540</v>
+      </c>
+      <c r="C555" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A556" t="s">
+        <v>520</v>
+      </c>
+      <c r="B556" t="s">
+        <v>540</v>
+      </c>
+      <c r="C556" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A557" t="s">
+        <v>521</v>
+      </c>
+      <c r="B557" t="s">
+        <v>540</v>
+      </c>
+      <c r="C557" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A558" t="s">
+        <v>522</v>
+      </c>
+      <c r="B558" t="s">
+        <v>540</v>
+      </c>
+      <c r="C558" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A559" t="s">
+        <v>523</v>
+      </c>
+      <c r="B559" t="s">
+        <v>537</v>
+      </c>
+      <c r="C559" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A560" t="s">
+        <v>524</v>
+      </c>
+      <c r="B560" t="s">
+        <v>537</v>
+      </c>
+      <c r="C560" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="561" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A561" t="s">
+        <v>525</v>
+      </c>
+      <c r="B561" t="s">
+        <v>531</v>
+      </c>
+      <c r="C561" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="562" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A562" t="s">
+        <v>526</v>
+      </c>
+      <c r="B562" t="s">
+        <v>539</v>
+      </c>
+      <c r="C562" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="563" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A563" t="s">
+        <v>527</v>
+      </c>
+      <c r="B563" t="s">
+        <v>539</v>
+      </c>
+      <c r="C563" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="564" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A564" t="s">
+        <v>528</v>
+      </c>
+      <c r="B564" t="s">
+        <v>534</v>
+      </c>
+      <c r="C564" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="565" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A565" t="s">
+        <v>529</v>
+      </c>
+      <c r="B565" t="s">
+        <v>534</v>
+      </c>
+      <c r="C565" t="s">
+        <v>548</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A566" t="s">
+        <v>499</v>
+      </c>
+      <c r="B566" t="s">
+        <v>581</v>
+      </c>
+      <c r="C566" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="567" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A567" t="s">
+        <v>555</v>
+      </c>
+      <c r="B567" t="s">
+        <v>581</v>
+      </c>
+      <c r="C567" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="568" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A568" t="s">
+        <v>498</v>
+      </c>
+      <c r="B568" t="s">
+        <v>581</v>
+      </c>
+      <c r="C568" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="569" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A569" t="s">
+        <v>556</v>
+      </c>
+      <c r="B569" t="s">
+        <v>581</v>
+      </c>
+      <c r="C569" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="570" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A570" t="s">
+        <v>557</v>
+      </c>
+      <c r="B570" t="s">
+        <v>582</v>
+      </c>
+      <c r="C570" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="571" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A571" t="s">
+        <v>500</v>
+      </c>
+      <c r="B571" t="s">
+        <v>583</v>
+      </c>
+      <c r="C571" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="572" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A572" t="s">
+        <v>558</v>
+      </c>
+      <c r="B572" t="s">
+        <v>584</v>
+      </c>
+      <c r="C572" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="573" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A573" t="s">
+        <v>559</v>
+      </c>
+      <c r="B573" t="s">
+        <v>585</v>
+      </c>
+      <c r="C573" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="574" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A574" t="s">
+        <v>560</v>
+      </c>
+      <c r="B574" t="s">
+        <v>584</v>
+      </c>
+      <c r="C574" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="575" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A575" t="s">
+        <v>561</v>
+      </c>
+      <c r="B575" t="s">
+        <v>586</v>
+      </c>
+      <c r="C575" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="576" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A576" t="s">
+        <v>562</v>
+      </c>
+      <c r="B576" t="s">
+        <v>587</v>
+      </c>
+      <c r="C576" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A577" t="s">
+        <v>563</v>
+      </c>
+      <c r="B577" t="s">
+        <v>588</v>
+      </c>
+      <c r="C577" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A578" t="s">
+        <v>564</v>
+      </c>
+      <c r="B578" t="s">
+        <v>589</v>
+      </c>
+      <c r="C578" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A579" t="s">
+        <v>565</v>
+      </c>
+      <c r="B579" t="s">
+        <v>590</v>
+      </c>
+      <c r="C579" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A580" t="s">
+        <v>566</v>
+      </c>
+      <c r="B580" t="s">
+        <v>590</v>
+      </c>
+      <c r="C580" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="581" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A581" t="s">
+        <v>567</v>
+      </c>
+      <c r="B581" t="s">
+        <v>591</v>
+      </c>
+      <c r="C581" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A582" t="s">
+        <v>568</v>
+      </c>
+      <c r="B582" t="s">
+        <v>591</v>
+      </c>
+      <c r="C582" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A583" t="s">
+        <v>569</v>
+      </c>
+      <c r="B583" t="s">
+        <v>592</v>
+      </c>
+      <c r="C583" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A584" t="s">
+        <v>570</v>
+      </c>
+      <c r="B584" t="s">
+        <v>592</v>
+      </c>
+      <c r="C584" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A585" t="s">
+        <v>508</v>
+      </c>
+      <c r="B585" t="s">
+        <v>593</v>
+      </c>
+      <c r="C585" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A586" t="s">
+        <v>571</v>
+      </c>
+      <c r="B586" t="s">
+        <v>594</v>
+      </c>
+      <c r="C586" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="587" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A587" t="s">
+        <v>572</v>
+      </c>
+      <c r="B587" t="s">
+        <v>595</v>
+      </c>
+      <c r="C587" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="588" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A588" t="s">
+        <v>573</v>
+      </c>
+      <c r="B588" t="s">
+        <v>595</v>
+      </c>
+      <c r="C588" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="589" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A589" t="s">
+        <v>574</v>
+      </c>
+      <c r="B589" t="s">
+        <v>596</v>
+      </c>
+      <c r="C589" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="590" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A590" t="s">
+        <v>575</v>
+      </c>
+      <c r="B590" t="s">
+        <v>596</v>
+      </c>
+      <c r="C590" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="591" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A591" t="s">
+        <v>576</v>
+      </c>
+      <c r="B591" t="s">
+        <v>596</v>
+      </c>
+      <c r="C591" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="592" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A592" t="s">
+        <v>577</v>
+      </c>
+      <c r="B592" t="s">
+        <v>597</v>
+      </c>
+      <c r="C592" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="593" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A593" t="s">
+        <v>578</v>
+      </c>
+      <c r="B593" t="s">
+        <v>598</v>
+      </c>
+      <c r="C593" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="594" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A594" t="s">
+        <v>579</v>
+      </c>
+      <c r="B594" t="s">
+        <v>599</v>
+      </c>
+      <c r="C594" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="595" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A595" t="s">
+        <v>580</v>
+      </c>
+      <c r="B595" t="s">
+        <v>599</v>
+      </c>
+      <c r="C595" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="596" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A596" t="s">
+        <v>370</v>
+      </c>
+      <c r="B596" t="s">
+        <v>637</v>
+      </c>
+      <c r="C596" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="597" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A597" t="s">
+        <v>613</v>
+      </c>
+      <c r="B597" t="s">
+        <v>637</v>
+      </c>
+      <c r="C597" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="598" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A598" t="s">
+        <v>614</v>
+      </c>
+      <c r="B598" t="s">
+        <v>638</v>
+      </c>
+      <c r="C598" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="599" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A599" t="s">
+        <v>615</v>
+      </c>
+      <c r="B599" t="s">
+        <v>638</v>
+      </c>
+      <c r="C599" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="600" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A600" t="s">
+        <v>616</v>
+      </c>
+      <c r="B600" t="s">
+        <v>638</v>
+      </c>
+      <c r="C600" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="601" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A601" t="s">
+        <v>373</v>
+      </c>
+      <c r="B601" t="s">
+        <v>639</v>
+      </c>
+      <c r="C601" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="602" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A602" t="s">
+        <v>617</v>
+      </c>
+      <c r="B602" t="s">
+        <v>639</v>
+      </c>
+      <c r="C602" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="603" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A603" t="s">
+        <v>618</v>
+      </c>
+      <c r="B603" t="s">
+        <v>640</v>
+      </c>
+      <c r="C603" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="604" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A604" t="s">
+        <v>619</v>
+      </c>
+      <c r="B604" t="s">
+        <v>640</v>
+      </c>
+      <c r="C604" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="605" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A605" t="s">
+        <v>620</v>
+      </c>
+      <c r="B605" t="s">
+        <v>640</v>
+      </c>
+      <c r="C605" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="606" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A606" t="s">
+        <v>621</v>
+      </c>
+      <c r="B606" t="s">
+        <v>641</v>
+      </c>
+      <c r="C606" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="607" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A607" t="s">
+        <v>622</v>
+      </c>
+      <c r="B607" t="s">
+        <v>641</v>
+      </c>
+      <c r="C607" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="608" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A608" t="s">
+        <v>623</v>
+      </c>
+      <c r="B608" t="s">
+        <v>642</v>
+      </c>
+      <c r="C608" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="609" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A609" t="s">
+        <v>558</v>
+      </c>
+      <c r="B609" t="s">
+        <v>643</v>
+      </c>
+      <c r="C609" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="610" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A610" t="s">
+        <v>624</v>
+      </c>
+      <c r="B610" t="s">
+        <v>644</v>
+      </c>
+      <c r="C610" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="611" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A611" t="s">
+        <v>625</v>
+      </c>
+      <c r="B611" t="s">
+        <v>644</v>
+      </c>
+      <c r="C611" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="612" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A612" t="s">
+        <v>626</v>
+      </c>
+      <c r="B612" t="s">
+        <v>645</v>
+      </c>
+      <c r="C612" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="613" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A613" t="s">
+        <v>579</v>
+      </c>
+      <c r="B613" t="s">
+        <v>646</v>
+      </c>
+      <c r="C613" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="614" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A614" t="s">
+        <v>627</v>
+      </c>
+      <c r="B614" t="s">
+        <v>646</v>
+      </c>
+      <c r="C614" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="615" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A615" t="s">
+        <v>563</v>
+      </c>
+      <c r="B615" t="s">
+        <v>647</v>
+      </c>
+      <c r="C615" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="616" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A616" t="s">
+        <v>628</v>
+      </c>
+      <c r="B616" t="s">
+        <v>648</v>
+      </c>
+      <c r="C616" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="617" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A617" t="s">
+        <v>629</v>
+      </c>
+      <c r="B617" t="s">
+        <v>648</v>
+      </c>
+      <c r="C617" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="618" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A618" t="s">
+        <v>630</v>
+      </c>
+      <c r="B618" t="s">
+        <v>648</v>
+      </c>
+      <c r="C618" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="619" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A619" t="s">
+        <v>631</v>
+      </c>
+      <c r="B619" t="s">
+        <v>649</v>
+      </c>
+      <c r="C619" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="620" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A620" t="s">
+        <v>632</v>
+      </c>
+      <c r="B620" t="s">
+        <v>649</v>
+      </c>
+      <c r="C620" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="621" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A621" t="s">
+        <v>633</v>
+      </c>
+      <c r="B621" t="s">
+        <v>650</v>
+      </c>
+      <c r="C621" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="622" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A622" t="s">
+        <v>503</v>
+      </c>
+      <c r="B622" t="s">
+        <v>650</v>
+      </c>
+      <c r="C622" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="623" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A623" t="s">
+        <v>634</v>
+      </c>
+      <c r="B623" t="s">
+        <v>651</v>
+      </c>
+      <c r="C623" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="624" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A624" t="s">
+        <v>635</v>
+      </c>
+      <c r="B624" t="s">
+        <v>652</v>
+      </c>
+      <c r="C624" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="625" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A625" t="s">
+        <v>636</v>
+      </c>
+      <c r="B625" t="s">
+        <v>652</v>
+      </c>
+      <c r="C625" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="626" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A626" t="s">
+        <v>396</v>
+      </c>
+      <c r="B626" t="s">
+        <v>675</v>
+      </c>
+      <c r="C626" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="627" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A627" t="s">
+        <v>665</v>
+      </c>
+      <c r="B627" t="s">
+        <v>675</v>
+      </c>
+      <c r="C627" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="628" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A628" t="s">
+        <v>666</v>
+      </c>
+      <c r="B628" t="s">
+        <v>676</v>
+      </c>
+      <c r="C628" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="629" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A629" t="s">
+        <v>667</v>
+      </c>
+      <c r="B629" t="s">
+        <v>676</v>
+      </c>
+      <c r="C629" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="630" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A630" t="s">
+        <v>668</v>
+      </c>
+      <c r="B630" t="s">
+        <v>677</v>
+      </c>
+      <c r="C630" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="631" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A631" t="s">
+        <v>669</v>
+      </c>
+      <c r="B631" t="s">
+        <v>677</v>
+      </c>
+      <c r="C631" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="632" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A632" t="s">
+        <v>670</v>
+      </c>
+      <c r="B632" t="s">
+        <v>677</v>
+      </c>
+      <c r="C632" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="633" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A633" t="s">
+        <v>671</v>
+      </c>
+      <c r="B633" t="s">
+        <v>677</v>
+      </c>
+      <c r="C633" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="634" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A634" t="s">
+        <v>672</v>
+      </c>
+      <c r="B634" t="s">
+        <v>678</v>
+      </c>
+      <c r="C634" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="635" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A635" t="s">
+        <v>369</v>
+      </c>
+      <c r="B635" t="s">
+        <v>678</v>
+      </c>
+      <c r="C635" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="636" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A636" t="s">
+        <v>613</v>
+      </c>
+      <c r="B636" t="s">
+        <v>679</v>
+      </c>
+      <c r="C636" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="637" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A637" t="s">
+        <v>373</v>
+      </c>
+      <c r="B637" t="s">
+        <v>679</v>
+      </c>
+      <c r="C637" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="638" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A638" t="s">
+        <v>556</v>
+      </c>
+      <c r="B638" t="s">
+        <v>680</v>
+      </c>
+      <c r="C638" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="639" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A639" t="s">
+        <v>673</v>
+      </c>
+      <c r="B639" t="s">
+        <v>681</v>
+      </c>
+      <c r="C639" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="640" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A640" t="s">
+        <v>674</v>
+      </c>
+      <c r="B640" t="s">
+        <v>682</v>
+      </c>
+      <c r="C640" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="641" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A641" t="s">
+        <v>690</v>
+      </c>
+      <c r="B641" t="s">
+        <v>702</v>
+      </c>
+      <c r="C641" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="642" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A642" t="s">
+        <v>691</v>
+      </c>
+      <c r="B642" t="s">
+        <v>702</v>
+      </c>
+      <c r="C642" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="643" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A643" t="s">
+        <v>692</v>
+      </c>
+      <c r="B643" t="s">
+        <v>702</v>
+      </c>
+      <c r="C643" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="644" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A644" t="s">
+        <v>693</v>
+      </c>
+      <c r="B644" t="s">
+        <v>703</v>
+      </c>
+      <c r="C644" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="645" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A645" t="s">
+        <v>694</v>
+      </c>
+      <c r="B645" t="s">
+        <v>704</v>
+      </c>
+      <c r="C645" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="646" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A646" t="s">
+        <v>695</v>
+      </c>
+      <c r="B646" t="s">
+        <v>704</v>
+      </c>
+      <c r="C646" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="647" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A647" t="s">
+        <v>696</v>
+      </c>
+      <c r="B647" t="s">
+        <v>227</v>
+      </c>
+      <c r="C647" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="648" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A648" t="s">
+        <v>697</v>
+      </c>
+      <c r="B648" t="s">
+        <v>227</v>
+      </c>
+      <c r="C648" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="649" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A649" t="s">
+        <v>698</v>
+      </c>
+      <c r="B649" t="s">
+        <v>705</v>
+      </c>
+      <c r="C649" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="650" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A650" t="s">
+        <v>699</v>
+      </c>
+      <c r="B650" t="s">
+        <v>706</v>
+      </c>
+      <c r="C650" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="651" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A651" t="s">
+        <v>700</v>
+      </c>
+      <c r="B651" t="s">
+        <v>707</v>
+      </c>
+      <c r="C651" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="652" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A652" t="s">
+        <v>365</v>
+      </c>
+      <c r="B652" t="s">
+        <v>707</v>
+      </c>
+      <c r="C652" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="653" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A653" t="s">
+        <v>374</v>
+      </c>
+      <c r="B653" t="s">
+        <v>708</v>
+      </c>
+      <c r="C653" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="654" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A654" t="s">
+        <v>672</v>
+      </c>
+      <c r="B654" t="s">
+        <v>709</v>
+      </c>
+      <c r="C654" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="655" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A655" t="s">
+        <v>701</v>
+      </c>
+      <c r="B655" t="s">
+        <v>709</v>
+      </c>
+      <c r="C655" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="656" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A656" t="s">
+        <v>713</v>
+      </c>
+      <c r="B656" t="s">
+        <v>724</v>
+      </c>
+      <c r="C656" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="657" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A657" t="s">
+        <v>714</v>
+      </c>
+      <c r="B657" t="s">
+        <v>725</v>
+      </c>
+      <c r="C657" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="658" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A658" t="s">
+        <v>715</v>
+      </c>
+      <c r="B658" t="s">
+        <v>726</v>
+      </c>
+      <c r="C658" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="659" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A659" t="s">
+        <v>716</v>
+      </c>
+      <c r="B659" t="s">
+        <v>727</v>
+      </c>
+      <c r="C659" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="660" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A660" t="s">
+        <v>717</v>
+      </c>
+      <c r="B660" t="s">
+        <v>727</v>
+      </c>
+      <c r="C660" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="661" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A661" t="s">
+        <v>430</v>
+      </c>
+      <c r="B661" t="s">
+        <v>431</v>
+      </c>
+      <c r="C661" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="662" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A662" t="s">
+        <v>459</v>
+      </c>
+      <c r="B662" t="s">
+        <v>431</v>
+      </c>
+      <c r="C662" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="663" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A663" t="s">
+        <v>432</v>
+      </c>
+      <c r="B663" t="s">
+        <v>431</v>
+      </c>
+      <c r="C663" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="664" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A664" t="s">
+        <v>718</v>
+      </c>
+      <c r="B664" t="s">
+        <v>728</v>
+      </c>
+      <c r="C664" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="665" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A665" t="s">
+        <v>719</v>
+      </c>
+      <c r="B665" t="s">
+        <v>729</v>
+      </c>
+      <c r="C665" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="666" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A666" t="s">
+        <v>720</v>
+      </c>
+      <c r="B666" t="s">
+        <v>730</v>
+      </c>
+      <c r="C666" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="667" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A667" t="s">
+        <v>721</v>
+      </c>
+      <c r="B667" t="s">
+        <v>731</v>
+      </c>
+      <c r="C667" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="668" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A668" t="s">
+        <v>722</v>
+      </c>
+      <c r="B668" t="s">
+        <v>730</v>
+      </c>
+      <c r="C668" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="669" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A669" t="s">
+        <v>723</v>
+      </c>
+      <c r="B669" t="s">
+        <v>732</v>
+      </c>
+      <c r="C669" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="670" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A670" t="s">
+        <v>667</v>
+      </c>
+      <c r="B670" t="s">
+        <v>732</v>
+      </c>
+      <c r="C670" t="s">
+        <v>738</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/DRUG DISEASE.xlsx
+++ b/DRUG DISEASE.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT Room\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E3093246-44F4-4B8C-ABD6-625F8D07DC0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDDA733B-D326-492B-A504-31FEF71C3DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="12210" windowHeight="12885" xr2:uid="{3244C3E9-4DF0-4247-BD4E-75BB2D6BE0CE}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{3244C3E9-4DF0-4247-BD4E-75BB2D6BE0CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="739">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1912" uniqueCount="853">
   <si>
     <t>ชื่อยา</t>
   </si>
@@ -2260,6 +2261,348 @@
   </si>
   <si>
     <t>L50</t>
+  </si>
+  <si>
+    <t>ICD-10</t>
+  </si>
+  <si>
+    <t>ชื่อโรค</t>
+  </si>
+  <si>
+    <t>สรรพคุณยา</t>
+  </si>
+  <si>
+    <t>E11</t>
+  </si>
+  <si>
+    <t>เบาหวาน</t>
+  </si>
+  <si>
+    <t>Metformin</t>
+  </si>
+  <si>
+    <t>ลดการสร้างน้ำตาลจากตับ</t>
+  </si>
+  <si>
+    <t>Insulin</t>
+  </si>
+  <si>
+    <t>ลดน้ำตาลในเลือด</t>
+  </si>
+  <si>
+    <t>Glimepiride</t>
+  </si>
+  <si>
+    <t>กระตุ้นอินซูลิน</t>
+  </si>
+  <si>
+    <t>Gliclazide</t>
+  </si>
+  <si>
+    <t>Empagliflozin</t>
+  </si>
+  <si>
+    <t>ขับน้ำตาลออกทางปัสสาวะ</t>
+  </si>
+  <si>
+    <t>Dapagliflozin</t>
+  </si>
+  <si>
+    <t>ขับน้ำตาล</t>
+  </si>
+  <si>
+    <t>Sitagliptin</t>
+  </si>
+  <si>
+    <t>เพิ่ม incretin</t>
+  </si>
+  <si>
+    <t>Linagliptin</t>
+  </si>
+  <si>
+    <t>ควบคุมน้ำตาล</t>
+  </si>
+  <si>
+    <t>Pioglitazone</t>
+  </si>
+  <si>
+    <t>เพิ่มความไวอินซูลิน</t>
+  </si>
+  <si>
+    <t>ความดันโลหิตสูง</t>
+  </si>
+  <si>
+    <t>Amlodipine</t>
+  </si>
+  <si>
+    <t>ขยายหลอดเลือด</t>
+  </si>
+  <si>
+    <t>Losartan</t>
+  </si>
+  <si>
+    <t>ARB ลดความดัน</t>
+  </si>
+  <si>
+    <t>Enalapril</t>
+  </si>
+  <si>
+    <t>ACE inhibitor</t>
+  </si>
+  <si>
+    <t>Lisinopril</t>
+  </si>
+  <si>
+    <t>ลดความดัน</t>
+  </si>
+  <si>
+    <t>Atenolol</t>
+  </si>
+  <si>
+    <t>ลดชีพจร</t>
+  </si>
+  <si>
+    <t>Bisoprolol</t>
+  </si>
+  <si>
+    <t>ลดภาระหัวใจ</t>
+  </si>
+  <si>
+    <t>ขับปัสสาวะ</t>
+  </si>
+  <si>
+    <t>Valsartan</t>
+  </si>
+  <si>
+    <t>Telmisartan</t>
+  </si>
+  <si>
+    <t>ARB</t>
+  </si>
+  <si>
+    <t>I50</t>
+  </si>
+  <si>
+    <t>หัวใจล้มเหลว</t>
+  </si>
+  <si>
+    <t>ขับน้ำ</t>
+  </si>
+  <si>
+    <t>ลดน้ำคั่ง</t>
+  </si>
+  <si>
+    <t>Digoxin</t>
+  </si>
+  <si>
+    <t>เพิ่มแรงบีบหัวใจ</t>
+  </si>
+  <si>
+    <t>Carvedilol</t>
+  </si>
+  <si>
+    <t>Metoprolol</t>
+  </si>
+  <si>
+    <t>ลด afterload</t>
+  </si>
+  <si>
+    <t>I63</t>
+  </si>
+  <si>
+    <t>Stroke</t>
+  </si>
+  <si>
+    <t>ต้านเกล็ดเลือด</t>
+  </si>
+  <si>
+    <t>ป้องกันลิ่มเลือด</t>
+  </si>
+  <si>
+    <t>ต้านการแข็งตัว</t>
+  </si>
+  <si>
+    <t>Rivaroxaban</t>
+  </si>
+  <si>
+    <t>ยาต้านลิ่มเลือด</t>
+  </si>
+  <si>
+    <t>Apixaban</t>
+  </si>
+  <si>
+    <t>ต้านลิ่มเลือด</t>
+  </si>
+  <si>
+    <t>J44</t>
+  </si>
+  <si>
+    <t>COPD</t>
+  </si>
+  <si>
+    <t>ขยายหลอดลม</t>
+  </si>
+  <si>
+    <t>Tiotropium</t>
+  </si>
+  <si>
+    <t>ขยายหลอดลมยาว</t>
+  </si>
+  <si>
+    <t>Salmeterol</t>
+  </si>
+  <si>
+    <t>Theophylline</t>
+  </si>
+  <si>
+    <t>คลายหลอดลม</t>
+  </si>
+  <si>
+    <t>ไตวายเรื้อรัง</t>
+  </si>
+  <si>
+    <t>กระตุ้นเม็ดเลือด</t>
+  </si>
+  <si>
+    <t>จับฟอสเฟต</t>
+  </si>
+  <si>
+    <t>Calcitriol</t>
+  </si>
+  <si>
+    <t>วิตามิน D</t>
+  </si>
+  <si>
+    <t>แก้กรด</t>
+  </si>
+  <si>
+    <t>เสริมธาตุเหล็ก</t>
+  </si>
+  <si>
+    <t>E78</t>
+  </si>
+  <si>
+    <t>ไขมันในเลือดสูง</t>
+  </si>
+  <si>
+    <t>Atorvastatin</t>
+  </si>
+  <si>
+    <t>ลด LDL</t>
+  </si>
+  <si>
+    <t>Simvastatin</t>
+  </si>
+  <si>
+    <t>ลดไขมัน</t>
+  </si>
+  <si>
+    <t>Rosuvastatin</t>
+  </si>
+  <si>
+    <t>Fenofibrate</t>
+  </si>
+  <si>
+    <t>ลด triglyceride</t>
+  </si>
+  <si>
+    <t>Gemfibrozil</t>
+  </si>
+  <si>
+    <t>G20</t>
+  </si>
+  <si>
+    <t>พาร์กินสัน</t>
+  </si>
+  <si>
+    <t>Levodopa</t>
+  </si>
+  <si>
+    <t>เพิ่ม dopamine</t>
+  </si>
+  <si>
+    <t>Carbidopa</t>
+  </si>
+  <si>
+    <t>เสริม levodopa</t>
+  </si>
+  <si>
+    <t>Pramipexole</t>
+  </si>
+  <si>
+    <t>dopamine agonist</t>
+  </si>
+  <si>
+    <t>Ropinirole</t>
+  </si>
+  <si>
+    <t>Selegiline</t>
+  </si>
+  <si>
+    <t>MAO-B inhibitor</t>
+  </si>
+  <si>
+    <t>G30</t>
+  </si>
+  <si>
+    <t>สมองเสื่อม</t>
+  </si>
+  <si>
+    <t>Donepezil</t>
+  </si>
+  <si>
+    <t>เพิ่ม acetylcholine</t>
+  </si>
+  <si>
+    <t>Rivastigmine</t>
+  </si>
+  <si>
+    <t>Memantine</t>
+  </si>
+  <si>
+    <t>ป้องกันเซลล์สมอง</t>
+  </si>
+  <si>
+    <t>HIV/AIDS</t>
+  </si>
+  <si>
+    <t>ต้านไวรัส</t>
+  </si>
+  <si>
+    <t>NNRTI</t>
+  </si>
+  <si>
+    <t>NRTI</t>
+  </si>
+  <si>
+    <t>Integrase inhibitor</t>
+  </si>
+  <si>
+    <t>Ritonavir</t>
+  </si>
+  <si>
+    <t>boost protease inhibitor</t>
+  </si>
+  <si>
+    <t>C80</t>
+  </si>
+  <si>
+    <t>มะเร็ง</t>
+  </si>
+  <si>
+    <t>ยับยั้งเซลล์</t>
+  </si>
+  <si>
+    <t>ทำลาย DNA</t>
+  </si>
+  <si>
+    <t>หยุด cell division</t>
+  </si>
+  <si>
+    <t>targeted therapy</t>
+  </si>
+  <si>
+    <t>alkylating agent</t>
   </si>
 </sst>
 </file>
@@ -2632,13 +2975,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36EC5C3C-1E59-4742-8E49-52DA351D6E49}">
   <dimension ref="A1:C670"/>
-  <sheetFormatPr defaultColWidth="17.5" defaultRowHeight="22.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="17.5" defaultRowHeight="22.8" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="1" width="27.25" customWidth="1"/>
-    <col min="2" max="2" width="40.25" customWidth="1"/>
+    <col min="1" max="1" width="27.19921875" customWidth="1"/>
+    <col min="2" max="2" width="40.19921875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2649,7 +2992,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A2" s="1" t="s">
         <v>3</v>
       </c>
@@ -2657,7 +3000,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
@@ -2665,7 +3008,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -2673,7 +3016,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -2681,7 +3024,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -2689,7 +3032,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A7" s="1" t="s">
         <v>10</v>
       </c>
@@ -2697,7 +3040,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A8" s="1" t="s">
         <v>12</v>
       </c>
@@ -2705,7 +3048,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
@@ -2713,7 +3056,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
@@ -2721,7 +3064,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A11" s="1" t="s">
         <v>17</v>
       </c>
@@ -2729,7 +3072,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
@@ -2737,7 +3080,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="1" t="s">
         <v>20</v>
       </c>
@@ -2745,7 +3088,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="1" t="s">
         <v>21</v>
       </c>
@@ -2753,7 +3096,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1" t="s">
         <v>22</v>
       </c>
@@ -2761,7 +3104,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
@@ -2769,7 +3112,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="1" t="s">
         <v>25</v>
       </c>
@@ -2777,7 +3120,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="1" t="s">
         <v>23</v>
       </c>
@@ -2785,7 +3128,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="1" t="s">
         <v>17</v>
       </c>
@@ -2793,7 +3136,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="1" t="s">
         <v>26</v>
       </c>
@@ -2801,7 +3144,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="1" t="s">
         <v>28</v>
       </c>
@@ -2809,7 +3152,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="1" t="s">
         <v>29</v>
       </c>
@@ -2817,7 +3160,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="1" t="s">
         <v>30</v>
       </c>
@@ -2825,7 +3168,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="1" t="s">
         <v>31</v>
       </c>
@@ -2833,7 +3176,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="1" t="s">
         <v>32</v>
       </c>
@@ -2841,7 +3184,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="1" t="s">
         <v>33</v>
       </c>
@@ -2849,7 +3192,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="1" t="s">
         <v>25</v>
       </c>
@@ -2857,7 +3200,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="1" t="s">
         <v>20</v>
       </c>
@@ -2865,7 +3208,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="1" t="s">
         <v>36</v>
       </c>
@@ -2873,7 +3216,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="1" t="s">
         <v>37</v>
       </c>
@@ -2881,7 +3224,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="1" t="s">
         <v>39</v>
       </c>
@@ -2889,7 +3232,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="1" t="s">
         <v>41</v>
       </c>
@@ -2897,7 +3240,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="1" t="s">
         <v>42</v>
       </c>
@@ -2905,7 +3248,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A34" s="1" t="s">
         <v>44</v>
       </c>
@@ -2913,7 +3256,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A35" s="1" t="s">
         <v>42</v>
       </c>
@@ -2921,7 +3264,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A36" s="1" t="s">
         <v>46</v>
       </c>
@@ -2929,7 +3272,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A37" s="1" t="s">
         <v>47</v>
       </c>
@@ -2937,7 +3280,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A38" s="1" t="s">
         <v>48</v>
       </c>
@@ -2945,7 +3288,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A39" s="1" t="s">
         <v>20</v>
       </c>
@@ -2953,7 +3296,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A40" s="1" t="s">
         <v>44</v>
       </c>
@@ -2961,7 +3304,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A41" s="1" t="s">
         <v>42</v>
       </c>
@@ -2969,7 +3312,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A42" s="1" t="s">
         <v>50</v>
       </c>
@@ -2977,7 +3320,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A43" s="1" t="s">
         <v>33</v>
       </c>
@@ -2985,7 +3328,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A44" s="1" t="s">
         <v>25</v>
       </c>
@@ -2993,7 +3336,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A45" s="1" t="s">
         <v>20</v>
       </c>
@@ -3001,7 +3344,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A46" s="1" t="s">
         <v>7</v>
       </c>
@@ -3009,7 +3352,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A47" s="1" t="s">
         <v>37</v>
       </c>
@@ -3017,7 +3360,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A48" s="1" t="s">
         <v>36</v>
       </c>
@@ -3025,7 +3368,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A49" s="1" t="s">
         <v>53</v>
       </c>
@@ -3033,7 +3376,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A50" s="1" t="s">
         <v>33</v>
       </c>
@@ -3041,7 +3384,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A51" s="1" t="s">
         <v>20</v>
       </c>
@@ -3049,7 +3392,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A52" s="1" t="s">
         <v>54</v>
       </c>
@@ -3057,7 +3400,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A53" s="1" t="s">
         <v>56</v>
       </c>
@@ -3065,7 +3408,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A54" s="1" t="s">
         <v>57</v>
       </c>
@@ -3073,7 +3416,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A55" s="1" t="s">
         <v>58</v>
       </c>
@@ -3081,7 +3424,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A56" s="1" t="s">
         <v>59</v>
       </c>
@@ -3089,7 +3432,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A57" s="1" t="s">
         <v>60</v>
       </c>
@@ -3097,7 +3440,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A58" s="1" t="s">
         <v>41</v>
       </c>
@@ -3105,7 +3448,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A59" s="1" t="s">
         <v>42</v>
       </c>
@@ -3113,7 +3456,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A60" s="1" t="s">
         <v>36</v>
       </c>
@@ -3121,7 +3464,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A61" s="1" t="s">
         <v>62</v>
       </c>
@@ -3129,7 +3472,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="1" t="s">
         <v>60</v>
       </c>
@@ -3137,7 +3480,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A63" s="1" t="s">
         <v>64</v>
       </c>
@@ -3145,7 +3488,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A64" s="1" t="s">
         <v>65</v>
       </c>
@@ -3153,7 +3496,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A65" s="1" t="s">
         <v>60</v>
       </c>
@@ -3161,7 +3504,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A66" s="1" t="s">
         <v>70</v>
       </c>
@@ -3169,7 +3512,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A67" s="1" t="s">
         <v>69</v>
       </c>
@@ -3177,7 +3520,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" s="1" t="s">
         <v>36</v>
       </c>
@@ -3185,7 +3528,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" s="1" t="s">
         <v>62</v>
       </c>
@@ -3193,7 +3536,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" s="1" t="s">
         <v>72</v>
       </c>
@@ -3201,7 +3544,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="1" t="s">
         <v>74</v>
       </c>
@@ -3209,7 +3552,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" s="1" t="s">
         <v>54</v>
       </c>
@@ -3217,7 +3560,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" s="1" t="s">
         <v>8</v>
       </c>
@@ -3225,7 +3568,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" s="1" t="s">
         <v>78</v>
       </c>
@@ -3233,7 +3576,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" s="1" t="s">
         <v>80</v>
       </c>
@@ -3241,7 +3584,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="112.5" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:3" ht="114" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" s="2" t="s">
         <v>82</v>
       </c>
@@ -3249,7 +3592,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="112.5" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:3" ht="114" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" s="2" t="s">
         <v>83</v>
       </c>
@@ -3257,7 +3600,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" s="1" t="s">
         <v>48</v>
       </c>
@@ -3265,7 +3608,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" s="1" t="s">
         <v>85</v>
       </c>
@@ -3273,7 +3616,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" s="1" t="s">
         <v>32</v>
       </c>
@@ -3281,7 +3624,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" s="1" t="s">
         <v>29</v>
       </c>
@@ -3289,7 +3632,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" s="1" t="s">
         <v>48</v>
       </c>
@@ -3297,7 +3640,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" s="1" t="s">
         <v>23</v>
       </c>
@@ -3305,7 +3648,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" s="1" t="s">
         <v>86</v>
       </c>
@@ -3313,7 +3656,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" s="1" t="s">
         <v>88</v>
       </c>
@@ -3321,7 +3664,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" s="1" t="s">
         <v>54</v>
       </c>
@@ -3329,7 +3672,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" s="1" t="s">
         <v>105</v>
       </c>
@@ -3337,7 +3680,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" s="1" t="s">
         <v>89</v>
       </c>
@@ -3345,7 +3688,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" s="1" t="s">
         <v>91</v>
       </c>
@@ -3353,7 +3696,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" s="1" t="s">
         <v>65</v>
       </c>
@@ -3361,7 +3704,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" s="1" t="s">
         <v>93</v>
       </c>
@@ -3369,7 +3712,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" s="1" t="s">
         <v>94</v>
       </c>
@@ -3377,7 +3720,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" s="1" t="s">
         <v>46</v>
       </c>
@@ -3385,7 +3728,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" s="1" t="s">
         <v>36</v>
       </c>
@@ -3393,7 +3736,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" s="1" t="s">
         <v>54</v>
       </c>
@@ -3401,7 +3744,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" s="1" t="s">
         <v>30</v>
       </c>
@@ -3409,7 +3752,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" s="1" t="s">
         <v>17</v>
       </c>
@@ -3417,7 +3760,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" s="1" t="s">
         <v>100</v>
       </c>
@@ -3425,7 +3768,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" s="1" t="s">
         <v>94</v>
       </c>
@@ -3433,7 +3776,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" s="1" t="s">
         <v>101</v>
       </c>
@@ -3441,7 +3784,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" s="1" t="s">
         <v>3</v>
       </c>
@@ -3449,7 +3792,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" s="1" t="s">
         <v>103</v>
       </c>
@@ -3457,7 +3800,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" s="1" t="s">
         <v>106</v>
       </c>
@@ -3465,7 +3808,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" s="1" t="s">
         <v>108</v>
       </c>
@@ -3473,7 +3816,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" s="1" t="s">
         <v>109</v>
       </c>
@@ -3481,7 +3824,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" s="1" t="s">
         <v>110</v>
       </c>
@@ -3489,7 +3832,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" s="1" t="s">
         <v>94</v>
       </c>
@@ -3497,7 +3840,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" s="1" t="s">
         <v>41</v>
       </c>
@@ -3505,7 +3848,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" s="1" t="s">
         <v>42</v>
       </c>
@@ -3513,7 +3856,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" s="1" t="s">
         <v>101</v>
       </c>
@@ -3521,7 +3864,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" s="1" t="s">
         <v>33</v>
       </c>
@@ -3529,7 +3872,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" s="1" t="s">
         <v>48</v>
       </c>
@@ -3537,7 +3880,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" s="1" t="s">
         <v>20</v>
       </c>
@@ -3545,7 +3888,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" s="1" t="s">
         <v>8</v>
       </c>
@@ -3553,7 +3896,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" s="1" t="s">
         <v>65</v>
       </c>
@@ -3561,7 +3904,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" s="1" t="s">
         <v>113</v>
       </c>
@@ -3569,7 +3912,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" s="1" t="s">
         <v>37</v>
       </c>
@@ -3577,7 +3920,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" s="1" t="s">
         <v>36</v>
       </c>
@@ -3585,7 +3928,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" s="1" t="s">
         <v>116</v>
       </c>
@@ -3593,7 +3936,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" s="1" t="s">
         <v>116</v>
       </c>
@@ -3601,7 +3944,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" s="1" t="s">
         <v>44</v>
       </c>
@@ -3609,7 +3952,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" s="1" t="s">
         <v>118</v>
       </c>
@@ -3617,7 +3960,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" s="1" t="s">
         <v>42</v>
       </c>
@@ -3625,7 +3968,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" s="1" t="s">
         <v>120</v>
       </c>
@@ -3633,7 +3976,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" s="1" t="s">
         <v>121</v>
       </c>
@@ -3641,7 +3984,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" s="1" t="s">
         <v>46</v>
       </c>
@@ -3649,7 +3992,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" s="1" t="s">
         <v>122</v>
       </c>
@@ -3657,7 +4000,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" s="1" t="s">
         <v>20</v>
       </c>
@@ -3665,7 +4008,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" s="2" t="s">
         <v>126</v>
       </c>
@@ -3673,7 +4016,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="130" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" t="s">
         <v>125</v>
       </c>
@@ -3681,7 +4024,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="131" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" s="1" t="s">
         <v>127</v>
       </c>
@@ -3689,7 +4032,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="132" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" s="1" t="s">
         <v>129</v>
       </c>
@@ -3697,7 +4040,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="133" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" s="1" t="s">
         <v>37</v>
       </c>
@@ -3705,7 +4048,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="134" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" s="1" t="s">
         <v>36</v>
       </c>
@@ -3713,7 +4056,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="135" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" s="1" t="s">
         <v>53</v>
       </c>
@@ -3721,7 +4064,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="136" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" s="1" t="s">
         <v>132</v>
       </c>
@@ -3729,7 +4072,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="137" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" s="1" t="s">
         <v>134</v>
       </c>
@@ -3737,7 +4080,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="138" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" s="1" t="s">
         <v>135</v>
       </c>
@@ -3745,7 +4088,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="139" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" s="1" t="s">
         <v>137</v>
       </c>
@@ -3753,7 +4096,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="140" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" s="1" t="s">
         <v>139</v>
       </c>
@@ -3761,7 +4104,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="141" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" s="1" t="s">
         <v>19</v>
       </c>
@@ -3769,7 +4112,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="142" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" s="1" t="s">
         <v>37</v>
       </c>
@@ -3777,7 +4120,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" s="1" t="s">
         <v>134</v>
       </c>
@@ -3785,7 +4128,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="144" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" s="1" t="s">
         <v>7</v>
       </c>
@@ -3793,7 +4136,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" s="1" t="s">
         <v>8</v>
       </c>
@@ -3801,7 +4144,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="146" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A146" s="1" t="s">
         <v>41</v>
       </c>
@@ -3809,7 +4152,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="147" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A147" s="1" t="s">
         <v>42</v>
       </c>
@@ -3817,7 +4160,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="148" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A148" s="1" t="s">
         <v>93</v>
       </c>
@@ -3825,7 +4168,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="149" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A149" s="1" t="s">
         <v>143</v>
       </c>
@@ -3833,7 +4176,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="150" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A150" s="1" t="s">
         <v>94</v>
       </c>
@@ -3841,7 +4184,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="151" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A151" s="1" t="s">
         <v>100</v>
       </c>
@@ -3849,7 +4192,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="152" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A152" s="1" t="s">
         <v>109</v>
       </c>
@@ -3857,7 +4200,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="153" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A153" s="1" t="s">
         <v>108</v>
       </c>
@@ -3865,7 +4208,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="154" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A154" s="1" t="s">
         <v>144</v>
       </c>
@@ -3873,7 +4216,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="155" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A155" s="1" t="s">
         <v>134</v>
       </c>
@@ -3881,7 +4224,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="156" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A156" s="1" t="s">
         <v>145</v>
       </c>
@@ -3889,7 +4232,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="157" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A157" s="1" t="s">
         <v>147</v>
       </c>
@@ -3897,7 +4240,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="158" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A158" s="1" t="s">
         <v>72</v>
       </c>
@@ -3905,7 +4248,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="159" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A159" s="1" t="s">
         <v>149</v>
       </c>
@@ -3913,7 +4256,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="160" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A160" t="s">
         <v>150</v>
       </c>
@@ -3921,7 +4264,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A161" s="1" t="s">
         <v>152</v>
       </c>
@@ -3929,7 +4272,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A162" s="1" t="s">
         <v>153</v>
       </c>
@@ -3937,7 +4280,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A163" t="s">
         <v>8</v>
       </c>
@@ -3948,7 +4291,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A164" s="1" t="s">
         <v>157</v>
       </c>
@@ -3959,7 +4302,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A165" s="1" t="s">
         <v>46</v>
       </c>
@@ -3970,7 +4313,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A166" s="1" t="s">
         <v>160</v>
       </c>
@@ -3981,7 +4324,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A167" s="1" t="s">
         <v>42</v>
       </c>
@@ -3992,7 +4335,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A168" s="1" t="s">
         <v>100</v>
       </c>
@@ -4003,7 +4346,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A169" s="1" t="s">
         <v>94</v>
       </c>
@@ -4014,7 +4357,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A170" s="1" t="s">
         <v>46</v>
       </c>
@@ -4025,7 +4368,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A171" s="1" t="s">
         <v>36</v>
       </c>
@@ -4036,7 +4379,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A172" s="1" t="s">
         <v>62</v>
       </c>
@@ -4047,7 +4390,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A173" s="1" t="s">
         <v>109</v>
       </c>
@@ -4058,7 +4401,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A174" s="1" t="s">
         <v>53</v>
       </c>
@@ -4069,7 +4412,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A175" s="1" t="s">
         <v>166</v>
       </c>
@@ -4080,7 +4423,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A176" s="1" t="s">
         <v>20</v>
       </c>
@@ -4091,7 +4434,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A177" s="1" t="s">
         <v>47</v>
       </c>
@@ -4102,7 +4445,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A178" s="1" t="s">
         <v>137</v>
       </c>
@@ -4113,7 +4456,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A179" s="1" t="s">
         <v>168</v>
       </c>
@@ -4124,7 +4467,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A180" s="1" t="s">
         <v>42</v>
       </c>
@@ -4135,7 +4478,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A181" s="1" t="s">
         <v>33</v>
       </c>
@@ -4146,7 +4489,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A182" s="1" t="s">
         <v>46</v>
       </c>
@@ -4157,7 +4500,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A183" s="1" t="s">
         <v>48</v>
       </c>
@@ -4168,7 +4511,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A184" s="1" t="s">
         <v>20</v>
       </c>
@@ -4179,7 +4522,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A185" s="1" t="s">
         <v>171</v>
       </c>
@@ -4190,7 +4533,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A186" s="1" t="s">
         <v>106</v>
       </c>
@@ -4198,7 +4541,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A187" s="1" t="s">
         <v>74</v>
       </c>
@@ -4209,7 +4552,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A188" s="1" t="s">
         <v>145</v>
       </c>
@@ -4220,7 +4563,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A189" s="1" t="s">
         <v>137</v>
       </c>
@@ -4231,7 +4574,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A190" s="1" t="s">
         <v>127</v>
       </c>
@@ -4242,7 +4585,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A191" s="1" t="s">
         <v>177</v>
       </c>
@@ -4253,7 +4596,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A192" s="1" t="s">
         <v>178</v>
       </c>
@@ -4264,7 +4607,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="193" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A193" s="1" t="s">
         <v>36</v>
       </c>
@@ -4275,7 +4618,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="194" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A194" s="1" t="s">
         <v>181</v>
       </c>
@@ -4286,7 +4629,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A195" s="1" t="s">
         <v>182</v>
       </c>
@@ -4297,7 +4640,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="196" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A196" s="1" t="s">
         <v>183</v>
       </c>
@@ -4308,7 +4651,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="197" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A197" s="1" t="s">
         <v>20</v>
       </c>
@@ -4319,7 +4662,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="198" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A198" s="1" t="s">
         <v>37</v>
       </c>
@@ -4330,7 +4673,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="199" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A199" s="1" t="s">
         <v>36</v>
       </c>
@@ -4341,7 +4684,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="200" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A200" s="1" t="s">
         <v>53</v>
       </c>
@@ -4352,7 +4695,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="201" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A201" s="1" t="s">
         <v>7</v>
       </c>
@@ -4363,7 +4706,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A202" s="1" t="s">
         <v>187</v>
       </c>
@@ -4374,7 +4717,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="203" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A203" s="1" t="s">
         <v>137</v>
       </c>
@@ -4385,7 +4728,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="204" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A204" s="1" t="s">
         <v>145</v>
       </c>
@@ -4396,7 +4739,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="205" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A205" s="1" t="s">
         <v>127</v>
       </c>
@@ -4407,7 +4750,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="206" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A206" s="1" t="s">
         <v>109</v>
       </c>
@@ -4418,7 +4761,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="207" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A207" s="1" t="s">
         <v>110</v>
       </c>
@@ -4429,7 +4772,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="208" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A208" s="1" t="s">
         <v>54</v>
       </c>
@@ -4440,7 +4783,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="90" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:3" ht="91.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A209" s="2" t="s">
         <v>194</v>
       </c>
@@ -4451,7 +4794,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="90" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:3" ht="91.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A210" s="1" t="s">
         <v>195</v>
       </c>
@@ -4462,7 +4805,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="90" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:3" ht="91.2" x14ac:dyDescent="0.55000000000000004">
       <c r="A211" s="1" t="s">
         <v>196</v>
       </c>
@@ -4473,7 +4816,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A212" s="1" t="s">
         <v>199</v>
       </c>
@@ -4484,7 +4827,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A213" s="1" t="s">
         <v>200</v>
       </c>
@@ -4495,7 +4838,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="214" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A214" s="1" t="s">
         <v>8</v>
       </c>
@@ -4506,7 +4849,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="215" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A215" s="1" t="s">
         <v>3</v>
       </c>
@@ -4517,7 +4860,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="216" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A216" s="1" t="s">
         <v>42</v>
       </c>
@@ -4528,7 +4871,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="217" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A217" s="1" t="s">
         <v>202</v>
       </c>
@@ -4539,7 +4882,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="218" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A218" s="1" t="s">
         <v>206</v>
       </c>
@@ -4550,7 +4893,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="219" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A219" s="1" t="s">
         <v>54</v>
       </c>
@@ -4561,7 +4904,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="220" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A220" s="1" t="s">
         <v>20</v>
       </c>
@@ -4572,7 +4915,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="221" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A221" s="1" t="s">
         <v>132</v>
       </c>
@@ -4583,7 +4926,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="222" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A222" s="1" t="s">
         <v>120</v>
       </c>
@@ -4594,7 +4937,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="223" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A223" s="1" t="s">
         <v>210</v>
       </c>
@@ -4605,7 +4948,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="224" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A224" s="1" t="s">
         <v>122</v>
       </c>
@@ -4616,7 +4959,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="135" x14ac:dyDescent="0.45">
+    <row r="225" spans="1:3" ht="159.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A225" s="2" t="s">
         <v>212</v>
       </c>
@@ -4627,7 +4970,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="226" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="226" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A226" s="1" t="s">
         <v>215</v>
       </c>
@@ -4635,7 +4978,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="227" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="227" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A227" s="1" t="s">
         <v>37</v>
       </c>
@@ -4643,7 +4986,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="228" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="228" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A228" s="1" t="s">
         <v>72</v>
       </c>
@@ -4651,7 +4994,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="229" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="229" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A229" s="1" t="s">
         <v>218</v>
       </c>
@@ -4659,7 +5002,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="230" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="230" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A230" s="1" t="s">
         <v>72</v>
       </c>
@@ -4667,7 +5010,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="231" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="231" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A231" s="1" t="s">
         <v>20</v>
       </c>
@@ -4675,7 +5018,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="232" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="232" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A232" s="1" t="s">
         <v>85</v>
       </c>
@@ -4683,7 +5026,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="233" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A233" s="1" t="s">
         <v>219</v>
       </c>
@@ -4691,7 +5034,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="234" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="234" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A234" s="1" t="s">
         <v>221</v>
       </c>
@@ -4699,7 +5042,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="235" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="235" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A235" s="1" t="s">
         <v>47</v>
       </c>
@@ -4707,7 +5050,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="236" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A236" s="1" t="s">
         <v>30</v>
       </c>
@@ -4715,7 +5058,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="237" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A237" s="1" t="s">
         <v>23</v>
       </c>
@@ -4723,7 +5066,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="238" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A238" s="1" t="s">
         <v>137</v>
       </c>
@@ -4731,7 +5074,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="239" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="239" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A239" t="s">
         <v>224</v>
       </c>
@@ -4742,7 +5085,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="240" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="240" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A240" s="1" t="s">
         <v>226</v>
       </c>
@@ -4753,7 +5096,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="241" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="241" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A241" s="2" t="s">
         <v>152</v>
       </c>
@@ -4761,7 +5104,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="242" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="242" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A242" s="1" t="s">
         <v>153</v>
       </c>
@@ -4769,7 +5112,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="243" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="243" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A243" s="1" t="s">
         <v>230</v>
       </c>
@@ -4777,7 +5120,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="244" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="244" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A244" s="1" t="s">
         <v>231</v>
       </c>
@@ -4785,7 +5128,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="245" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="245" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A245" t="s">
         <v>233</v>
       </c>
@@ -4793,7 +5136,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="246" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="246" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A246" s="1" t="s">
         <v>234</v>
       </c>
@@ -4801,7 +5144,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="247" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="247" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A247" t="s">
         <v>235</v>
       </c>
@@ -4809,7 +5152,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="248" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="248" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A248" s="1" t="s">
         <v>237</v>
       </c>
@@ -4817,7 +5160,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="249" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="249" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A249" s="1" t="s">
         <v>239</v>
       </c>
@@ -4825,7 +5168,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="250" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="250" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A250" s="1" t="s">
         <v>240</v>
       </c>
@@ -4833,7 +5176,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="251" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="251" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A251" s="2" t="s">
         <v>243</v>
       </c>
@@ -4841,7 +5184,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="252" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="252" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A252" t="s">
         <v>233</v>
       </c>
@@ -4849,7 +5192,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="253" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="253" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A253" s="1" t="s">
         <v>245</v>
       </c>
@@ -4857,7 +5200,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="254" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="254" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A254" s="1" t="s">
         <v>246</v>
       </c>
@@ -4865,7 +5208,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="255" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="255" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A255" s="1" t="s">
         <v>247</v>
       </c>
@@ -4873,7 +5216,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="256" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="256" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A256" s="1" t="s">
         <v>46</v>
       </c>
@@ -4881,7 +5224,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="257" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="257" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A257" s="1" t="s">
         <v>109</v>
       </c>
@@ -4889,7 +5232,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="258" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="258" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A258" s="1" t="s">
         <v>122</v>
       </c>
@@ -4897,7 +5240,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="259" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="259" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A259" s="1" t="s">
         <v>249</v>
       </c>
@@ -4905,7 +5248,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="260" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="260" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A260" s="1" t="s">
         <v>233</v>
       </c>
@@ -4913,7 +5256,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="261" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="261" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A261" s="1" t="s">
         <v>17</v>
       </c>
@@ -4921,7 +5264,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="262" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="262" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A262" s="1" t="s">
         <v>254</v>
       </c>
@@ -4929,7 +5272,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="263" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="263" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A263" s="1" t="s">
         <v>46</v>
       </c>
@@ -4937,7 +5280,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="264" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="264" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A264" s="1" t="s">
         <v>47</v>
       </c>
@@ -4945,7 +5288,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="265" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="265" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A265" s="1" t="s">
         <v>20</v>
       </c>
@@ -4953,7 +5296,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="266" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="266" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A266" s="1" t="s">
         <v>110</v>
       </c>
@@ -4961,7 +5304,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="267" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="267" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A267" s="1" t="s">
         <v>20</v>
       </c>
@@ -4969,7 +5312,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="268" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="268" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A268" s="1" t="s">
         <v>255</v>
       </c>
@@ -4977,7 +5320,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="269" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="269" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A269" s="1" t="s">
         <v>44</v>
       </c>
@@ -4985,7 +5328,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="270" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="270" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A270" s="1" t="s">
         <v>72</v>
       </c>
@@ -4993,7 +5336,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="271" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="271" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A271" s="1" t="s">
         <v>42</v>
       </c>
@@ -5001,7 +5344,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="272" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="272" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A272" s="1" t="s">
         <v>226</v>
       </c>
@@ -5009,7 +5352,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="273" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="273" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A273" t="s">
         <v>256</v>
       </c>
@@ -5017,7 +5360,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="274" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="274" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A274" t="s">
         <v>258</v>
       </c>
@@ -5025,7 +5368,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="275" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="275" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A275" t="s">
         <v>259</v>
       </c>
@@ -5033,7 +5376,7 @@
         <v>260</v>
       </c>
     </row>
-    <row r="276" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="276" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A276" s="1" t="s">
         <v>46</v>
       </c>
@@ -5041,7 +5384,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="277" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="277" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A277" s="1" t="s">
         <v>261</v>
       </c>
@@ -5049,7 +5392,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="278" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="278" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A278" s="1" t="s">
         <v>262</v>
       </c>
@@ -5057,7 +5400,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="279" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="279" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A279" s="1" t="s">
         <v>100</v>
       </c>
@@ -5065,7 +5408,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="280" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="280" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A280" s="1" t="s">
         <v>109</v>
       </c>
@@ -5073,7 +5416,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="281" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="281" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A281" s="1" t="s">
         <v>20</v>
       </c>
@@ -5081,7 +5424,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="282" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="282" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A282" t="s">
         <v>263</v>
       </c>
@@ -5089,7 +5432,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="283" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="283" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A283" s="1" t="s">
         <v>265</v>
       </c>
@@ -5097,7 +5440,7 @@
         <v>266</v>
       </c>
     </row>
-    <row r="284" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="284" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A284" s="1" t="s">
         <v>22</v>
       </c>
@@ -5105,7 +5448,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="285" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="285" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A285" s="1" t="s">
         <v>37</v>
       </c>
@@ -5113,7 +5456,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="286" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="286" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A286" s="1" t="s">
         <v>36</v>
       </c>
@@ -5121,7 +5464,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="287" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="287" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A287" s="1" t="s">
         <v>100</v>
       </c>
@@ -5129,7 +5472,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="288" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="288" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A288" s="1" t="s">
         <v>268</v>
       </c>
@@ -5137,7 +5480,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="289" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="289" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A289" s="1" t="s">
         <v>60</v>
       </c>
@@ -5145,7 +5488,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="290" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="290" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A290" t="s">
         <v>270</v>
       </c>
@@ -5153,7 +5496,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="291" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="291" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A291" s="1" t="s">
         <v>271</v>
       </c>
@@ -5161,7 +5504,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="292" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="292" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A292" t="s">
         <v>120</v>
       </c>
@@ -5169,7 +5512,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="293" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="293" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A293" s="1" t="s">
         <v>274</v>
       </c>
@@ -5177,7 +5520,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="294" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="294" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A294" s="1" t="s">
         <v>275</v>
       </c>
@@ -5185,7 +5528,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="295" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="295" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A295" s="1" t="s">
         <v>276</v>
       </c>
@@ -5193,7 +5536,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="296" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="296" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A296" s="1" t="s">
         <v>182</v>
       </c>
@@ -5201,7 +5544,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="297" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="297" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A297" s="1" t="s">
         <v>278</v>
       </c>
@@ -5209,7 +5552,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="298" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="298" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A298" s="1" t="s">
         <v>57</v>
       </c>
@@ -5217,7 +5560,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="299" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="299" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A299" s="1" t="s">
         <v>181</v>
       </c>
@@ -5225,7 +5568,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="300" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="300" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A300" s="1" t="s">
         <v>281</v>
       </c>
@@ -5233,7 +5576,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="301" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="301" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A301" s="1" t="s">
         <v>59</v>
       </c>
@@ -5241,7 +5584,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="302" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="302" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A302" s="1" t="s">
         <v>108</v>
       </c>
@@ -5249,7 +5592,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="303" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="303" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A303" s="1" t="s">
         <v>28</v>
       </c>
@@ -5257,7 +5600,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="304" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="304" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A304" s="1" t="s">
         <v>282</v>
       </c>
@@ -5265,7 +5608,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="305" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A305" s="1" t="s">
         <v>54</v>
       </c>
@@ -5273,7 +5616,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="306" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A306" s="1" t="s">
         <v>30</v>
       </c>
@@ -5281,7 +5624,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="307" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A307" s="1" t="s">
         <v>283</v>
       </c>
@@ -5289,7 +5632,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="308" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A308" s="1" t="s">
         <v>60</v>
       </c>
@@ -5297,7 +5640,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="309" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A309" s="1" t="s">
         <v>284</v>
       </c>
@@ -5305,7 +5648,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="310" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A310" s="1" t="s">
         <v>240</v>
       </c>
@@ -5313,7 +5656,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="311" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A311" s="1" t="s">
         <v>268</v>
       </c>
@@ -5321,7 +5664,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="312" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A312" s="1" t="s">
         <v>285</v>
       </c>
@@ -5329,7 +5672,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="313" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A313" s="1" t="s">
         <v>94</v>
       </c>
@@ -5337,7 +5680,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="314" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A314" s="1" t="s">
         <v>101</v>
       </c>
@@ -5345,7 +5688,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A315" s="1" t="s">
         <v>42</v>
       </c>
@@ -5353,7 +5696,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="316" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A316" t="s">
         <v>287</v>
       </c>
@@ -5361,7 +5704,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="317" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A317" s="1" t="s">
         <v>233</v>
       </c>
@@ -5369,7 +5712,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="318" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A318" s="1" t="s">
         <v>268</v>
       </c>
@@ -5377,7 +5720,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="319" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A319" s="1" t="s">
         <v>239</v>
       </c>
@@ -5385,7 +5728,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="320" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A320" s="1" t="s">
         <v>221</v>
       </c>
@@ -5393,7 +5736,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="321" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="321" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A321" s="1" t="s">
         <v>59</v>
       </c>
@@ -5401,7 +5744,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="322" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="322" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A322" t="s">
         <v>290</v>
       </c>
@@ -5409,7 +5752,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="323" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="323" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A323" t="s">
         <v>292</v>
       </c>
@@ -5417,7 +5760,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="324" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="324" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A324" s="1" t="s">
         <v>25</v>
       </c>
@@ -5425,7 +5768,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="325" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="325" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A325" s="1" t="s">
         <v>54</v>
       </c>
@@ -5433,7 +5776,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="326" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="326" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A326" s="1" t="s">
         <v>145</v>
       </c>
@@ -5441,7 +5784,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="327" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="327" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A327" s="1" t="s">
         <v>23</v>
       </c>
@@ -5449,7 +5792,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="328" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="328" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A328" s="1" t="s">
         <v>26</v>
       </c>
@@ -5457,7 +5800,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="329" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="329" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A329" s="1" t="s">
         <v>295</v>
       </c>
@@ -5465,7 +5808,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="330" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="330" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A330" s="1" t="s">
         <v>296</v>
       </c>
@@ -5473,7 +5816,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="331" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="331" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A331" s="1" t="s">
         <v>297</v>
       </c>
@@ -5481,7 +5824,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="332" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="332" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A332" s="1" t="s">
         <v>298</v>
       </c>
@@ -5489,7 +5832,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="333" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="333" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A333" s="1" t="s">
         <v>299</v>
       </c>
@@ -5497,7 +5840,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="334" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="334" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A334" s="1" t="s">
         <v>53</v>
       </c>
@@ -5505,7 +5848,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="335" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="335" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A335" s="1" t="s">
         <v>48</v>
       </c>
@@ -5513,7 +5856,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="336" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="336" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A336" s="1" t="s">
         <v>23</v>
       </c>
@@ -5521,7 +5864,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="337" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="337" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A337" s="1" t="s">
         <v>21</v>
       </c>
@@ -5529,7 +5872,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="338" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="338" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A338" s="1" t="s">
         <v>301</v>
       </c>
@@ -5537,7 +5880,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="339" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="339" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A339" s="1" t="s">
         <v>145</v>
       </c>
@@ -5545,7 +5888,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="340" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="340" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A340" s="1" t="s">
         <v>302</v>
       </c>
@@ -5553,7 +5896,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="341" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="341" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A341" s="1" t="s">
         <v>46</v>
       </c>
@@ -5561,7 +5904,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="342" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="342" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A342" s="1" t="s">
         <v>25</v>
       </c>
@@ -5569,7 +5912,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="343" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="343" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A343" t="s">
         <v>243</v>
       </c>
@@ -5577,7 +5920,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="344" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="344" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A344" t="s">
         <v>304</v>
       </c>
@@ -5585,7 +5928,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="345" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="345" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A345" s="1" t="s">
         <v>305</v>
       </c>
@@ -5593,7 +5936,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="346" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="346" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A346" s="1" t="s">
         <v>307</v>
       </c>
@@ -5601,7 +5944,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="347" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="347" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A347" s="1" t="s">
         <v>137</v>
       </c>
@@ -5609,7 +5952,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="348" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="348" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A348" s="1" t="s">
         <v>200</v>
       </c>
@@ -5617,7 +5960,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="349" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="349" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A349" t="s">
         <v>127</v>
       </c>
@@ -5625,7 +5968,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="350" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="350" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A350" s="1" t="s">
         <v>305</v>
       </c>
@@ -5633,7 +5976,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="351" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="351" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A351" s="1" t="s">
         <v>181</v>
       </c>
@@ -5641,7 +5984,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="352" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="352" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A352" t="s">
         <v>310</v>
       </c>
@@ -5649,7 +5992,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="353" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A353" s="1" t="s">
         <v>312</v>
       </c>
@@ -5660,7 +6003,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="354" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A354" s="1" t="s">
         <v>313</v>
       </c>
@@ -5671,7 +6014,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="355" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A355" s="1" t="s">
         <v>314</v>
       </c>
@@ -5682,7 +6025,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="356" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A356" s="1" t="s">
         <v>36</v>
       </c>
@@ -5690,7 +6033,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="357" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="357" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A357" s="1" t="s">
         <v>62</v>
       </c>
@@ -5698,7 +6041,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="358" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="358" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A358" s="1" t="s">
         <v>62</v>
       </c>
@@ -5706,7 +6049,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="359" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A359" s="1" t="s">
         <v>320</v>
       </c>
@@ -5714,7 +6057,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="360" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A360" s="1" t="s">
         <v>37</v>
       </c>
@@ -5722,7 +6065,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="361" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A361" s="1" t="s">
         <v>36</v>
       </c>
@@ -5730,7 +6073,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="362" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A362" t="s">
         <v>322</v>
       </c>
@@ -5738,7 +6081,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="363" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A363" t="s">
         <v>322</v>
       </c>
@@ -5746,7 +6089,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="364" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A364" s="1" t="s">
         <v>46</v>
       </c>
@@ -5754,7 +6097,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="365" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A365" s="1" t="s">
         <v>258</v>
       </c>
@@ -5762,7 +6105,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="366" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A366" s="1" t="s">
         <v>230</v>
       </c>
@@ -5770,7 +6113,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="367" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A367" s="1" t="s">
         <v>36</v>
       </c>
@@ -5781,7 +6124,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="368" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="368" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A368" s="1" t="s">
         <v>62</v>
       </c>
@@ -5792,7 +6135,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="369" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="369" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A369" s="1" t="s">
         <v>17</v>
       </c>
@@ -5803,7 +6146,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="370" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="370" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A370" s="1" t="s">
         <v>25</v>
       </c>
@@ -5814,7 +6157,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="371" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="371" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A371" s="1" t="s">
         <v>46</v>
       </c>
@@ -5825,7 +6168,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="372" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="372" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A372" s="1" t="s">
         <v>329</v>
       </c>
@@ -5833,7 +6176,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="373" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="373" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A373" t="s">
         <v>251</v>
       </c>
@@ -5841,7 +6184,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="374" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="374" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A374" s="1" t="s">
         <v>160</v>
       </c>
@@ -5849,7 +6192,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="375" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="375" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A375" s="1" t="s">
         <v>332</v>
       </c>
@@ -5857,7 +6200,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="376" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="376" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A376" s="1" t="s">
         <v>100</v>
       </c>
@@ -5865,7 +6208,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="377" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="377" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A377" s="1" t="s">
         <v>332</v>
       </c>
@@ -5873,7 +6216,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="378" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="378" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A378" s="1" t="s">
         <v>100</v>
       </c>
@@ -5881,7 +6224,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="379" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="379" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A379" t="s">
         <v>253</v>
       </c>
@@ -5889,7 +6232,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="380" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="380" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A380" t="s">
         <v>336</v>
       </c>
@@ -5897,7 +6240,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="381" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="381" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A381" s="1" t="s">
         <v>137</v>
       </c>
@@ -5905,7 +6248,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="382" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="382" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A382" s="1" t="s">
         <v>145</v>
       </c>
@@ -5913,7 +6256,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="383" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="383" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A383" s="1" t="s">
         <v>337</v>
       </c>
@@ -5921,7 +6264,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="384" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="384" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A384" s="1" t="s">
         <v>22</v>
       </c>
@@ -5929,7 +6272,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="385" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="385" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A385" s="1" t="s">
         <v>112</v>
       </c>
@@ -5937,7 +6280,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="386" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="386" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A386" s="1" t="s">
         <v>338</v>
       </c>
@@ -5945,7 +6288,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="387" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="387" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A387" s="1" t="s">
         <v>199</v>
       </c>
@@ -5953,7 +6296,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="388" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="388" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A388" s="1" t="s">
         <v>340</v>
       </c>
@@ -5961,7 +6304,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="389" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="389" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A389" s="1" t="s">
         <v>341</v>
       </c>
@@ -5969,7 +6312,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="390" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="390" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A390" s="1" t="s">
         <v>343</v>
       </c>
@@ -5977,7 +6320,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="391" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="391" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A391" s="1" t="s">
         <v>46</v>
       </c>
@@ -5985,7 +6328,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="392" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="392" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A392" s="1" t="s">
         <v>344</v>
       </c>
@@ -5993,7 +6336,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="393" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="393" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A393" s="1" t="s">
         <v>305</v>
       </c>
@@ -6001,7 +6344,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="394" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="394" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A394" s="1" t="s">
         <v>17</v>
       </c>
@@ -6009,7 +6352,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="395" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="395" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A395" s="1" t="s">
         <v>25</v>
       </c>
@@ -6017,7 +6360,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="396" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="396" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A396" s="1" t="s">
         <v>47</v>
       </c>
@@ -6025,7 +6368,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="397" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="397" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A397" s="1" t="s">
         <v>20</v>
       </c>
@@ -6033,7 +6376,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="398" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="398" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A398" t="s">
         <v>347</v>
       </c>
@@ -6041,7 +6384,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="399" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="399" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A399" t="s">
         <v>349</v>
       </c>
@@ -6049,7 +6392,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="400" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="400" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A400" s="1" t="s">
         <v>350</v>
       </c>
@@ -6057,7 +6400,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="401" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="401" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A401" t="s">
         <v>351</v>
       </c>
@@ -6065,7 +6408,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="402" spans="1:3" ht="23.25" x14ac:dyDescent="0.5">
+    <row r="402" spans="1:3" ht="24" x14ac:dyDescent="0.65">
       <c r="A402" s="1" t="s">
         <v>135</v>
       </c>
@@ -6076,7 +6419,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="403" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="403" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A403" s="1" t="s">
         <v>183</v>
       </c>
@@ -6087,7 +6430,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="404" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="404" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A404" s="1" t="s">
         <v>74</v>
       </c>
@@ -6098,7 +6441,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="405" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="405" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A405" s="1" t="s">
         <v>80</v>
       </c>
@@ -6106,7 +6449,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="406" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="406" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A406" s="1" t="s">
         <v>274</v>
       </c>
@@ -6114,7 +6457,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="407" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="407" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A407" s="1" t="s">
         <v>206</v>
       </c>
@@ -6122,7 +6465,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="408" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="408" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A408" s="1" t="s">
         <v>343</v>
       </c>
@@ -6130,7 +6473,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="409" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="409" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A409" s="1" t="s">
         <v>17</v>
       </c>
@@ -6138,7 +6481,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="410" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="410" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A410" t="s">
         <v>243</v>
       </c>
@@ -6146,7 +6489,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="411" spans="1:3" ht="45" x14ac:dyDescent="0.45">
+    <row r="411" spans="1:3" ht="45.6" x14ac:dyDescent="0.55000000000000004">
       <c r="A411" s="1" t="s">
         <v>62</v>
       </c>
@@ -6157,7 +6500,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="412" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="412" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A412" t="s">
         <v>356</v>
       </c>
@@ -6165,7 +6508,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="413" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="413" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A413" s="1" t="s">
         <v>78</v>
       </c>
@@ -6173,7 +6516,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="414" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="414" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A414" s="1" t="s">
         <v>8</v>
       </c>
@@ -6181,7 +6524,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="415" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="415" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A415" s="1" t="s">
         <v>258</v>
       </c>
@@ -6189,7 +6532,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="416" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="416" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A416" s="1" t="s">
         <v>359</v>
       </c>
@@ -6197,7 +6540,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="417" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A417" s="1" t="s">
         <v>261</v>
       </c>
@@ -6205,7 +6548,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="418" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A418" s="1" t="s">
         <v>60</v>
       </c>
@@ -6213,7 +6556,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="419" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A419" s="1" t="s">
         <v>72</v>
       </c>
@@ -6221,7 +6564,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="420" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A420" s="1" t="s">
         <v>42</v>
       </c>
@@ -6229,7 +6572,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="421" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A421" s="1" t="s">
         <v>226</v>
       </c>
@@ -6237,7 +6580,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="422" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A422" s="1" t="s">
         <v>230</v>
       </c>
@@ -6245,7 +6588,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="423" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A423" s="1" t="s">
         <v>145</v>
       </c>
@@ -6253,7 +6596,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="424" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A424" s="1" t="s">
         <v>252</v>
       </c>
@@ -6261,7 +6604,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="425" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A425" s="1" t="s">
         <v>251</v>
       </c>
@@ -6269,7 +6612,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="426" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A426" s="1" t="s">
         <v>363</v>
       </c>
@@ -6277,7 +6620,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="427" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A427" s="1" t="s">
         <v>23</v>
       </c>
@@ -6285,7 +6628,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="428" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A428" t="s">
         <v>365</v>
       </c>
@@ -6296,7 +6639,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="429" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A429" t="s">
         <v>368</v>
       </c>
@@ -6307,7 +6650,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="430" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A430" t="s">
         <v>369</v>
       </c>
@@ -6318,7 +6661,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="431" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A431" t="s">
         <v>370</v>
       </c>
@@ -6329,7 +6672,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="432" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A432" t="s">
         <v>373</v>
       </c>
@@ -6340,7 +6683,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="433" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="433" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A433" t="s">
         <v>369</v>
       </c>
@@ -6351,7 +6694,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="434" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="434" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A434" t="s">
         <v>374</v>
       </c>
@@ -6362,7 +6705,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="435" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="435" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A435" t="s">
         <v>370</v>
       </c>
@@ -6373,7 +6716,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="436" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="436" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A436" t="s">
         <v>373</v>
       </c>
@@ -6384,7 +6727,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="437" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="437" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A437" t="s">
         <v>374</v>
       </c>
@@ -6395,7 +6738,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="438" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="438" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A438" t="s">
         <v>370</v>
       </c>
@@ -6406,7 +6749,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="439" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="439" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A439" t="s">
         <v>369</v>
       </c>
@@ -6417,7 +6760,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="440" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="440" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A440" t="s">
         <v>374</v>
       </c>
@@ -6428,7 +6771,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="441" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="441" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A441" t="s">
         <v>370</v>
       </c>
@@ -6439,7 +6782,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="442" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="442" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A442" t="s">
         <v>365</v>
       </c>
@@ -6450,7 +6793,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="443" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="443" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A443" t="s">
         <v>379</v>
       </c>
@@ -6461,7 +6804,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="444" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="444" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A444" t="s">
         <v>374</v>
       </c>
@@ -6472,7 +6815,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="445" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="445" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A445" t="s">
         <v>365</v>
       </c>
@@ -6483,7 +6826,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="446" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="446" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A446" t="s">
         <v>384</v>
       </c>
@@ -6494,7 +6837,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="447" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="447" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A447" t="s">
         <v>370</v>
       </c>
@@ -6505,7 +6848,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="448" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="448" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A448" t="s">
         <v>374</v>
       </c>
@@ -6516,7 +6859,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="449" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A449" t="s">
         <v>387</v>
       </c>
@@ -6527,7 +6870,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="450" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A450" t="s">
         <v>388</v>
       </c>
@@ -6538,7 +6881,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="451" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A451" t="s">
         <v>374</v>
       </c>
@@ -6549,7 +6892,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="452" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A452" t="s">
         <v>390</v>
       </c>
@@ -6560,7 +6903,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="453" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A453" t="s">
         <v>365</v>
       </c>
@@ -6571,7 +6914,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="454" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A454" t="s">
         <v>393</v>
       </c>
@@ -6582,7 +6925,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="455" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A455" t="s">
         <v>365</v>
       </c>
@@ -6593,7 +6936,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="456" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A456" t="s">
         <v>398</v>
       </c>
@@ -6604,7 +6947,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="457" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A457" t="s">
         <v>400</v>
       </c>
@@ -6615,7 +6958,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="458" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A458" t="s">
         <v>401</v>
       </c>
@@ -6626,7 +6969,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="459" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A459" t="s">
         <v>402</v>
       </c>
@@ -6637,7 +6980,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="460" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A460" t="s">
         <v>403</v>
       </c>
@@ -6648,7 +6991,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="461" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A461" t="s">
         <v>400</v>
       </c>
@@ -6659,7 +7002,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="462" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A462" t="s">
         <v>406</v>
       </c>
@@ -6670,7 +7013,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="463" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A463" t="s">
         <v>407</v>
       </c>
@@ -6681,7 +7024,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="464" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="464" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A464" t="s">
         <v>409</v>
       </c>
@@ -6692,7 +7035,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="465" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="465" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A465" t="s">
         <v>368</v>
       </c>
@@ -6703,7 +7046,7 @@
         <v>448</v>
       </c>
     </row>
-    <row r="466" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="466" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A466" t="s">
         <v>373</v>
       </c>
@@ -6714,7 +7057,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="467" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="467" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A467" t="s">
         <v>369</v>
       </c>
@@ -6725,7 +7068,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="468" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="468" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A468" t="s">
         <v>368</v>
       </c>
@@ -6736,7 +7079,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="469" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="469" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A469" t="s">
         <v>369</v>
       </c>
@@ -6747,7 +7090,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="470" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="470" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A470" t="s">
         <v>374</v>
       </c>
@@ -6758,7 +7101,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="471" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="471" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A471" t="s">
         <v>387</v>
       </c>
@@ -6769,7 +7112,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="472" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="472" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A472" t="s">
         <v>415</v>
       </c>
@@ -6780,7 +7123,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="473" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="473" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A473" t="s">
         <v>418</v>
       </c>
@@ -6791,7 +7134,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="474" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="474" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A474" t="s">
         <v>421</v>
       </c>
@@ -6802,7 +7145,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="475" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="475" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A475" t="s">
         <v>424</v>
       </c>
@@ -6813,7 +7156,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="476" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="476" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A476" t="s">
         <v>425</v>
       </c>
@@ -6824,7 +7167,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="477" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="477" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A477" t="s">
         <v>426</v>
       </c>
@@ -6835,7 +7178,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="478" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="478" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A478" t="s">
         <v>427</v>
       </c>
@@ -6846,7 +7189,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="479" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="479" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A479" t="s">
         <v>430</v>
       </c>
@@ -6857,7 +7200,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="480" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="480" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A480" t="s">
         <v>432</v>
       </c>
@@ -6868,7 +7211,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="481" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="481" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A481" t="s">
         <v>434</v>
       </c>
@@ -6879,7 +7222,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="482" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="482" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A482" t="s">
         <v>436</v>
       </c>
@@ -6890,7 +7233,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="483" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="483" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A483" t="s">
         <v>438</v>
       </c>
@@ -6901,7 +7244,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="484" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="484" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A484" t="s">
         <v>439</v>
       </c>
@@ -6912,7 +7255,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="485" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="485" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A485" t="s">
         <v>440</v>
       </c>
@@ -6923,7 +7266,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="486" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="486" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A486" t="s">
         <v>415</v>
       </c>
@@ -6934,7 +7277,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="487" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="487" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A487" t="s">
         <v>418</v>
       </c>
@@ -6945,7 +7288,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="488" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="488" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A488" t="s">
         <v>451</v>
       </c>
@@ -6956,7 +7299,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="489" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="489" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A489" t="s">
         <v>452</v>
       </c>
@@ -6967,7 +7310,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="490" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="490" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A490" t="s">
         <v>453</v>
       </c>
@@ -6978,7 +7321,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="491" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="491" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A491" t="s">
         <v>419</v>
       </c>
@@ -6989,7 +7332,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="492" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="492" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A492" t="s">
         <v>454</v>
       </c>
@@ -7000,7 +7343,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="493" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="493" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A493" t="s">
         <v>455</v>
       </c>
@@ -7011,7 +7354,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="494" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="494" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A494" t="s">
         <v>456</v>
       </c>
@@ -7022,7 +7365,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="495" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="495" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A495" t="s">
         <v>421</v>
       </c>
@@ -7033,7 +7376,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="496" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="496" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A496" t="s">
         <v>424</v>
       </c>
@@ -7044,7 +7387,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="497" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="497" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A497" t="s">
         <v>425</v>
       </c>
@@ -7055,7 +7398,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="498" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="498" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A498" t="s">
         <v>426</v>
       </c>
@@ -7066,7 +7409,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="499" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="499" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A499" t="s">
         <v>457</v>
       </c>
@@ -7077,7 +7420,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="500" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="500" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A500" t="s">
         <v>427</v>
       </c>
@@ -7088,7 +7431,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="501" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="501" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A501" t="s">
         <v>458</v>
       </c>
@@ -7099,7 +7442,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="502" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="502" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A502" t="s">
         <v>459</v>
       </c>
@@ -7110,7 +7453,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="503" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="503" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A503" t="s">
         <v>430</v>
       </c>
@@ -7121,7 +7464,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="504" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="504" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A504" t="s">
         <v>432</v>
       </c>
@@ -7132,7 +7475,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="505" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="505" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A505" t="s">
         <v>434</v>
       </c>
@@ -7143,7 +7486,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="506" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="506" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A506" t="s">
         <v>460</v>
       </c>
@@ -7154,7 +7497,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="507" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="507" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A507" t="s">
         <v>461</v>
       </c>
@@ -7165,7 +7508,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="508" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="508" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A508" t="s">
         <v>436</v>
       </c>
@@ -7176,7 +7519,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="509" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="509" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A509" t="s">
         <v>438</v>
       </c>
@@ -7187,7 +7530,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="510" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="510" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A510" t="s">
         <v>439</v>
       </c>
@@ -7198,7 +7541,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="511" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="511" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A511" t="s">
         <v>440</v>
       </c>
@@ -7209,7 +7552,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="512" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="512" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A512" t="s">
         <v>462</v>
       </c>
@@ -7220,7 +7563,7 @@
         <v>486</v>
       </c>
     </row>
-    <row r="513" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="513" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A513" t="s">
         <v>463</v>
       </c>
@@ -7231,7 +7574,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="514" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="514" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A514" t="s">
         <v>374</v>
       </c>
@@ -7242,7 +7585,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="515" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="515" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A515" t="s">
         <v>387</v>
       </c>
@@ -7253,7 +7596,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="516" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="516" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A516" t="s">
         <v>390</v>
       </c>
@@ -7264,7 +7607,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="517" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="517" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A517" t="s">
         <v>464</v>
       </c>
@@ -7275,7 +7618,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="518" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="518" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A518" t="s">
         <v>465</v>
       </c>
@@ -7286,7 +7629,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="519" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="519" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A519" t="s">
         <v>403</v>
       </c>
@@ -7297,7 +7640,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="520" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="520" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A520" t="s">
         <v>466</v>
       </c>
@@ -7308,7 +7651,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="521" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="521" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A521" t="s">
         <v>467</v>
       </c>
@@ -7319,7 +7662,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="522" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="522" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A522" t="s">
         <v>468</v>
       </c>
@@ -7330,7 +7673,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="523" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="523" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A523" t="s">
         <v>469</v>
       </c>
@@ -7341,7 +7684,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="524" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="524" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A524" t="s">
         <v>470</v>
       </c>
@@ -7352,7 +7695,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="525" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="525" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A525" t="s">
         <v>471</v>
       </c>
@@ -7363,7 +7706,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="526" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="526" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A526" t="s">
         <v>490</v>
       </c>
@@ -7374,7 +7717,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="527" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="527" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A527" t="s">
         <v>491</v>
       </c>
@@ -7385,7 +7728,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="528" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="528" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A528" t="s">
         <v>492</v>
       </c>
@@ -7396,7 +7739,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="529" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="529" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A529" t="s">
         <v>493</v>
       </c>
@@ -7407,7 +7750,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="530" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="530" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A530" t="s">
         <v>494</v>
       </c>
@@ -7418,7 +7761,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="531" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="531" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A531" t="s">
         <v>495</v>
       </c>
@@ -7429,7 +7772,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="532" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="532" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A532" t="s">
         <v>496</v>
       </c>
@@ -7440,7 +7783,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="533" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="533" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A533" t="s">
         <v>497</v>
       </c>
@@ -7451,7 +7794,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="534" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="534" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A534" t="s">
         <v>498</v>
       </c>
@@ -7462,7 +7805,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="535" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="535" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A535" t="s">
         <v>499</v>
       </c>
@@ -7473,7 +7816,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="536" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="536" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A536" t="s">
         <v>500</v>
       </c>
@@ -7484,7 +7827,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="537" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="537" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A537" t="s">
         <v>501</v>
       </c>
@@ -7495,7 +7838,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="538" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="538" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A538" t="s">
         <v>502</v>
       </c>
@@ -7506,7 +7849,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="539" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="539" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A539" t="s">
         <v>503</v>
       </c>
@@ -7517,7 +7860,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="540" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="540" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A540" t="s">
         <v>504</v>
       </c>
@@ -7528,7 +7871,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="541" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="541" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A541" t="s">
         <v>505</v>
       </c>
@@ -7539,7 +7882,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="542" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="542" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A542" t="s">
         <v>506</v>
       </c>
@@ -7550,7 +7893,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="543" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="543" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A543" t="s">
         <v>507</v>
       </c>
@@ -7561,7 +7904,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="544" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="544" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A544" t="s">
         <v>508</v>
       </c>
@@ -7572,7 +7915,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="545" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="545" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A545" t="s">
         <v>509</v>
       </c>
@@ -7583,7 +7926,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="546" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="546" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A546" t="s">
         <v>510</v>
       </c>
@@ -7594,7 +7937,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="547" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="547" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A547" t="s">
         <v>511</v>
       </c>
@@ -7605,7 +7948,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="548" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="548" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A548" t="s">
         <v>512</v>
       </c>
@@ -7616,7 +7959,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="549" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="549" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A549" t="s">
         <v>513</v>
       </c>
@@ -7627,7 +7970,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="550" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="550" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A550" t="s">
         <v>514</v>
       </c>
@@ -7638,7 +7981,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="551" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="551" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A551" t="s">
         <v>515</v>
       </c>
@@ -7649,7 +7992,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="552" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="552" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A552" t="s">
         <v>516</v>
       </c>
@@ -7660,7 +8003,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="553" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="553" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A553" t="s">
         <v>517</v>
       </c>
@@ -7671,7 +8014,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="554" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="554" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A554" t="s">
         <v>518</v>
       </c>
@@ -7682,7 +8025,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="555" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="555" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A555" t="s">
         <v>519</v>
       </c>
@@ -7693,7 +8036,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="556" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="556" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A556" t="s">
         <v>520</v>
       </c>
@@ -7704,7 +8047,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="557" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="557" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A557" t="s">
         <v>521</v>
       </c>
@@ -7715,7 +8058,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="558" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="558" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A558" t="s">
         <v>522</v>
       </c>
@@ -7726,7 +8069,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="559" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="559" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A559" t="s">
         <v>523</v>
       </c>
@@ -7737,7 +8080,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="560" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="560" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A560" t="s">
         <v>524</v>
       </c>
@@ -7748,7 +8091,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="561" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="561" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A561" t="s">
         <v>525</v>
       </c>
@@ -7759,7 +8102,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="562" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="562" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A562" t="s">
         <v>526</v>
       </c>
@@ -7770,7 +8113,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="563" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="563" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A563" t="s">
         <v>527</v>
       </c>
@@ -7781,7 +8124,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="564" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="564" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A564" t="s">
         <v>528</v>
       </c>
@@ -7792,7 +8135,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="565" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="565" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A565" t="s">
         <v>529</v>
       </c>
@@ -7803,7 +8146,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="566" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="566" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A566" t="s">
         <v>499</v>
       </c>
@@ -7814,7 +8157,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="567" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="567" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A567" t="s">
         <v>555</v>
       </c>
@@ -7825,7 +8168,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="568" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="568" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A568" t="s">
         <v>498</v>
       </c>
@@ -7836,7 +8179,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="569" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="569" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A569" t="s">
         <v>556</v>
       </c>
@@ -7847,7 +8190,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="570" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="570" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A570" t="s">
         <v>557</v>
       </c>
@@ -7858,7 +8201,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="571" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="571" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A571" t="s">
         <v>500</v>
       </c>
@@ -7869,7 +8212,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="572" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="572" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A572" t="s">
         <v>558</v>
       </c>
@@ -7880,7 +8223,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="573" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="573" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A573" t="s">
         <v>559</v>
       </c>
@@ -7891,7 +8234,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="574" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="574" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A574" t="s">
         <v>560</v>
       </c>
@@ -7902,7 +8245,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="575" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="575" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A575" t="s">
         <v>561</v>
       </c>
@@ -7913,7 +8256,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="576" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="576" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A576" t="s">
         <v>562</v>
       </c>
@@ -7924,7 +8267,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="577" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="577" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A577" t="s">
         <v>563</v>
       </c>
@@ -7935,7 +8278,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="578" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="578" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A578" t="s">
         <v>564</v>
       </c>
@@ -7946,7 +8289,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="579" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="579" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A579" t="s">
         <v>565</v>
       </c>
@@ -7957,7 +8300,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="580" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="580" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A580" t="s">
         <v>566</v>
       </c>
@@ -7968,7 +8311,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="581" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="581" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A581" t="s">
         <v>567</v>
       </c>
@@ -7979,7 +8322,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="582" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="582" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A582" t="s">
         <v>568</v>
       </c>
@@ -7990,7 +8333,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="583" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="583" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A583" t="s">
         <v>569</v>
       </c>
@@ -8001,7 +8344,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="584" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="584" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A584" t="s">
         <v>570</v>
       </c>
@@ -8012,7 +8355,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="585" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="585" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A585" t="s">
         <v>508</v>
       </c>
@@ -8023,7 +8366,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="586" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="586" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A586" t="s">
         <v>571</v>
       </c>
@@ -8034,7 +8377,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="587" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="587" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A587" t="s">
         <v>572</v>
       </c>
@@ -8045,7 +8388,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="588" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="588" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A588" t="s">
         <v>573</v>
       </c>
@@ -8056,7 +8399,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="589" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="589" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A589" t="s">
         <v>574</v>
       </c>
@@ -8067,7 +8410,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="590" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="590" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A590" t="s">
         <v>575</v>
       </c>
@@ -8078,7 +8421,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="591" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="591" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A591" t="s">
         <v>576</v>
       </c>
@@ -8089,7 +8432,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="592" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="592" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A592" t="s">
         <v>577</v>
       </c>
@@ -8100,7 +8443,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="593" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="593" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A593" t="s">
         <v>578</v>
       </c>
@@ -8111,7 +8454,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="594" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="594" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A594" t="s">
         <v>579</v>
       </c>
@@ -8122,7 +8465,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="595" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="595" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A595" t="s">
         <v>580</v>
       </c>
@@ -8133,7 +8476,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="596" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="596" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A596" t="s">
         <v>370</v>
       </c>
@@ -8144,7 +8487,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="597" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="597" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A597" t="s">
         <v>613</v>
       </c>
@@ -8155,7 +8498,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="598" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="598" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A598" t="s">
         <v>614</v>
       </c>
@@ -8166,7 +8509,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="599" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="599" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A599" t="s">
         <v>615</v>
       </c>
@@ -8177,7 +8520,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="600" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="600" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A600" t="s">
         <v>616</v>
       </c>
@@ -8188,7 +8531,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="601" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="601" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A601" t="s">
         <v>373</v>
       </c>
@@ -8199,7 +8542,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="602" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="602" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A602" t="s">
         <v>617</v>
       </c>
@@ -8210,7 +8553,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="603" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="603" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A603" t="s">
         <v>618</v>
       </c>
@@ -8221,7 +8564,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="604" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="604" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A604" t="s">
         <v>619</v>
       </c>
@@ -8232,7 +8575,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="605" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="605" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A605" t="s">
         <v>620</v>
       </c>
@@ -8243,7 +8586,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="606" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="606" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A606" t="s">
         <v>621</v>
       </c>
@@ -8254,7 +8597,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="607" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="607" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A607" t="s">
         <v>622</v>
       </c>
@@ -8265,7 +8608,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="608" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="608" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A608" t="s">
         <v>623</v>
       </c>
@@ -8276,7 +8619,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="609" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="609" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A609" t="s">
         <v>558</v>
       </c>
@@ -8287,7 +8630,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="610" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="610" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A610" t="s">
         <v>624</v>
       </c>
@@ -8298,7 +8641,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="611" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="611" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A611" t="s">
         <v>625</v>
       </c>
@@ -8309,7 +8652,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="612" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="612" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A612" t="s">
         <v>626</v>
       </c>
@@ -8320,7 +8663,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="613" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="613" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A613" t="s">
         <v>579</v>
       </c>
@@ -8331,7 +8674,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="614" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="614" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A614" t="s">
         <v>627</v>
       </c>
@@ -8342,7 +8685,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="615" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="615" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A615" t="s">
         <v>563</v>
       </c>
@@ -8353,7 +8696,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="616" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="616" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A616" t="s">
         <v>628</v>
       </c>
@@ -8364,7 +8707,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="617" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="617" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A617" t="s">
         <v>629</v>
       </c>
@@ -8375,7 +8718,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="618" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="618" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A618" t="s">
         <v>630</v>
       </c>
@@ -8386,7 +8729,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="619" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="619" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A619" t="s">
         <v>631</v>
       </c>
@@ -8397,7 +8740,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="620" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="620" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A620" t="s">
         <v>632</v>
       </c>
@@ -8408,7 +8751,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="621" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="621" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A621" t="s">
         <v>633</v>
       </c>
@@ -8419,7 +8762,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="622" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="622" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A622" t="s">
         <v>503</v>
       </c>
@@ -8430,7 +8773,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="623" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="623" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A623" t="s">
         <v>634</v>
       </c>
@@ -8441,7 +8784,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="624" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="624" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A624" t="s">
         <v>635</v>
       </c>
@@ -8452,7 +8795,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="625" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="625" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A625" t="s">
         <v>636</v>
       </c>
@@ -8463,7 +8806,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="626" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="626" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A626" t="s">
         <v>396</v>
       </c>
@@ -8474,7 +8817,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="627" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="627" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A627" t="s">
         <v>665</v>
       </c>
@@ -8485,7 +8828,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="628" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="628" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A628" t="s">
         <v>666</v>
       </c>
@@ -8496,7 +8839,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="629" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="629" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A629" t="s">
         <v>667</v>
       </c>
@@ -8507,7 +8850,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="630" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="630" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A630" t="s">
         <v>668</v>
       </c>
@@ -8518,7 +8861,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="631" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="631" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A631" t="s">
         <v>669</v>
       </c>
@@ -8529,7 +8872,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="632" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="632" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A632" t="s">
         <v>670</v>
       </c>
@@ -8540,7 +8883,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="633" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="633" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A633" t="s">
         <v>671</v>
       </c>
@@ -8551,7 +8894,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="634" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="634" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A634" t="s">
         <v>672</v>
       </c>
@@ -8562,7 +8905,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="635" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="635" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A635" t="s">
         <v>369</v>
       </c>
@@ -8573,7 +8916,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="636" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="636" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A636" t="s">
         <v>613</v>
       </c>
@@ -8584,7 +8927,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="637" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="637" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A637" t="s">
         <v>373</v>
       </c>
@@ -8595,7 +8938,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="638" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="638" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A638" t="s">
         <v>556</v>
       </c>
@@ -8606,7 +8949,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="639" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="639" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A639" t="s">
         <v>673</v>
       </c>
@@ -8617,7 +8960,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="640" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="640" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A640" t="s">
         <v>674</v>
       </c>
@@ -8628,7 +8971,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="641" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="641" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A641" t="s">
         <v>690</v>
       </c>
@@ -8639,7 +8982,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="642" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="642" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A642" t="s">
         <v>691</v>
       </c>
@@ -8650,7 +8993,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="643" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="643" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A643" t="s">
         <v>692</v>
       </c>
@@ -8661,7 +9004,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="644" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="644" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A644" t="s">
         <v>693</v>
       </c>
@@ -8672,7 +9015,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="645" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="645" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A645" t="s">
         <v>694</v>
       </c>
@@ -8683,7 +9026,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="646" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="646" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A646" t="s">
         <v>695</v>
       </c>
@@ -8694,7 +9037,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="647" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="647" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A647" t="s">
         <v>696</v>
       </c>
@@ -8705,7 +9048,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="648" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="648" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A648" t="s">
         <v>697</v>
       </c>
@@ -8716,7 +9059,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="649" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="649" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A649" t="s">
         <v>698</v>
       </c>
@@ -8727,7 +9070,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="650" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="650" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A650" t="s">
         <v>699</v>
       </c>
@@ -8738,7 +9081,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="651" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="651" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A651" t="s">
         <v>700</v>
       </c>
@@ -8749,7 +9092,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="652" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="652" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A652" t="s">
         <v>365</v>
       </c>
@@ -8760,7 +9103,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="653" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="653" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A653" t="s">
         <v>374</v>
       </c>
@@ -8771,7 +9114,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="654" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="654" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A654" t="s">
         <v>672</v>
       </c>
@@ -8782,7 +9125,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="655" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="655" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A655" t="s">
         <v>701</v>
       </c>
@@ -8793,7 +9136,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="656" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="656" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A656" t="s">
         <v>713</v>
       </c>
@@ -8804,7 +9147,7 @@
         <v>733</v>
       </c>
     </row>
-    <row r="657" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="657" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A657" t="s">
         <v>714</v>
       </c>
@@ -8815,7 +9158,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="658" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="658" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A658" t="s">
         <v>715</v>
       </c>
@@ -8826,7 +9169,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="659" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="659" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A659" t="s">
         <v>716</v>
       </c>
@@ -8837,7 +9180,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="660" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="660" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A660" t="s">
         <v>717</v>
       </c>
@@ -8848,7 +9191,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="661" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="661" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A661" t="s">
         <v>430</v>
       </c>
@@ -8859,7 +9202,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="662" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="662" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A662" t="s">
         <v>459</v>
       </c>
@@ -8870,7 +9213,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="663" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="663" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A663" t="s">
         <v>432</v>
       </c>
@@ -8881,7 +9224,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="664" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="664" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A664" t="s">
         <v>718</v>
       </c>
@@ -8892,7 +9235,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="665" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="665" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A665" t="s">
         <v>719</v>
       </c>
@@ -8903,7 +9246,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="666" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="666" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A666" t="s">
         <v>720</v>
       </c>
@@ -8914,7 +9257,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="667" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="667" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A667" t="s">
         <v>721</v>
       </c>
@@ -8925,7 +9268,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="668" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="668" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A668" t="s">
         <v>722</v>
       </c>
@@ -8936,7 +9279,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="669" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="669" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A669" t="s">
         <v>723</v>
       </c>
@@ -8947,7 +9290,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="670" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="670" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A670" t="s">
         <v>667</v>
       </c>
@@ -8962,4 +9305,899 @@
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C664218-0DFD-4B9B-898E-4542568909C9}">
+  <dimension ref="A1:D63"/>
+  <sheetFormatPr defaultRowHeight="22.8" x14ac:dyDescent="0.55000000000000004"/>
+  <cols>
+    <col min="2" max="2" width="23.3984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>739</v>
+      </c>
+      <c r="B1" t="s">
+        <v>740</v>
+      </c>
+      <c r="C1" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
+        <v>742</v>
+      </c>
+      <c r="B2" t="s">
+        <v>743</v>
+      </c>
+      <c r="C2" t="s">
+        <v>744</v>
+      </c>
+      <c r="D2" t="s">
+        <v>745</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>742</v>
+      </c>
+      <c r="B3" t="s">
+        <v>743</v>
+      </c>
+      <c r="C3" t="s">
+        <v>746</v>
+      </c>
+      <c r="D3" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
+        <v>742</v>
+      </c>
+      <c r="B4" t="s">
+        <v>743</v>
+      </c>
+      <c r="C4" t="s">
+        <v>748</v>
+      </c>
+      <c r="D4" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>742</v>
+      </c>
+      <c r="B5" t="s">
+        <v>743</v>
+      </c>
+      <c r="C5" t="s">
+        <v>750</v>
+      </c>
+      <c r="D5" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>742</v>
+      </c>
+      <c r="B6" t="s">
+        <v>743</v>
+      </c>
+      <c r="C6" t="s">
+        <v>751</v>
+      </c>
+      <c r="D6" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A7" t="s">
+        <v>742</v>
+      </c>
+      <c r="B7" t="s">
+        <v>743</v>
+      </c>
+      <c r="C7" t="s">
+        <v>753</v>
+      </c>
+      <c r="D7" t="s">
+        <v>754</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A8" t="s">
+        <v>742</v>
+      </c>
+      <c r="B8" t="s">
+        <v>743</v>
+      </c>
+      <c r="C8" t="s">
+        <v>755</v>
+      </c>
+      <c r="D8" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A9" t="s">
+        <v>742</v>
+      </c>
+      <c r="B9" t="s">
+        <v>743</v>
+      </c>
+      <c r="C9" t="s">
+        <v>757</v>
+      </c>
+      <c r="D9" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A10" t="s">
+        <v>742</v>
+      </c>
+      <c r="B10" t="s">
+        <v>743</v>
+      </c>
+      <c r="C10" t="s">
+        <v>759</v>
+      </c>
+      <c r="D10" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11" t="s">
+        <v>761</v>
+      </c>
+      <c r="C11" t="s">
+        <v>762</v>
+      </c>
+      <c r="D11" t="s">
+        <v>763</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>761</v>
+      </c>
+      <c r="C12" t="s">
+        <v>764</v>
+      </c>
+      <c r="D12" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13" t="s">
+        <v>761</v>
+      </c>
+      <c r="C13" t="s">
+        <v>766</v>
+      </c>
+      <c r="D13" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" t="s">
+        <v>761</v>
+      </c>
+      <c r="C14" t="s">
+        <v>768</v>
+      </c>
+      <c r="D14" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15" t="s">
+        <v>761</v>
+      </c>
+      <c r="C15" t="s">
+        <v>770</v>
+      </c>
+      <c r="D15" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s">
+        <v>761</v>
+      </c>
+      <c r="C16" t="s">
+        <v>772</v>
+      </c>
+      <c r="D16" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17" t="s">
+        <v>761</v>
+      </c>
+      <c r="C17" t="s">
+        <v>623</v>
+      </c>
+      <c r="D17" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18" t="s">
+        <v>761</v>
+      </c>
+      <c r="C18" t="s">
+        <v>775</v>
+      </c>
+      <c r="D18" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19" t="s">
+        <v>761</v>
+      </c>
+      <c r="C19" t="s">
+        <v>776</v>
+      </c>
+      <c r="D19" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" t="s">
+        <v>778</v>
+      </c>
+      <c r="B20" t="s">
+        <v>779</v>
+      </c>
+      <c r="C20" t="s">
+        <v>621</v>
+      </c>
+      <c r="D20" t="s">
+        <v>780</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" t="s">
+        <v>778</v>
+      </c>
+      <c r="B21" t="s">
+        <v>779</v>
+      </c>
+      <c r="C21" t="s">
+        <v>622</v>
+      </c>
+      <c r="D21" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" t="s">
+        <v>778</v>
+      </c>
+      <c r="B22" t="s">
+        <v>779</v>
+      </c>
+      <c r="C22" t="s">
+        <v>782</v>
+      </c>
+      <c r="D22" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" t="s">
+        <v>778</v>
+      </c>
+      <c r="B23" t="s">
+        <v>779</v>
+      </c>
+      <c r="C23" t="s">
+        <v>784</v>
+      </c>
+      <c r="D23" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" t="s">
+        <v>778</v>
+      </c>
+      <c r="B24" t="s">
+        <v>779</v>
+      </c>
+      <c r="C24" t="s">
+        <v>785</v>
+      </c>
+      <c r="D24" t="s">
+        <v>771</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" t="s">
+        <v>778</v>
+      </c>
+      <c r="B25" t="s">
+        <v>779</v>
+      </c>
+      <c r="C25" t="s">
+        <v>766</v>
+      </c>
+      <c r="D25" t="s">
+        <v>786</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" t="s">
+        <v>787</v>
+      </c>
+      <c r="B26" t="s">
+        <v>788</v>
+      </c>
+      <c r="C26" t="s">
+        <v>567</v>
+      </c>
+      <c r="D26" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" t="s">
+        <v>787</v>
+      </c>
+      <c r="B27" t="s">
+        <v>788</v>
+      </c>
+      <c r="C27" t="s">
+        <v>568</v>
+      </c>
+      <c r="D27" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" t="s">
+        <v>787</v>
+      </c>
+      <c r="B28" t="s">
+        <v>788</v>
+      </c>
+      <c r="C28" t="s">
+        <v>565</v>
+      </c>
+      <c r="D28" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A29" t="s">
+        <v>787</v>
+      </c>
+      <c r="B29" t="s">
+        <v>788</v>
+      </c>
+      <c r="C29" t="s">
+        <v>792</v>
+      </c>
+      <c r="D29" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A30" t="s">
+        <v>787</v>
+      </c>
+      <c r="B30" t="s">
+        <v>788</v>
+      </c>
+      <c r="C30" t="s">
+        <v>794</v>
+      </c>
+      <c r="D30" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A31" t="s">
+        <v>796</v>
+      </c>
+      <c r="B31" t="s">
+        <v>797</v>
+      </c>
+      <c r="C31" t="s">
+        <v>668</v>
+      </c>
+      <c r="D31" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A32" t="s">
+        <v>796</v>
+      </c>
+      <c r="B32" t="s">
+        <v>797</v>
+      </c>
+      <c r="C32" t="s">
+        <v>799</v>
+      </c>
+      <c r="D32" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A33" t="s">
+        <v>796</v>
+      </c>
+      <c r="B33" t="s">
+        <v>797</v>
+      </c>
+      <c r="C33" t="s">
+        <v>670</v>
+      </c>
+      <c r="D33" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A34" t="s">
+        <v>796</v>
+      </c>
+      <c r="B34" t="s">
+        <v>797</v>
+      </c>
+      <c r="C34" t="s">
+        <v>801</v>
+      </c>
+      <c r="D34" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A35" t="s">
+        <v>796</v>
+      </c>
+      <c r="B35" t="s">
+        <v>797</v>
+      </c>
+      <c r="C35" t="s">
+        <v>802</v>
+      </c>
+      <c r="D35" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A36" t="s">
+        <v>657</v>
+      </c>
+      <c r="B36" t="s">
+        <v>804</v>
+      </c>
+      <c r="C36" t="s">
+        <v>558</v>
+      </c>
+      <c r="D36" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A37" t="s">
+        <v>657</v>
+      </c>
+      <c r="B37" t="s">
+        <v>804</v>
+      </c>
+      <c r="C37" t="s">
+        <v>624</v>
+      </c>
+      <c r="D37" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A38" t="s">
+        <v>657</v>
+      </c>
+      <c r="B38" t="s">
+        <v>804</v>
+      </c>
+      <c r="C38" t="s">
+        <v>807</v>
+      </c>
+      <c r="D38" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A39" t="s">
+        <v>657</v>
+      </c>
+      <c r="B39" t="s">
+        <v>804</v>
+      </c>
+      <c r="C39" t="s">
+        <v>626</v>
+      </c>
+      <c r="D39" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A40" t="s">
+        <v>657</v>
+      </c>
+      <c r="B40" t="s">
+        <v>804</v>
+      </c>
+      <c r="C40" t="s">
+        <v>559</v>
+      </c>
+      <c r="D40" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A41" t="s">
+        <v>811</v>
+      </c>
+      <c r="B41" t="s">
+        <v>812</v>
+      </c>
+      <c r="C41" t="s">
+        <v>813</v>
+      </c>
+      <c r="D41" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A42" t="s">
+        <v>811</v>
+      </c>
+      <c r="B42" t="s">
+        <v>812</v>
+      </c>
+      <c r="C42" t="s">
+        <v>815</v>
+      </c>
+      <c r="D42" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A43" t="s">
+        <v>811</v>
+      </c>
+      <c r="B43" t="s">
+        <v>812</v>
+      </c>
+      <c r="C43" t="s">
+        <v>817</v>
+      </c>
+      <c r="D43" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A44" t="s">
+        <v>811</v>
+      </c>
+      <c r="B44" t="s">
+        <v>812</v>
+      </c>
+      <c r="C44" t="s">
+        <v>818</v>
+      </c>
+      <c r="D44" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A45" t="s">
+        <v>811</v>
+      </c>
+      <c r="B45" t="s">
+        <v>812</v>
+      </c>
+      <c r="C45" t="s">
+        <v>820</v>
+      </c>
+      <c r="D45" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A46" t="s">
+        <v>821</v>
+      </c>
+      <c r="B46" t="s">
+        <v>822</v>
+      </c>
+      <c r="C46" t="s">
+        <v>823</v>
+      </c>
+      <c r="D46" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A47" t="s">
+        <v>821</v>
+      </c>
+      <c r="B47" t="s">
+        <v>822</v>
+      </c>
+      <c r="C47" t="s">
+        <v>825</v>
+      </c>
+      <c r="D47" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A48" t="s">
+        <v>821</v>
+      </c>
+      <c r="B48" t="s">
+        <v>822</v>
+      </c>
+      <c r="C48" t="s">
+        <v>827</v>
+      </c>
+      <c r="D48" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A49" t="s">
+        <v>821</v>
+      </c>
+      <c r="B49" t="s">
+        <v>822</v>
+      </c>
+      <c r="C49" t="s">
+        <v>829</v>
+      </c>
+      <c r="D49" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A50" t="s">
+        <v>821</v>
+      </c>
+      <c r="B50" t="s">
+        <v>822</v>
+      </c>
+      <c r="C50" t="s">
+        <v>830</v>
+      </c>
+      <c r="D50" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A51" t="s">
+        <v>832</v>
+      </c>
+      <c r="B51" t="s">
+        <v>833</v>
+      </c>
+      <c r="C51" t="s">
+        <v>834</v>
+      </c>
+      <c r="D51" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A52" t="s">
+        <v>832</v>
+      </c>
+      <c r="B52" t="s">
+        <v>833</v>
+      </c>
+      <c r="C52" t="s">
+        <v>836</v>
+      </c>
+      <c r="D52" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A53" t="s">
+        <v>832</v>
+      </c>
+      <c r="B53" t="s">
+        <v>833</v>
+      </c>
+      <c r="C53" t="s">
+        <v>837</v>
+      </c>
+      <c r="D53" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A54" t="s">
+        <v>423</v>
+      </c>
+      <c r="B54" t="s">
+        <v>839</v>
+      </c>
+      <c r="C54" t="s">
+        <v>424</v>
+      </c>
+      <c r="D54" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A55" t="s">
+        <v>423</v>
+      </c>
+      <c r="B55" t="s">
+        <v>839</v>
+      </c>
+      <c r="C55" t="s">
+        <v>426</v>
+      </c>
+      <c r="D55" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A56" t="s">
+        <v>423</v>
+      </c>
+      <c r="B56" t="s">
+        <v>839</v>
+      </c>
+      <c r="C56" t="s">
+        <v>425</v>
+      </c>
+      <c r="D56" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A57" t="s">
+        <v>423</v>
+      </c>
+      <c r="B57" t="s">
+        <v>839</v>
+      </c>
+      <c r="C57" t="s">
+        <v>457</v>
+      </c>
+      <c r="D57" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A58" t="s">
+        <v>423</v>
+      </c>
+      <c r="B58" t="s">
+        <v>839</v>
+      </c>
+      <c r="C58" t="s">
+        <v>844</v>
+      </c>
+      <c r="D58" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A59" t="s">
+        <v>846</v>
+      </c>
+      <c r="B59" t="s">
+        <v>847</v>
+      </c>
+      <c r="C59" t="s">
+        <v>499</v>
+      </c>
+      <c r="D59" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A60" t="s">
+        <v>846</v>
+      </c>
+      <c r="B60" t="s">
+        <v>847</v>
+      </c>
+      <c r="C60" t="s">
+        <v>490</v>
+      </c>
+      <c r="D60" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A61" t="s">
+        <v>846</v>
+      </c>
+      <c r="B61" t="s">
+        <v>847</v>
+      </c>
+      <c r="C61" t="s">
+        <v>492</v>
+      </c>
+      <c r="D61" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A62" t="s">
+        <v>846</v>
+      </c>
+      <c r="B62" t="s">
+        <v>847</v>
+      </c>
+      <c r="C62" t="s">
+        <v>500</v>
+      </c>
+      <c r="D62" t="s">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="A63" t="s">
+        <v>846</v>
+      </c>
+      <c r="B63" t="s">
+        <v>847</v>
+      </c>
+      <c r="C63" t="s">
+        <v>498</v>
+      </c>
+      <c r="D63" t="s">
+        <v>852</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/DRUG DISEASE.xlsx
+++ b/DRUG DISEASE.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EDDA733B-D326-492B-A504-31FEF71C3DDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{827C7BED-339F-4CAB-A57C-F6E4C6C3947E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{3244C3E9-4DF0-4247-BD4E-75BB2D6BE0CE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="ALL_DATA" sheetId="1" r:id="rId1"/>
+    <sheet name="CHRONIC_26" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>

--- a/DRUG DISEASE.xlsx
+++ b/DRUG DISEASE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{827C7BED-339F-4CAB-A57C-F6E4C6C3947E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7061F440-D5FA-4D81-8EB0-16003CFDE52C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{3244C3E9-4DF0-4247-BD4E-75BB2D6BE0CE}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{3244C3E9-4DF0-4247-BD4E-75BB2D6BE0CE}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL_DATA" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1912" uniqueCount="853">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2098" uniqueCount="969">
   <si>
     <t>ชื่อยา</t>
   </si>
@@ -2604,12 +2604,360 @@
   <si>
     <t>alkylating agent</t>
   </si>
+  <si>
+    <t>01 โรคเบาหวาน</t>
+  </si>
+  <si>
+    <t>02 โรคความดันโลหิตสูง</t>
+  </si>
+  <si>
+    <t>03A โรคตับอักเสบเรื้อรัง</t>
+  </si>
+  <si>
+    <t>K74</t>
+  </si>
+  <si>
+    <t>03B โรคตับแข็ง</t>
+  </si>
+  <si>
+    <t>04 โรคหัวใจล้มเหลว</t>
+  </si>
+  <si>
+    <t>05 โรคหลอดเลือดสมอง</t>
+  </si>
+  <si>
+    <t>06 โรคมะเร็ง</t>
+  </si>
+  <si>
+    <t>09 โรคไตวายเรื้อรัง</t>
+  </si>
+  <si>
+    <t>10 โรคพาร์กินสัน</t>
+  </si>
+  <si>
+    <t>G70</t>
+  </si>
+  <si>
+    <t>11 Myasthenia Gravis</t>
+  </si>
+  <si>
+    <t>E23</t>
+  </si>
+  <si>
+    <t>12 โรคเบาจืด</t>
+  </si>
+  <si>
+    <t>14 ไขมันในเลือดสูง</t>
+  </si>
+  <si>
+    <t>H40</t>
+  </si>
+  <si>
+    <t>16 ต้อหิน</t>
+  </si>
+  <si>
+    <t>M32</t>
+  </si>
+  <si>
+    <t>D61</t>
+  </si>
+  <si>
+    <t>19 Aplastic anemia</t>
+  </si>
+  <si>
+    <t>acarbose</t>
+  </si>
+  <si>
+    <t>ยับยั้งการดูดซึมน้ำตาลจากลำไส้</t>
+  </si>
+  <si>
+    <t>voglibose</t>
+  </si>
+  <si>
+    <t>ลดระดับน้ำตาลในเลือดหลังรับประทานอาหาร</t>
+  </si>
+  <si>
+    <t>metformin</t>
+  </si>
+  <si>
+    <t>ลดการสร้างน้ำตาลที่ตับและเพิ่มความไวอินซูลิน</t>
+  </si>
+  <si>
+    <t>gliclazide</t>
+  </si>
+  <si>
+    <t>กระตุ้นตับอ่อนให้หลั่งอินซูลิน</t>
+  </si>
+  <si>
+    <t>sitagliptin</t>
+  </si>
+  <si>
+    <t>ยับยั้ง DPP-4 ช่วยควบคุมระดับน้ำตาล</t>
+  </si>
+  <si>
+    <t>dapagliflozin</t>
+  </si>
+  <si>
+    <t>ขับน้ำตาลออกทางปัสสาวะ (SGLT2)</t>
+  </si>
+  <si>
+    <t>insulin</t>
+  </si>
+  <si>
+    <t>ฮอร์โมนทดแทนเพื่อคุมน้ำตาลในเลือด</t>
+  </si>
+  <si>
+    <t>amlodipine</t>
+  </si>
+  <si>
+    <t>ขยายหลอดเลือดแดง ลดความต้านทานส่วนปลาย</t>
+  </si>
+  <si>
+    <t>enalapril</t>
+  </si>
+  <si>
+    <t>ยับยั้ง ACE ลดความดันและป้องกันไตเสื่อม</t>
+  </si>
+  <si>
+    <t>losartan</t>
+  </si>
+  <si>
+    <t>ยับยั้งตัวรับ Angiotensin II ขยายหลอดเลือด</t>
+  </si>
+  <si>
+    <t>atenolol</t>
+  </si>
+  <si>
+    <t>ปิดกั้น Beta-1 ลดอัตราการเต้นหัวใจ</t>
+  </si>
+  <si>
+    <t>propranolol</t>
+  </si>
+  <si>
+    <t>ปิดกั้น Beta-receptors ลดความตื่นตัวหัวใจ</t>
+  </si>
+  <si>
+    <t>hydrochlorothiazide</t>
+  </si>
+  <si>
+    <t>ยาขับปัสสาวะกลุ่ม Thiazide ลดความดัน</t>
+  </si>
+  <si>
+    <t>interferon α</t>
+  </si>
+  <si>
+    <t>กระตุ้นภูมิคุ้มกันต่อต้านไวรัสตับอักเสบ</t>
+  </si>
+  <si>
+    <t>tenofovir</t>
+  </si>
+  <si>
+    <t>ยับยั้งการจำลองตัวของไวรัสตับอักเสบบี</t>
+  </si>
+  <si>
+    <t>entecavir</t>
+  </si>
+  <si>
+    <t>ยาต้านไวรัสรักษาตับอักเสบบีเรื้อรัง</t>
+  </si>
+  <si>
+    <t>sofosbuvir</t>
+  </si>
+  <si>
+    <t>ยาต้านไวรัสออกฤทธิ์โดยตรง (DAA) รักษาตับซี</t>
+  </si>
+  <si>
+    <t>spironolactone</t>
+  </si>
+  <si>
+    <t>ยาขับปัสสาวะชนิดรักษาโพแทสเซียม ลดท้องมาน</t>
+  </si>
+  <si>
+    <t>lactulose</t>
+  </si>
+  <si>
+    <t>ยาระบายลดการดูดซึมแอมโมเนียในกระแสเลือด</t>
+  </si>
+  <si>
+    <t>furosemide</t>
+  </si>
+  <si>
+    <t>ยาขับปัสสาวะออกฤทธิ์แรง ลดอาการบวม</t>
+  </si>
+  <si>
+    <t>digoxin</t>
+  </si>
+  <si>
+    <t>ช่วยเพิ่มแรงบีบและคุมจังหวะหัวใจ</t>
+  </si>
+  <si>
+    <t>sacubitril</t>
+  </si>
+  <si>
+    <t>ยาผสมกลุ่ม ARNI ลดภาระการทำงานของหัวใจ</t>
+  </si>
+  <si>
+    <t>ISMO</t>
+  </si>
+  <si>
+    <t>ขยายหลอดเลือดดำและแดง ป้องกันแน่นหน้าอก</t>
+  </si>
+  <si>
+    <t>05 หลอดเลือดสมอง</t>
+  </si>
+  <si>
+    <t>ASA (Aspirin)</t>
+  </si>
+  <si>
+    <t>ต้านเกล็ดเลือด ป้องกันอัมพาตจากลิ่มเลือด</t>
+  </si>
+  <si>
+    <t>warfarin</t>
+  </si>
+  <si>
+    <t>ต้านการแข็งตัวของเลือด (ต้องตรวจ INR)</t>
+  </si>
+  <si>
+    <t>clopidogrel</t>
+  </si>
+  <si>
+    <t>ป้องกันการเกิดลิ่มเลือดอุดตันในหลอดเลือด</t>
+  </si>
+  <si>
+    <t>cisplatin</t>
+  </si>
+  <si>
+    <t>ยาเคมีบำบัดรบกวนการจำลองตัวของ DNA</t>
+  </si>
+  <si>
+    <t>cyclophosphamide</t>
+  </si>
+  <si>
+    <t>ยากดภูมิคุ้มกันและยาเคมีบำบัด</t>
+  </si>
+  <si>
+    <t>methotrexate</t>
+  </si>
+  <si>
+    <t>ยายับยั้งการเจริญเติบโตของเซลล์มะเร็ง</t>
+  </si>
+  <si>
+    <t>07 HIV/AIDS</t>
+  </si>
+  <si>
+    <t>ยาต้านไวรัสกลุ่ม NRTI สำหรับ HIV</t>
+  </si>
+  <si>
+    <t>07 โรคภูมิคุ้มกันบกพร่อง</t>
+  </si>
+  <si>
+    <t>efavirenz</t>
+  </si>
+  <si>
+    <t>ยาต้านไวรัสกลุ่ม NNRTI</t>
+  </si>
+  <si>
+    <t>ritonavir</t>
+  </si>
+  <si>
+    <t>ยาช่วยเสริมระดับยาต้านไวรัสตัวอื่น</t>
+  </si>
+  <si>
+    <t>salbutamol</t>
+  </si>
+  <si>
+    <t>ยาพ่นขยายหลอดลมออกฤทธิ์เร็วเมื่อมีอาการ</t>
+  </si>
+  <si>
+    <t>08 โรคถุงลมโป่งพอง</t>
+  </si>
+  <si>
+    <t>theophylline</t>
+  </si>
+  <si>
+    <t>ยาขยายหลอดลมชนิดเม็ด</t>
+  </si>
+  <si>
+    <t>calcitriol</t>
+  </si>
+  <si>
+    <t>วิตามินดีที่ออกฤทธิ์ทันที ป้องกันกระดูกพรุน</t>
+  </si>
+  <si>
+    <t>ferrous sulfate</t>
+  </si>
+  <si>
+    <t>ยาบำรุงเลือด รักษาภาวะซีดจากโรคไต</t>
+  </si>
+  <si>
+    <t>levodopa</t>
+  </si>
+  <si>
+    <t>สารตั้งต้นของโดปามีน ลดอาการสั่นและเกร็ง</t>
+  </si>
+  <si>
+    <t>trihexyphenidyl</t>
+  </si>
+  <si>
+    <t>ลดอาการเกร็งและการหลั่งน้ำลายมากผิดปกติ</t>
+  </si>
+  <si>
+    <t>pyridostigmine</t>
+  </si>
+  <si>
+    <t>เพิ่มการส่งสัญญาณประสาทสู่กล้ามเนื้อ</t>
+  </si>
+  <si>
+    <t>prednisolone</t>
+  </si>
+  <si>
+    <t>ยาสเตียรอยด์ลดการอักเสบและกดภูมิคุ้มกัน</t>
+  </si>
+  <si>
+    <t>desmopressin</t>
+  </si>
+  <si>
+    <t>ควบคุมปริมาณน้ำและปัสสาวะ</t>
+  </si>
+  <si>
+    <t>atorvastatin</t>
+  </si>
+  <si>
+    <t>ยาลดคอเลสเตอรอลในเลือด</t>
+  </si>
+  <si>
+    <t>gemfibrozil</t>
+  </si>
+  <si>
+    <t>ยาลดไตรกลีเซอไรด์ในเลือด</t>
+  </si>
+  <si>
+    <t>hydroxychloroquine</t>
+  </si>
+  <si>
+    <t>ลดการอักเสบในโรค SLE และรูมาตอยด์</t>
+  </si>
+  <si>
+    <t>15, 18 รูมาตอยด์/SLE</t>
+  </si>
+  <si>
+    <t>timolol</t>
+  </si>
+  <si>
+    <t>ยาหยอดตาเพื่อลดความดันในลูกตา</t>
+  </si>
+  <si>
+    <t>ciclosporine</t>
+  </si>
+  <si>
+    <t>ยากดภูมิคุ้มกันป้องกันไขกระดูกทำงานผิดปกติ</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="16"/>
       <color theme="1"/>
@@ -2630,6 +2978,19 @@
       <name val="BrowalliaUPC"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2639,7 +3000,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -2647,11 +3008,26 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2660,6 +3036,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
@@ -9309,7 +9691,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C664218-0DFD-4B9B-898E-4542568909C9}">
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D111"/>
   <sheetFormatPr defaultRowHeight="22.8" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="23.3984375" customWidth="1"/>
@@ -10183,7 +10565,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.55000000000000004">
+    <row r="63" spans="1:4" ht="23.4" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A63" t="s">
         <v>846</v>
       </c>
@@ -10195,6 +10577,664 @@
       </c>
       <c r="D63" t="s">
         <v>852</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" ht="55.8" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A64" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>873</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A65" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>875</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A66" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>877</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" ht="55.8" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A67" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>880</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A68" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>881</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" ht="55.8" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A69" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>883</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A70" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>885</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A71" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>854</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>887</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A72" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>854</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>889</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A73" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>854</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>891</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A74" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>854</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>893</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>894</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A75" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>854</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>895</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A76" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>854</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>897</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A77" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>899</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A78" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>901</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A79" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>903</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A80" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>905</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A81" s="4" t="s">
+        <v>856</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>857</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>907</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A82" s="4" t="s">
+        <v>856</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>857</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>909</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A83" s="4" t="s">
+        <v>856</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>857</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="D83" s="4" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A84" s="4" t="s">
+        <v>778</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>858</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>913</v>
+      </c>
+      <c r="D84" s="4" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A85" s="4" t="s">
+        <v>778</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>858</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>915</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" ht="97.2" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A86" s="4" t="s">
+        <v>778</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>858</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>917</v>
+      </c>
+      <c r="D86" s="4" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A87" s="4"/>
+      <c r="B87" s="4"/>
+      <c r="C87" s="5" t="s">
+        <v>919</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A88" s="4" t="s">
+        <v>787</v>
+      </c>
+      <c r="B88" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>920</v>
+      </c>
+      <c r="D88" s="4" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A89" s="4" t="s">
+        <v>787</v>
+      </c>
+      <c r="B89" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>922</v>
+      </c>
+      <c r="D89" s="4" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A90" s="4" t="s">
+        <v>787</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>859</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>924</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" ht="55.8" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A91" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>860</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>926</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A92" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>860</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>928</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A93" s="4" t="s">
+        <v>846</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>860</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A94" s="4"/>
+      <c r="B94" s="4"/>
+      <c r="C94" s="5" t="s">
+        <v>932</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A95" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>934</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>901</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A96" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>934</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>935</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A97" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>934</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>937</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A98" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>941</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>939</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A99" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>941</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>942</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A100" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="B100" s="4" t="s">
+        <v>861</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>944</v>
+      </c>
+      <c r="D100" s="4" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A101" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="B101" s="4" t="s">
+        <v>861</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>946</v>
+      </c>
+      <c r="D101" s="4" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A102" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>862</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>948</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A103" s="4" t="s">
+        <v>821</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>862</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>950</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" ht="55.8" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A104" s="4" t="s">
+        <v>863</v>
+      </c>
+      <c r="B104" s="4" t="s">
+        <v>864</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>952</v>
+      </c>
+      <c r="D104" s="4" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" ht="55.8" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A105" s="4" t="s">
+        <v>863</v>
+      </c>
+      <c r="B105" s="4" t="s">
+        <v>864</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="D105" s="4" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="55.8" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A106" s="4" t="s">
+        <v>865</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>866</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A107" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>867</v>
+      </c>
+      <c r="C107" s="4" t="s">
+        <v>958</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="55.8" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A108" s="4" t="s">
+        <v>811</v>
+      </c>
+      <c r="B108" s="4" t="s">
+        <v>867</v>
+      </c>
+      <c r="C108" s="4" t="s">
+        <v>960</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A109" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="B109" s="4" t="s">
+        <v>964</v>
+      </c>
+      <c r="C109" s="4" t="s">
+        <v>962</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" ht="23.4" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A110" s="4" t="s">
+        <v>868</v>
+      </c>
+      <c r="B110" s="4" t="s">
+        <v>869</v>
+      </c>
+      <c r="C110" s="4" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A111" s="4" t="s">
+        <v>871</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>872</v>
+      </c>
+      <c r="C111" s="4" t="s">
+        <v>967</v>
       </c>
     </row>
   </sheetData>

--- a/DRUG DISEASE.xlsx
+++ b/DRUG DISEASE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7061F440-D5FA-4D81-8EB0-16003CFDE52C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E8468130-11D5-4796-B686-83F79BB008CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" activeTab="1" xr2:uid="{3244C3E9-4DF0-4247-BD4E-75BB2D6BE0CE}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2098" uniqueCount="969">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2090" uniqueCount="961">
   <si>
     <t>ชื่อยา</t>
   </si>
@@ -2650,21 +2650,9 @@
     <t>14 ไขมันในเลือดสูง</t>
   </si>
   <si>
-    <t>H40</t>
-  </si>
-  <si>
-    <t>16 ต้อหิน</t>
-  </si>
-  <si>
     <t>M32</t>
   </si>
   <si>
-    <t>D61</t>
-  </si>
-  <si>
-    <t>19 Aplastic anemia</t>
-  </si>
-  <si>
     <t>acarbose</t>
   </si>
   <si>
@@ -2842,9 +2830,6 @@
     <t>ยายับยั้งการเจริญเติบโตของเซลล์มะเร็ง</t>
   </si>
   <si>
-    <t>07 HIV/AIDS</t>
-  </si>
-  <si>
     <t>ยาต้านไวรัสกลุ่ม NRTI สำหรับ HIV</t>
   </si>
   <si>
@@ -2854,9 +2839,6 @@
     <t>efavirenz</t>
   </si>
   <si>
-    <t>ยาต้านไวรัสกลุ่ม NNRTI</t>
-  </si>
-  <si>
     <t>ritonavir</t>
   </si>
   <si>
@@ -2941,13 +2923,7 @@
     <t>15, 18 รูมาตอยด์/SLE</t>
   </si>
   <si>
-    <t>timolol</t>
-  </si>
-  <si>
     <t>ยาหยอดตาเพื่อลดความดันในลูกตา</t>
-  </si>
-  <si>
-    <t>ciclosporine</t>
   </si>
   <si>
     <t>ยากดภูมิคุ้มกันป้องกันไขกระดูกทำงานผิดปกติ</t>
@@ -9691,7 +9667,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C664218-0DFD-4B9B-898E-4542568909C9}">
-  <dimension ref="A1:D111"/>
+  <dimension ref="A1:D108"/>
   <sheetFormatPr defaultRowHeight="22.8" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="2" max="2" width="23.3984375" customWidth="1"/>
@@ -10587,10 +10563,10 @@
         <v>853</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>873</v>
+        <v>869</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
@@ -10601,10 +10577,10 @@
         <v>853</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
@@ -10615,10 +10591,10 @@
         <v>853</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="55.8" thickBot="1" x14ac:dyDescent="0.6">
@@ -10629,10 +10605,10 @@
         <v>853</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>879</v>
+        <v>875</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>880</v>
+        <v>876</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
@@ -10643,10 +10619,10 @@
         <v>853</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>881</v>
+        <v>877</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="55.8" thickBot="1" x14ac:dyDescent="0.6">
@@ -10657,10 +10633,10 @@
         <v>853</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
@@ -10671,10 +10647,10 @@
         <v>853</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>885</v>
+        <v>881</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
@@ -10685,10 +10661,10 @@
         <v>854</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
@@ -10699,10 +10675,10 @@
         <v>854</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
@@ -10713,10 +10689,10 @@
         <v>854</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
@@ -10727,10 +10703,10 @@
         <v>854</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
@@ -10741,10 +10717,10 @@
         <v>854</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>895</v>
+        <v>891</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>896</v>
+        <v>892</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
@@ -10755,10 +10731,10 @@
         <v>854</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>898</v>
+        <v>894</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
@@ -10769,10 +10745,10 @@
         <v>855</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>899</v>
+        <v>895</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>900</v>
+        <v>896</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
@@ -10783,10 +10759,10 @@
         <v>855</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>901</v>
+        <v>897</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>902</v>
+        <v>898</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
@@ -10797,10 +10773,10 @@
         <v>855</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>903</v>
+        <v>899</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>904</v>
+        <v>900</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
@@ -10811,10 +10787,10 @@
         <v>855</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>905</v>
+        <v>901</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>906</v>
+        <v>902</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
@@ -10825,10 +10801,10 @@
         <v>857</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>908</v>
+        <v>904</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
@@ -10839,10 +10815,10 @@
         <v>857</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>909</v>
+        <v>905</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>910</v>
+        <v>906</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
@@ -10853,10 +10829,10 @@
         <v>857</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>911</v>
+        <v>907</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>912</v>
+        <v>908</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
@@ -10867,10 +10843,10 @@
         <v>858</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>913</v>
+        <v>909</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>914</v>
+        <v>910</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
@@ -10881,10 +10857,10 @@
         <v>858</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>915</v>
+        <v>911</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>916</v>
+        <v>912</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="97.2" thickBot="1" x14ac:dyDescent="0.6">
@@ -10895,20 +10871,20 @@
         <v>858</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>918</v>
+        <v>914</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A87" s="4"/>
       <c r="B87" s="4"/>
       <c r="C87" s="5" t="s">
-        <v>919</v>
+        <v>915</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
@@ -10919,10 +10895,10 @@
         <v>859</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>920</v>
+        <v>916</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>923</v>
+        <v>919</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
@@ -10933,10 +10909,10 @@
         <v>859</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>922</v>
+        <v>918</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>925</v>
+        <v>921</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
@@ -10947,10 +10923,10 @@
         <v>859</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>924</v>
+        <v>920</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>927</v>
+        <v>923</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="55.8" thickBot="1" x14ac:dyDescent="0.6">
@@ -10961,10 +10937,10 @@
         <v>860</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>926</v>
+        <v>922</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>929</v>
+        <v>925</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
@@ -10975,10 +10951,10 @@
         <v>860</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>928</v>
+        <v>924</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>931</v>
+        <v>927</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
@@ -10989,93 +10965,97 @@
         <v>860</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>930</v>
+        <v>926</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A94" s="4"/>
-      <c r="B94" s="4"/>
-      <c r="C94" s="5" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A94" s="4" t="s">
+        <v>423</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>929</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>897</v>
+      </c>
+      <c r="D94" s="4" t="s">
         <v>932</v>
       </c>
-      <c r="D94" s="4" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="95" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A95" s="4" t="s">
         <v>423</v>
       </c>
       <c r="B95" s="4" t="s">
+        <v>929</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>930</v>
+      </c>
+      <c r="D95" s="4" t="s">
         <v>934</v>
       </c>
-      <c r="C95" s="4" t="s">
-        <v>901</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
+    </row>
+    <row r="96" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A96" s="4" t="s">
         <v>423</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>934</v>
+        <v>929</v>
       </c>
       <c r="C96" s="4" t="s">
+        <v>931</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A97" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="B97" s="4" t="s">
         <v>935</v>
       </c>
-      <c r="D96" s="4" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4" ht="42" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A97" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="B97" s="4" t="s">
-        <v>934</v>
-      </c>
       <c r="C97" s="4" t="s">
-        <v>937</v>
+        <v>933</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A98" s="4" t="s">
         <v>796</v>
       </c>
       <c r="B98" s="4" t="s">
+        <v>935</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>936</v>
+      </c>
+      <c r="D98" s="4" t="s">
         <v>941</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>939</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>945</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A99" s="4" t="s">
-        <v>796</v>
+        <v>657</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>941</v>
+        <v>861</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>942</v>
+        <v>938</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A100" s="4" t="s">
         <v>657</v>
       </c>
@@ -11083,27 +11063,27 @@
         <v>861</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>944</v>
+        <v>940</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A101" s="4" t="s">
-        <v>657</v>
+        <v>821</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>946</v>
+        <v>942</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A102" s="4" t="s">
         <v>821</v>
       </c>
@@ -11111,24 +11091,24 @@
         <v>862</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>948</v>
+        <v>944</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" ht="55.8" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A103" s="4" t="s">
-        <v>821</v>
+        <v>863</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>862</v>
+        <v>864</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>950</v>
+        <v>946</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>955</v>
+        <v>951</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="55.8" thickBot="1" x14ac:dyDescent="0.6">
@@ -11139,41 +11119,41 @@
         <v>864</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>952</v>
+        <v>948</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>957</v>
+        <v>953</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="55.8" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A105" s="4" t="s">
-        <v>863</v>
+        <v>865</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>864</v>
+        <v>866</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>954</v>
+        <v>950</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4" ht="55.8" thickBot="1" x14ac:dyDescent="0.6">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A106" s="4" t="s">
-        <v>865</v>
+        <v>811</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>956</v>
+        <v>952</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4" ht="69.599999999999994" thickBot="1" x14ac:dyDescent="0.6">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" ht="55.8" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A107" s="4" t="s">
         <v>811</v>
       </c>
@@ -11181,60 +11161,24 @@
         <v>867</v>
       </c>
       <c r="C107" s="4" t="s">
+        <v>954</v>
+      </c>
+      <c r="D107" s="4" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
+      <c r="A108" s="4" t="s">
+        <v>868</v>
+      </c>
+      <c r="B108" s="4" t="s">
         <v>958</v>
       </c>
-      <c r="D107" s="4" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4" ht="55.8" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A108" s="4" t="s">
-        <v>811</v>
-      </c>
-      <c r="B108" s="4" t="s">
-        <v>867</v>
-      </c>
       <c r="C108" s="4" t="s">
+        <v>956</v>
+      </c>
+      <c r="D108" s="4" t="s">
         <v>960</v>
-      </c>
-      <c r="D108" s="4" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4" ht="83.4" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A109" s="4" t="s">
-        <v>870</v>
-      </c>
-      <c r="B109" s="4" t="s">
-        <v>964</v>
-      </c>
-      <c r="C109" s="4" t="s">
-        <v>962</v>
-      </c>
-      <c r="D109" s="4" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4" ht="23.4" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A110" s="4" t="s">
-        <v>868</v>
-      </c>
-      <c r="B110" s="4" t="s">
-        <v>869</v>
-      </c>
-      <c r="C110" s="4" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4" ht="28.2" thickBot="1" x14ac:dyDescent="0.6">
-      <c r="A111" s="4" t="s">
-        <v>871</v>
-      </c>
-      <c r="B111" s="4" t="s">
-        <v>872</v>
-      </c>
-      <c r="C111" s="4" t="s">
-        <v>967</v>
       </c>
     </row>
   </sheetData>

--- a/DRUG DISEASE.xlsx
+++ b/DRUG DISEASE.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IT Room\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1FB26712-E751-4382-8776-3E71684D4879}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C1C9E7C-8D09-4FC2-B022-7F9057148C9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11895" yWindow="0" windowWidth="12180" windowHeight="12885" activeTab="1" xr2:uid="{3244C3E9-4DF0-4247-BD4E-75BB2D6BE0CE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" activeTab="1" xr2:uid="{3244C3E9-4DF0-4247-BD4E-75BB2D6BE0CE}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL_DATA" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3136" uniqueCount="1335">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3136" uniqueCount="1329">
   <si>
     <t>ชื่อยา</t>
   </si>
@@ -2502,9 +2502,6 @@
     <t>I10,I11,I12,I13,I15</t>
   </si>
   <si>
-    <t>I10, I11,I12,I13,I15</t>
-  </si>
-  <si>
     <t>Esmolol</t>
   </si>
   <si>
@@ -2605,21 +2602,6 @@
   </si>
   <si>
     <t>(ขยายหลอดเลือดแดงโดยตรง) </t>
-  </si>
-  <si>
-    <t>I10, I11,I12,I13,I16</t>
-  </si>
-  <si>
-    <t>I10, I11,I12,I13,I17</t>
-  </si>
-  <si>
-    <t>I10, I11,I12,I13,I18</t>
-  </si>
-  <si>
-    <t>I10, I11,I12,I13,I19</t>
-  </si>
-  <si>
-    <t>I10, I11,I12,I13,I20</t>
   </si>
   <si>
     <t>B18.0,B18.1,B18.2,B18.8/B18.9</t>
@@ -11329,7 +11311,7 @@
   <sheetData>
     <row r="1" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
-        <v>1155</v>
+        <v>1149</v>
       </c>
       <c r="B1" t="s">
         <v>740</v>
@@ -11744,7 +11726,7 @@
         <v>756</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="31" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -11758,7 +11740,7 @@
         <v>755</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -11772,26 +11754,26 @@
         <v>761</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="33" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B33" s="7" t="s">
         <v>810</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B34" s="7" t="s">
         <v>810</v>
@@ -11800,40 +11782,40 @@
         <v>762</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B35" s="7" t="s">
         <v>810</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
     </row>
     <row r="36" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B36" s="7" t="s">
         <v>810</v>
       </c>
       <c r="C36" s="4" t="s">
+        <v>817</v>
+      </c>
+      <c r="D36" s="4" t="s">
         <v>818</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>819</v>
       </c>
     </row>
     <row r="37" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B37" s="7" t="s">
         <v>810</v>
@@ -11842,138 +11824,138 @@
         <v>751</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="38" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B38" s="7" t="s">
         <v>810</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="39" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>810</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
     </row>
     <row r="40" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B40" s="7" t="s">
         <v>810</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B41" s="7" t="s">
         <v>810</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B42" s="7" t="s">
         <v>810</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="43" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B43" s="7" t="s">
         <v>810</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B44" s="7" t="s">
         <v>810</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B45" s="7" t="s">
         <v>810</v>
       </c>
       <c r="C45" s="8" t="s">
+        <v>826</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>827</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>828</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B46" s="7" t="s">
         <v>810</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>810</v>
@@ -11982,12 +11964,12 @@
         <v>753</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B48" s="7" t="s">
         <v>810</v>
@@ -11996,82 +11978,82 @@
         <v>754</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="49" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B49" s="7" t="s">
         <v>810</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="50" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B50" s="7" t="s">
         <v>810</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B51" s="7" t="s">
         <v>810</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B52" s="7" t="s">
         <v>810</v>
       </c>
       <c r="C52" s="4" t="s">
+        <v>833</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>834</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>835</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B53" s="7" t="s">
         <v>810</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B54" s="7" t="s">
         <v>810</v>
@@ -12080,26 +12062,26 @@
         <v>752</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B55" s="7" t="s">
         <v>810</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>810</v>
@@ -12108,12 +12090,12 @@
         <v>758</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B57" s="7" t="s">
         <v>810</v>
@@ -12122,413 +12104,413 @@
         <v>757</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B58" s="7" t="s">
         <v>810</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B59" s="7" t="s">
         <v>810</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B60" s="7" t="s">
         <v>810</v>
       </c>
       <c r="C60" s="4" t="s">
+        <v>839</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>840</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>841</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" t="s">
-        <v>850</v>
+        <v>814</v>
       </c>
       <c r="B61" s="7" t="s">
         <v>810</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="D61" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" t="s">
-        <v>851</v>
+        <v>814</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>810</v>
       </c>
       <c r="C62" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="D62" t="s">
         <v>844</v>
-      </c>
-      <c r="D62" t="s">
-        <v>845</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" t="s">
-        <v>852</v>
+        <v>814</v>
       </c>
       <c r="B63" s="7" t="s">
         <v>810</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>853</v>
+        <v>814</v>
       </c>
       <c r="B64" s="7" t="s">
         <v>810</v>
       </c>
       <c r="C64" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>846</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>847</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>854</v>
+        <v>814</v>
       </c>
       <c r="B65" s="7" t="s">
         <v>810</v>
       </c>
       <c r="C65" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="D65" s="4" t="s">
         <v>848</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>849</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="6" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="6" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="6" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="C68" s="10" t="s">
         <v>425</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="6" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="6" t="s">
+        <v>849</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="C70" s="6" t="s">
         <v>855</v>
       </c>
-      <c r="B70" s="4" t="s">
-        <v>856</v>
-      </c>
-      <c r="C70" s="6" t="s">
-        <v>861</v>
-      </c>
       <c r="D70" s="4" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="6" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="B71" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="C71" s="6" t="s">
         <v>856</v>
       </c>
-      <c r="C71" s="6" t="s">
-        <v>862</v>
-      </c>
       <c r="D71" s="4" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="6" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="6" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="6" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="C74" s="6" t="s">
         <v>455</v>
       </c>
       <c r="D74" s="5" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="6" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="D75" s="5" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="6" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
       <c r="D76" s="5" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="6" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
       <c r="D77" s="5" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="6" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="D78" s="5" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="6" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>873</v>
+        <v>867</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="6" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="D80" s="5" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
     </row>
     <row r="81" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="6" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
       <c r="C81" s="6" t="s">
         <v>622</v>
       </c>
       <c r="D81" s="11" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
     </row>
     <row r="82" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="6" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>879</v>
+        <v>873</v>
       </c>
       <c r="D82" s="12" t="s">
-        <v>880</v>
+        <v>874</v>
       </c>
     </row>
     <row r="83" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="6" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="B83" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="C83" s="6" t="s">
         <v>876</v>
       </c>
-      <c r="C83" s="6" t="s">
-        <v>882</v>
-      </c>
       <c r="D83" s="11" t="s">
-        <v>881</v>
+        <v>875</v>
       </c>
     </row>
     <row r="84" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="6" t="s">
+        <v>871</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="C84" s="6" t="s">
         <v>877</v>
       </c>
-      <c r="B84" s="4" t="s">
-        <v>876</v>
-      </c>
-      <c r="C84" s="6" t="s">
-        <v>883</v>
-      </c>
       <c r="D84" s="12" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
     </row>
     <row r="85" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="6" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>884</v>
+        <v>878</v>
       </c>
       <c r="D85" s="12" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
     </row>
     <row r="86" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="6" t="s">
-        <v>877</v>
+        <v>871</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
       <c r="D86" s="11" t="s">
-        <v>888</v>
+        <v>882</v>
       </c>
     </row>
     <row r="87" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -12536,13 +12518,13 @@
         <v>759</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
     </row>
     <row r="88" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -12550,13 +12532,13 @@
         <v>759</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
     </row>
     <row r="89" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -12564,13 +12546,13 @@
         <v>759</v>
       </c>
       <c r="B89" s="4" t="s">
+        <v>883</v>
+      </c>
+      <c r="C89" s="6" t="s">
+        <v>886</v>
+      </c>
+      <c r="D89" s="13" t="s">
         <v>889</v>
-      </c>
-      <c r="C89" s="6" t="s">
-        <v>892</v>
-      </c>
-      <c r="D89" s="13" t="s">
-        <v>895</v>
       </c>
     </row>
     <row r="90" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -12578,13 +12560,13 @@
         <v>759</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="D90" s="13" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
     </row>
     <row r="91" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -12592,13 +12574,13 @@
         <v>759</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="C91" s="6" t="s">
         <v>753</v>
       </c>
       <c r="D91" s="5" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
     </row>
     <row r="92" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -12606,13 +12588,13 @@
         <v>759</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="C92" s="6" t="s">
         <v>754</v>
       </c>
       <c r="D92" s="5" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
     </row>
     <row r="93" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -12620,13 +12602,13 @@
         <v>759</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="D93" s="5" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
     </row>
     <row r="94" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -12634,13 +12616,13 @@
         <v>759</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D94" s="5" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
     </row>
     <row r="95" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -12648,13 +12630,13 @@
         <v>759</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="C95" s="6" t="s">
         <v>761</v>
       </c>
       <c r="D95" s="5" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
     </row>
     <row r="96" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -12662,13 +12644,13 @@
         <v>759</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="C96" s="6" t="s">
         <v>762</v>
       </c>
       <c r="D96" s="5" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
     </row>
     <row r="97" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -12676,13 +12658,13 @@
         <v>759</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="C97" s="6" t="s">
         <v>756</v>
       </c>
       <c r="D97" s="5" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
     </row>
     <row r="98" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -12690,13 +12672,13 @@
         <v>759</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
       <c r="D98" s="5" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
     </row>
     <row r="99" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -12704,839 +12686,839 @@
         <v>759</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="C99" s="6" t="s">
         <v>760</v>
       </c>
       <c r="D99" s="13" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
     </row>
     <row r="100" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="6" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="C100" s="6" t="s">
         <v>565</v>
       </c>
       <c r="D100" s="11" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
     </row>
     <row r="101" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="6" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="C101" s="6" t="s">
         <v>763</v>
       </c>
       <c r="D101" s="11" t="s">
-        <v>908</v>
+        <v>902</v>
       </c>
     </row>
     <row r="102" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="6" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="C102" s="6" t="s">
         <v>764</v>
       </c>
       <c r="D102" s="11" t="s">
-        <v>908</v>
+        <v>902</v>
       </c>
     </row>
     <row r="103" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="6" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
       <c r="B103" s="4" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>907</v>
+        <v>901</v>
       </c>
       <c r="D103" s="11" t="s">
-        <v>908</v>
+        <v>902</v>
       </c>
     </row>
     <row r="104" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="6" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>909</v>
+        <v>903</v>
       </c>
       <c r="D104" s="11" t="s">
-        <v>912</v>
+        <v>906</v>
       </c>
     </row>
     <row r="105" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="6" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
       <c r="B105" s="4" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="C105" s="6" t="s">
         <v>568</v>
       </c>
       <c r="D105" s="11" t="s">
-        <v>913</v>
+        <v>907</v>
       </c>
     </row>
     <row r="106" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="6" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
       <c r="B106" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="C106" s="6" t="s">
         <v>904</v>
       </c>
-      <c r="C106" s="6" t="s">
-        <v>910</v>
-      </c>
       <c r="D106" s="11" t="s">
-        <v>914</v>
+        <v>908</v>
       </c>
     </row>
     <row r="107" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="6" t="s">
+        <v>899</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>898</v>
+      </c>
+      <c r="C107" s="6" t="s">
         <v>905</v>
       </c>
-      <c r="B107" s="4" t="s">
-        <v>904</v>
-      </c>
-      <c r="C107" s="6" t="s">
-        <v>911</v>
-      </c>
       <c r="D107" s="11" t="s">
-        <v>915</v>
+        <v>909</v>
       </c>
     </row>
     <row r="108" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>918</v>
+        <v>912</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>928</v>
+        <v>922</v>
       </c>
     </row>
     <row r="109" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>919</v>
+        <v>913</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>929</v>
+        <v>923</v>
       </c>
     </row>
     <row r="110" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>930</v>
+        <v>924</v>
       </c>
     </row>
     <row r="111" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B111" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>921</v>
+        <v>915</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>931</v>
+        <v>925</v>
       </c>
     </row>
     <row r="112" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B112" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C112" s="6" t="s">
         <v>528</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
     </row>
     <row r="113" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A113" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B113" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C113" s="6" t="s">
         <v>529</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>932</v>
+        <v>926</v>
       </c>
     </row>
     <row r="114" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A114" s="6" t="s">
+        <v>910</v>
+      </c>
+      <c r="B114" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="C114" s="6" t="s">
         <v>916</v>
       </c>
-      <c r="B114" s="4" t="s">
-        <v>917</v>
-      </c>
-      <c r="C114" s="6" t="s">
-        <v>922</v>
-      </c>
       <c r="D114" s="6" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
     </row>
     <row r="115" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A115" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B115" s="4" t="s">
+        <v>911</v>
+      </c>
+      <c r="C115" s="6" t="s">
         <v>917</v>
       </c>
-      <c r="C115" s="6" t="s">
-        <v>923</v>
-      </c>
       <c r="D115" s="6" t="s">
-        <v>933</v>
+        <v>927</v>
       </c>
     </row>
     <row r="116" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>924</v>
+        <v>918</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
     </row>
     <row r="117" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C117" s="6" t="s">
         <v>520</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
     </row>
     <row r="118" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C118" s="6" t="s">
         <v>519</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>934</v>
+        <v>928</v>
       </c>
     </row>
     <row r="119" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A119" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B119" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>925</v>
+        <v>919</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>935</v>
+        <v>929</v>
       </c>
     </row>
     <row r="120" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A120" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>926</v>
+        <v>920</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
     </row>
     <row r="121" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A121" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C121" s="6" t="s">
         <v>501</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>936</v>
+        <v>930</v>
       </c>
     </row>
     <row r="122" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A122" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B122" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>927</v>
+        <v>921</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
     </row>
     <row r="123" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A123" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B123" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C123" s="6" t="s">
         <v>510</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
     </row>
     <row r="124" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A124" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B124" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C124" s="6" t="s">
         <v>511</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>937</v>
+        <v>931</v>
       </c>
     </row>
     <row r="125" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A125" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>938</v>
+        <v>932</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>942</v>
+        <v>936</v>
       </c>
     </row>
     <row r="126" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A126" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B126" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>939</v>
+        <v>933</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
     </row>
     <row r="127" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A127" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B127" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C127" s="6" t="s">
         <v>493</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
     </row>
     <row r="128" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A128" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B128" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C128" s="6" t="s">
         <v>492</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>943</v>
+        <v>937</v>
       </c>
     </row>
     <row r="129" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A129" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B129" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C129" s="6" t="s">
         <v>491</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
     </row>
     <row r="130" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A130" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B130" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C130" s="6" t="s">
         <v>490</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
     </row>
     <row r="131" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A131" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B131" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C131" s="6" t="s">
         <v>517</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>944</v>
+        <v>938</v>
       </c>
     </row>
     <row r="132" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A132" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B132" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C132" s="6" t="s">
         <v>498</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
     </row>
     <row r="133" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A133" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B133" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C133" s="6" t="s">
         <v>499</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>945</v>
+        <v>939</v>
       </c>
     </row>
     <row r="134" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A134" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B134" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C134" s="6" t="s">
+        <v>934</v>
+      </c>
+      <c r="D134" s="6" t="s">
         <v>940</v>
-      </c>
-      <c r="D134" s="6" t="s">
-        <v>946</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A135" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C135" s="6" t="s">
         <v>514</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
     </row>
     <row r="136" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A136" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C136" s="6" t="s">
         <v>513</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>947</v>
+        <v>941</v>
       </c>
     </row>
     <row r="137" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A137" s="6" t="s">
-        <v>916</v>
+        <v>910</v>
       </c>
       <c r="B137" s="4" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="C137" s="6" t="s">
+        <v>935</v>
+      </c>
+      <c r="D137" s="6" t="s">
         <v>941</v>
-      </c>
-      <c r="D137" s="6" t="s">
-        <v>947</v>
       </c>
     </row>
     <row r="138" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A138" s="6" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B138" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>951</v>
+        <v>945</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
     </row>
     <row r="139" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A139" s="6" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B139" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>952</v>
+        <v>946</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
     </row>
     <row r="140" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A140" s="6" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B140" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>953</v>
+        <v>947</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
     </row>
     <row r="141" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A141" s="6" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B141" t="s">
+        <v>942</v>
+      </c>
+      <c r="C141" s="6" t="s">
         <v>948</v>
       </c>
-      <c r="C141" s="6" t="s">
-        <v>954</v>
-      </c>
       <c r="D141" s="6" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
     </row>
     <row r="142" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A142" s="6" t="s">
+        <v>943</v>
+      </c>
+      <c r="B142" t="s">
+        <v>942</v>
+      </c>
+      <c r="C142" s="6" t="s">
         <v>949</v>
       </c>
-      <c r="B142" t="s">
-        <v>948</v>
-      </c>
-      <c r="C142" s="6" t="s">
-        <v>955</v>
-      </c>
       <c r="D142" s="6" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
     </row>
     <row r="143" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A143" s="6" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B143" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>956</v>
+        <v>950</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>950</v>
+        <v>944</v>
       </c>
     </row>
     <row r="144" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A144" s="6" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B144" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
     </row>
     <row r="145" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A145" s="6" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B145" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
     </row>
     <row r="146" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A146" s="6" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B146" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
     </row>
     <row r="147" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A147" s="6" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B147" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
     </row>
     <row r="148" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A148" s="6" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B148" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="C148" s="6" t="s">
+        <v>958</v>
+      </c>
+      <c r="D148" s="6" t="s">
         <v>964</v>
-      </c>
-      <c r="D148" s="6" t="s">
-        <v>970</v>
       </c>
     </row>
     <row r="149" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A149" s="6" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B149" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="C149" s="6" t="s">
+        <v>959</v>
+      </c>
+      <c r="D149" s="6" t="s">
         <v>965</v>
-      </c>
-      <c r="D149" s="6" t="s">
-        <v>971</v>
       </c>
     </row>
     <row r="150" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A150" s="6" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B150" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>966</v>
+        <v>960</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
     </row>
     <row r="151" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A151" s="6" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B151" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
     </row>
     <row r="152" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A152" s="6" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B152" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
     </row>
     <row r="153" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A153" s="6" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B153" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
     </row>
     <row r="154" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A154" s="6" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B154" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
     </row>
     <row r="155" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A155" s="6" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B155" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
     </row>
     <row r="156" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A156" s="6" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B156" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
     </row>
     <row r="157" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A157" s="6" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B157" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
     </row>
     <row r="158" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A158" s="6" t="s">
-        <v>949</v>
+        <v>943</v>
       </c>
       <c r="B158" t="s">
-        <v>948</v>
+        <v>942</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>979</v>
+        <v>973</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
     </row>
     <row r="159" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -13544,13 +13526,13 @@
         <v>765</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="C159" s="14" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
       <c r="D159" s="5" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
     </row>
     <row r="160" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -13558,13 +13540,13 @@
         <v>765</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="C160" s="14" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
       <c r="D160" s="5" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
     </row>
     <row r="161" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -13572,13 +13554,13 @@
         <v>765</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="C161" s="14" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
     </row>
     <row r="162" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -13586,13 +13568,13 @@
         <v>765</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="C162" s="14" t="s">
         <v>766</v>
       </c>
       <c r="D162" s="13" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
     </row>
     <row r="163" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -13600,13 +13582,13 @@
         <v>765</v>
       </c>
       <c r="B163" s="4" t="s">
+        <v>975</v>
+      </c>
+      <c r="C163" s="14" t="s">
         <v>981</v>
       </c>
-      <c r="C163" s="14" t="s">
-        <v>987</v>
-      </c>
       <c r="D163" s="13" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
     </row>
     <row r="164" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -13614,13 +13596,13 @@
         <v>765</v>
       </c>
       <c r="B164" s="4" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="C164" s="14" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="D164" s="13" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
     </row>
     <row r="165" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -13628,13 +13610,13 @@
         <v>765</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="C165" s="14" t="s">
-        <v>989</v>
+        <v>983</v>
       </c>
       <c r="D165" s="13" t="s">
-        <v>992</v>
+        <v>986</v>
       </c>
     </row>
     <row r="166" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -13642,13 +13624,13 @@
         <v>765</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="C166" s="14" t="s">
         <v>670</v>
       </c>
       <c r="D166" s="5" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
     </row>
     <row r="167" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -13656,13 +13638,13 @@
         <v>765</v>
       </c>
       <c r="B167" s="4" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="C167" s="14" t="s">
-        <v>990</v>
+        <v>984</v>
       </c>
       <c r="D167" s="5" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
     </row>
     <row r="168" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -13670,13 +13652,13 @@
         <v>765</v>
       </c>
       <c r="B168" s="4" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="C168" s="14" t="s">
-        <v>991</v>
+        <v>985</v>
       </c>
       <c r="D168" s="5" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
     </row>
     <row r="169" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -13684,13 +13666,13 @@
         <v>765</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="C169" s="14" t="s">
         <v>767</v>
       </c>
       <c r="D169" s="5" t="s">
-        <v>993</v>
+        <v>987</v>
       </c>
     </row>
     <row r="170" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -13698,13 +13680,13 @@
         <v>765</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="C170" s="14" t="s">
         <v>768</v>
       </c>
       <c r="D170" s="5" t="s">
-        <v>994</v>
+        <v>988</v>
       </c>
     </row>
     <row r="171" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -13712,139 +13694,139 @@
         <v>765</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="C171" s="14" t="s">
-        <v>996</v>
+        <v>990</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>995</v>
+        <v>989</v>
       </c>
     </row>
     <row r="172" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A172" s="5" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="B172" s="4" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="C172" t="s">
-        <v>999</v>
+        <v>993</v>
       </c>
       <c r="D172" s="11" t="s">
-        <v>1006</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="173" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A173" s="5" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="B173" s="4" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="C173" t="s">
         <v>777</v>
       </c>
       <c r="D173" s="11" t="s">
-        <v>1004</v>
+        <v>998</v>
       </c>
     </row>
     <row r="174" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A174" s="5" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="C174" t="s">
-        <v>1000</v>
+        <v>994</v>
       </c>
       <c r="D174" s="11" t="s">
-        <v>1005</v>
+        <v>999</v>
       </c>
     </row>
     <row r="175" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A175" s="5" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="C175" s="11" t="s">
         <v>559</v>
       </c>
       <c r="D175" s="11" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
     </row>
     <row r="176" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A176" s="5" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="B176" s="4" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="C176" s="11" t="s">
-        <v>1001</v>
+        <v>995</v>
       </c>
       <c r="D176" s="11" t="s">
-        <v>1002</v>
+        <v>996</v>
       </c>
     </row>
     <row r="177" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A177" s="5" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="B177" s="4" t="s">
+        <v>991</v>
+      </c>
+      <c r="C177" s="11" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D177" s="4" t="s">
         <v>997</v>
-      </c>
-      <c r="C177" s="11" t="s">
-        <v>1007</v>
-      </c>
-      <c r="D177" s="4" t="s">
-        <v>1003</v>
       </c>
     </row>
     <row r="178" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A178" s="5" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="B178" s="4" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="C178" s="6" t="s">
-        <v>1008</v>
+        <v>1002</v>
       </c>
       <c r="D178" s="11" t="s">
-        <v>1010</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="179" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A179" s="5" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="B179" s="4" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="C179" s="11" t="s">
-        <v>1009</v>
+        <v>1003</v>
       </c>
       <c r="D179" s="11" t="s">
-        <v>1011</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="180" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A180" s="5" t="s">
-        <v>998</v>
+        <v>992</v>
       </c>
       <c r="B180" s="4" t="s">
-        <v>997</v>
+        <v>991</v>
       </c>
       <c r="C180" s="11" t="s">
         <v>694</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>1012</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="181" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -13852,13 +13834,13 @@
         <v>773</v>
       </c>
       <c r="B181" s="5" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>1014</v>
+        <v>1008</v>
       </c>
       <c r="D181" s="5" t="s">
-        <v>1015</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="182" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -13866,13 +13848,13 @@
         <v>773</v>
       </c>
       <c r="B182" s="5" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="C182" s="6" t="s">
-        <v>1016</v>
+        <v>1010</v>
       </c>
       <c r="D182" t="s">
-        <v>1017</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="183" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -13880,13 +13862,13 @@
         <v>773</v>
       </c>
       <c r="B183" s="5" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="C183" s="6" t="s">
         <v>774</v>
       </c>
       <c r="D183" s="5" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="184" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -13894,13 +13876,13 @@
         <v>773</v>
       </c>
       <c r="B184" s="5" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="C184" s="6" t="s">
         <v>775</v>
       </c>
       <c r="D184" s="5" t="s">
-        <v>1019</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="185" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -13908,13 +13890,13 @@
         <v>773</v>
       </c>
       <c r="B185" s="5" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C185" s="6" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D185" s="5" t="s">
         <v>1013</v>
-      </c>
-      <c r="C185" s="6" t="s">
-        <v>1018</v>
-      </c>
-      <c r="D185" s="5" t="s">
-        <v>1019</v>
       </c>
     </row>
     <row r="186" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -13922,13 +13904,13 @@
         <v>773</v>
       </c>
       <c r="B186" s="5" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="C186" s="6" t="s">
-        <v>1020</v>
+        <v>1014</v>
       </c>
       <c r="D186" s="5" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="187" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -13936,13 +13918,13 @@
         <v>773</v>
       </c>
       <c r="B187" s="5" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="C187" s="6" t="s">
-        <v>1021</v>
+        <v>1015</v>
       </c>
       <c r="D187" s="5" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="188" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -13950,13 +13932,13 @@
         <v>773</v>
       </c>
       <c r="B188" s="5" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="C188" s="6" t="s">
-        <v>1023</v>
+        <v>1017</v>
       </c>
       <c r="D188" s="5" t="s">
-        <v>1024</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="189" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -13964,13 +13946,13 @@
         <v>773</v>
       </c>
       <c r="B189" s="5" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="C189" s="6" t="s">
         <v>776</v>
       </c>
       <c r="D189" s="5" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="190" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -13978,13 +13960,13 @@
         <v>773</v>
       </c>
       <c r="B190" s="5" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="C190" s="6" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="D190" s="5" t="s">
-        <v>1029</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="191" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -13992,13 +13974,13 @@
         <v>773</v>
       </c>
       <c r="B191" s="5" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="C191" s="6" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
       <c r="D191" s="5" t="s">
-        <v>1030</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="192" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14006,13 +13988,13 @@
         <v>773</v>
       </c>
       <c r="B192" s="5" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="C192" s="6" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="D192" s="5" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="193" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14020,13 +14002,13 @@
         <v>773</v>
       </c>
       <c r="B193" s="5" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="C193" s="6" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
       <c r="D193" s="5" t="s">
-        <v>1031</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="194" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14034,13 +14016,13 @@
         <v>778</v>
       </c>
       <c r="B194" s="7" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="C194" s="6" t="s">
-        <v>1033</v>
+        <v>1027</v>
       </c>
       <c r="D194" s="15" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="195" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14048,13 +14030,13 @@
         <v>778</v>
       </c>
       <c r="B195" s="7" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="C195" s="4" t="s">
-        <v>1034</v>
+        <v>1028</v>
       </c>
       <c r="D195" s="15" t="s">
-        <v>1035</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="196" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14062,13 +14044,13 @@
         <v>778</v>
       </c>
       <c r="B196" s="7" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="C196" s="6" t="s">
         <v>556</v>
       </c>
       <c r="D196" s="15" t="s">
-        <v>1039</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="197" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14076,13 +14058,13 @@
         <v>778</v>
       </c>
       <c r="B197" s="7" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="C197" s="6" t="s">
         <v>555</v>
       </c>
       <c r="D197" s="15" t="s">
-        <v>1040</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="198" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14090,13 +14072,13 @@
         <v>778</v>
       </c>
       <c r="B198" s="7" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="C198" s="6" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="D198" s="15" t="s">
-        <v>1041</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="199" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14104,13 +14086,13 @@
         <v>778</v>
       </c>
       <c r="B199" s="7" t="s">
-        <v>1032</v>
+        <v>1026</v>
       </c>
       <c r="C199" s="6" t="s">
-        <v>1037</v>
+        <v>1031</v>
       </c>
       <c r="D199" s="15" t="s">
-        <v>1042</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="200" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14118,223 +14100,223 @@
         <v>778</v>
       </c>
       <c r="B200" s="7" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C200" s="6" t="s">
         <v>1032</v>
       </c>
-      <c r="C200" s="6" t="s">
-        <v>1038</v>
-      </c>
       <c r="D200" s="15" t="s">
-        <v>1043</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="201" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A201" s="6" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="B201" s="4" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="C201" s="5" t="s">
         <v>563</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="202" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A202" s="6" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="B202" s="4" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="C202" s="5" t="s">
-        <v>1046</v>
+        <v>1040</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>1047</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="203" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A203" s="6" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="B203" s="4" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="C203" s="5" t="s">
-        <v>1048</v>
+        <v>1042</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>1055</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="204" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A204" s="6" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="B204" s="4" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="C204" s="5" t="s">
-        <v>1049</v>
+        <v>1043</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>1054</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="205" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A205" s="6" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="B205" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C205" s="13" t="s">
         <v>1044</v>
       </c>
-      <c r="C205" s="13" t="s">
-        <v>1050</v>
-      </c>
       <c r="D205" s="4" t="s">
-        <v>1053</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="206" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A206" s="6" t="s">
-        <v>1045</v>
+        <v>1039</v>
       </c>
       <c r="B206" s="4" t="s">
-        <v>1044</v>
+        <v>1038</v>
       </c>
       <c r="C206" s="5" t="s">
         <v>665</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="207" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A207" s="6" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B207" s="4" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C207" s="5" t="s">
         <v>1045</v>
       </c>
-      <c r="B207" s="4" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C207" s="5" t="s">
-        <v>1051</v>
-      </c>
       <c r="D207" s="4" t="s">
-        <v>1052</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="208" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A208" s="5" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="B208" s="4" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="C208" s="6" t="s">
-        <v>1058</v>
+        <v>1052</v>
       </c>
       <c r="D208" s="12" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="209" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A209" s="5" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="B209" s="4" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>1059</v>
+        <v>1053</v>
       </c>
       <c r="D209" s="12" t="s">
-        <v>1060</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="210" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A210" s="5" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="B210" s="4" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C210" s="6" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D210" s="11" t="s">
         <v>1056</v>
-      </c>
-      <c r="C210" s="6" t="s">
-        <v>1061</v>
-      </c>
-      <c r="D210" s="11" t="s">
-        <v>1062</v>
       </c>
     </row>
     <row r="211" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A211" s="5" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B211" s="4" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C211" s="6" t="s">
         <v>1057</v>
       </c>
-      <c r="B211" s="4" t="s">
-        <v>1056</v>
-      </c>
-      <c r="C211" s="6" t="s">
-        <v>1063</v>
-      </c>
       <c r="D211" s="11" t="s">
-        <v>1066</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="212" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A212" s="5" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="B212" s="4" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="C212" s="6" t="s">
-        <v>1064</v>
+        <v>1058</v>
       </c>
       <c r="D212" s="11" t="s">
-        <v>1067</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="213" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A213" s="5" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="B213" s="4" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>1065</v>
+        <v>1059</v>
       </c>
       <c r="D213" s="11" t="s">
-        <v>1068</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="214" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A214" s="5" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="B214" s="4" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="C214" s="6" t="s">
-        <v>1069</v>
+        <v>1063</v>
       </c>
       <c r="D214" s="11" t="s">
-        <v>1071</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="215" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A215" s="5" t="s">
-        <v>1057</v>
+        <v>1051</v>
       </c>
       <c r="B215" s="4" t="s">
-        <v>1056</v>
+        <v>1050</v>
       </c>
       <c r="C215" s="6" t="s">
-        <v>1070</v>
+        <v>1064</v>
       </c>
       <c r="D215" s="11" t="s">
-        <v>1072</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="216" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14342,13 +14324,13 @@
         <v>40</v>
       </c>
       <c r="B216" s="4" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="C216" s="6" t="s">
         <v>770</v>
       </c>
       <c r="D216" s="5" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="217" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14356,13 +14338,13 @@
         <v>40</v>
       </c>
       <c r="B217" s="4" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="C217" s="6" t="s">
-        <v>1074</v>
+        <v>1068</v>
       </c>
       <c r="D217" s="5" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="218" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14370,13 +14352,13 @@
         <v>40</v>
       </c>
       <c r="B218" s="4" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="C218" s="6" t="s">
-        <v>1075</v>
+        <v>1069</v>
       </c>
       <c r="D218" s="5" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="219" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14384,13 +14366,13 @@
         <v>40</v>
       </c>
       <c r="B219" s="4" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="C219" s="6" t="s">
-        <v>1076</v>
+        <v>1070</v>
       </c>
       <c r="D219" s="5" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="220" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14398,13 +14380,13 @@
         <v>40</v>
       </c>
       <c r="B220" s="4" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="C220" s="6" t="s">
         <v>771</v>
       </c>
       <c r="D220" s="5" t="s">
-        <v>1077</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="221" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14412,13 +14394,13 @@
         <v>769</v>
       </c>
       <c r="B221" s="4" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="C221" s="6" t="s">
-        <v>1078</v>
+        <v>1072</v>
       </c>
       <c r="D221" s="13" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="222" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14426,13 +14408,13 @@
         <v>769</v>
       </c>
       <c r="B222" s="4" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="C222" s="6" t="s">
         <v>772</v>
       </c>
       <c r="D222" s="13" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="223" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14440,13 +14422,13 @@
         <v>769</v>
       </c>
       <c r="B223" s="4" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C223" s="6" t="s">
         <v>1073</v>
       </c>
-      <c r="C223" s="6" t="s">
-        <v>1079</v>
-      </c>
       <c r="D223" s="13" t="s">
-        <v>1080</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="224" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14454,13 +14436,13 @@
         <v>769</v>
       </c>
       <c r="B224" s="4" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="C224" s="6" t="s">
-        <v>1081</v>
+        <v>1075</v>
       </c>
       <c r="D224" s="13" t="s">
-        <v>1082</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="225" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14468,13 +14450,13 @@
         <v>769</v>
       </c>
       <c r="B225" s="4" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="C225" s="6" t="s">
-        <v>1083</v>
+        <v>1077</v>
       </c>
       <c r="D225" s="5" t="s">
-        <v>1084</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="226" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14482,13 +14464,13 @@
         <v>769</v>
       </c>
       <c r="B226" s="4" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="C226" s="6" t="s">
-        <v>1085</v>
+        <v>1079</v>
       </c>
       <c r="D226" s="5" t="s">
-        <v>1086</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="227" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14496,363 +14478,363 @@
         <v>769</v>
       </c>
       <c r="B227" s="4" t="s">
-        <v>1073</v>
+        <v>1067</v>
       </c>
       <c r="C227" s="6" t="s">
-        <v>1087</v>
+        <v>1081</v>
       </c>
       <c r="D227" s="5" t="s">
-        <v>1088</v>
+        <v>1082</v>
       </c>
     </row>
     <row r="228" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A228" s="6" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="B228" s="7" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="C228" s="6" t="s">
-        <v>1061</v>
+        <v>1055</v>
       </c>
       <c r="D228" s="4" t="s">
-        <v>1101</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="229" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A229" s="6" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="B229" s="7" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="C229" s="6" t="s">
-        <v>1091</v>
+        <v>1085</v>
       </c>
       <c r="D229" s="4" t="s">
-        <v>1102</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="230" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A230" s="6" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="B230" s="7" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="C230" s="6" t="s">
-        <v>1092</v>
+        <v>1086</v>
       </c>
       <c r="D230" s="4" t="s">
-        <v>1103</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="231" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A231" s="6" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="B231" s="7" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="C231" s="6" t="s">
-        <v>1093</v>
+        <v>1087</v>
       </c>
       <c r="D231" s="4" t="s">
-        <v>1104</v>
+        <v>1098</v>
       </c>
     </row>
     <row r="232" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A232" s="6" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="B232" s="7" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="C232" s="6" t="s">
-        <v>1094</v>
+        <v>1088</v>
       </c>
       <c r="D232" s="4" t="s">
-        <v>1105</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="233" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A233" s="6" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="B233" s="7" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C233" s="6" t="s">
         <v>1089</v>
       </c>
-      <c r="C233" s="6" t="s">
-        <v>1095</v>
-      </c>
       <c r="D233" s="4" t="s">
-        <v>1106</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="234" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A234" s="6" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B234" s="7" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C234" s="6" t="s">
         <v>1090</v>
       </c>
-      <c r="B234" s="7" t="s">
-        <v>1089</v>
-      </c>
-      <c r="C234" s="6" t="s">
-        <v>1096</v>
-      </c>
       <c r="D234" s="4" t="s">
-        <v>1107</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="235" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A235" s="6" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="B235" s="7" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>1097</v>
+        <v>1091</v>
       </c>
       <c r="D235" s="4" t="s">
-        <v>1108</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="236" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A236" s="6" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="B236" s="7" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="C236" s="6" t="s">
-        <v>1098</v>
+        <v>1092</v>
       </c>
       <c r="D236" s="8" t="s">
-        <v>1109</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="237" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A237" s="6" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="B237" s="7" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>1099</v>
+        <v>1093</v>
       </c>
       <c r="D237" s="8" t="s">
-        <v>1110</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="238" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A238" s="6" t="s">
-        <v>1090</v>
+        <v>1084</v>
       </c>
       <c r="B238" s="7" t="s">
-        <v>1089</v>
+        <v>1083</v>
       </c>
       <c r="C238" s="6" t="s">
-        <v>1100</v>
+        <v>1094</v>
       </c>
       <c r="D238" s="4" t="s">
-        <v>1111</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="239" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A239" s="16" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="B239" s="4" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C239" s="6" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D239" s="11" t="s">
         <v>1112</v>
-      </c>
-      <c r="C239" s="6" t="s">
-        <v>1114</v>
-      </c>
-      <c r="D239" s="11" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="240" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A240" s="16" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="B240" s="4" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C240" s="6" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D240" s="11" t="s">
         <v>1112</v>
-      </c>
-      <c r="C240" s="6" t="s">
-        <v>1115</v>
-      </c>
-      <c r="D240" s="11" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="241" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A241" s="16" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="B241" s="4" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C241" s="6" t="s">
+        <v>1110</v>
+      </c>
+      <c r="D241" s="11" t="s">
         <v>1112</v>
-      </c>
-      <c r="C241" s="6" t="s">
-        <v>1116</v>
-      </c>
-      <c r="D241" s="11" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="242" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A242" s="16" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="B242" s="4" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C242" s="6" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D242" s="11" t="s">
         <v>1112</v>
-      </c>
-      <c r="C242" s="6" t="s">
-        <v>1117</v>
-      </c>
-      <c r="D242" s="11" t="s">
-        <v>1118</v>
       </c>
     </row>
     <row r="243" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A243" s="16" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B243" s="4" t="s">
+        <v>1106</v>
+      </c>
+      <c r="C243" s="6" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D243" s="11" t="s">
         <v>1113</v>
-      </c>
-      <c r="B243" s="4" t="s">
-        <v>1112</v>
-      </c>
-      <c r="C243" s="6" t="s">
-        <v>1120</v>
-      </c>
-      <c r="D243" s="11" t="s">
-        <v>1119</v>
       </c>
     </row>
     <row r="244" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A244" s="16" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="B244" s="4" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="C244" s="6" t="s">
-        <v>1121</v>
+        <v>1115</v>
       </c>
       <c r="D244" s="11" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="245" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A245" s="16" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="B245" s="4" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="C245" s="6" t="s">
-        <v>1122</v>
+        <v>1116</v>
       </c>
       <c r="D245" s="11" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="246" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A246" s="16" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="B246" s="4" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="C246" s="6" t="s">
-        <v>1123</v>
+        <v>1117</v>
       </c>
       <c r="D246" s="11" t="s">
-        <v>1124</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="247" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A247" s="16" t="s">
-        <v>1113</v>
+        <v>1107</v>
       </c>
       <c r="B247" s="4" t="s">
-        <v>1112</v>
+        <v>1106</v>
       </c>
       <c r="C247" s="6" t="s">
-        <v>1125</v>
+        <v>1119</v>
       </c>
       <c r="D247" s="11" t="s">
-        <v>1126</v>
+        <v>1120</v>
       </c>
     </row>
     <row r="248" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A248" s="6" t="s">
-        <v>1128</v>
+        <v>1122</v>
       </c>
       <c r="B248" s="5" t="s">
-        <v>1127</v>
+        <v>1121</v>
       </c>
       <c r="C248" s="6" t="s">
-        <v>1129</v>
+        <v>1123</v>
       </c>
       <c r="D248" s="4" t="s">
-        <v>1130</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="249" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A249" s="6" t="s">
-        <v>1128</v>
+        <v>1122</v>
       </c>
       <c r="B249" s="5" t="s">
-        <v>1127</v>
+        <v>1121</v>
       </c>
       <c r="C249" s="6" t="s">
-        <v>1131</v>
+        <v>1125</v>
       </c>
       <c r="D249" s="4" t="s">
-        <v>1132</v>
+        <v>1126</v>
       </c>
     </row>
     <row r="250" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A250" s="6" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B250" s="5" t="s">
+        <v>1121</v>
+      </c>
+      <c r="C250" s="6" t="s">
+        <v>1127</v>
+      </c>
+      <c r="D250" s="4" t="s">
         <v>1128</v>
-      </c>
-      <c r="B250" s="5" t="s">
-        <v>1127</v>
-      </c>
-      <c r="C250" s="6" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D250" s="4" t="s">
-        <v>1134</v>
       </c>
     </row>
     <row r="251" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A251" s="6" t="s">
-        <v>1128</v>
+        <v>1122</v>
       </c>
       <c r="B251" s="5" t="s">
-        <v>1127</v>
+        <v>1121</v>
       </c>
       <c r="C251" s="6" t="s">
-        <v>1135</v>
+        <v>1129</v>
       </c>
       <c r="D251" s="4" t="s">
-        <v>1137</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="252" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A252" s="6" t="s">
-        <v>1128</v>
+        <v>1122</v>
       </c>
       <c r="B252" s="5" t="s">
-        <v>1127</v>
+        <v>1121</v>
       </c>
       <c r="C252" s="6" t="s">
-        <v>1136</v>
+        <v>1130</v>
       </c>
       <c r="D252" s="4" t="s">
-        <v>1138</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="253" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14860,13 +14842,13 @@
         <v>779</v>
       </c>
       <c r="B253" s="4" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
       <c r="C253" s="6" t="s">
-        <v>1140</v>
+        <v>1134</v>
       </c>
       <c r="D253" s="6" t="s">
-        <v>1141</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="254" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14874,13 +14856,13 @@
         <v>779</v>
       </c>
       <c r="B254" s="4" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
       <c r="C254" s="6" t="s">
         <v>469</v>
       </c>
       <c r="D254" s="6" t="s">
-        <v>1141</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="255" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14888,13 +14870,13 @@
         <v>779</v>
       </c>
       <c r="B255" s="4" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
       <c r="C255" s="6" t="s">
         <v>556</v>
       </c>
       <c r="D255" s="6" t="s">
-        <v>1142</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="256" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14902,13 +14884,13 @@
         <v>779</v>
       </c>
       <c r="B256" s="4" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
       <c r="C256" s="6" t="s">
-        <v>1143</v>
+        <v>1137</v>
       </c>
       <c r="D256" s="6" t="s">
-        <v>1144</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="257" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14916,13 +14898,13 @@
         <v>779</v>
       </c>
       <c r="B257" s="4" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
       <c r="C257" s="6" t="s">
         <v>508</v>
       </c>
       <c r="D257" s="6" t="s">
-        <v>1145</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="258" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14930,13 +14912,13 @@
         <v>779</v>
       </c>
       <c r="B258" s="4" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
       <c r="C258" s="6" t="s">
-        <v>1146</v>
+        <v>1140</v>
       </c>
       <c r="D258" s="6" t="s">
-        <v>1149</v>
+        <v>1143</v>
       </c>
     </row>
     <row r="259" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14944,13 +14926,13 @@
         <v>779</v>
       </c>
       <c r="B259" s="4" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
       <c r="C259" s="6" t="s">
         <v>555</v>
       </c>
       <c r="D259" s="6" t="s">
-        <v>1150</v>
+        <v>1144</v>
       </c>
     </row>
     <row r="260" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14958,13 +14940,13 @@
         <v>779</v>
       </c>
       <c r="B260" s="4" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
       <c r="C260" s="6" t="s">
         <v>498</v>
       </c>
       <c r="D260" s="6" t="s">
-        <v>1151</v>
+        <v>1145</v>
       </c>
     </row>
     <row r="261" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14972,13 +14954,13 @@
         <v>779</v>
       </c>
       <c r="B261" s="4" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
       <c r="C261" s="6" t="s">
-        <v>1147</v>
+        <v>1141</v>
       </c>
       <c r="D261" s="6" t="s">
-        <v>1152</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="262" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -14986,13 +14968,13 @@
         <v>779</v>
       </c>
       <c r="B262" s="4" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
       <c r="C262" s="6" t="s">
         <v>499</v>
       </c>
       <c r="D262" s="6" t="s">
-        <v>1153</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="263" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -15000,13 +14982,13 @@
         <v>779</v>
       </c>
       <c r="B263" s="4" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
       <c r="C263" s="6" t="s">
         <v>578</v>
       </c>
       <c r="D263" s="6" t="s">
-        <v>1154</v>
+        <v>1148</v>
       </c>
     </row>
     <row r="264" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
@@ -15014,1483 +14996,1483 @@
         <v>779</v>
       </c>
       <c r="B264" s="4" t="s">
-        <v>1139</v>
+        <v>1133</v>
       </c>
       <c r="C264" s="6" t="s">
+        <v>1142</v>
+      </c>
+      <c r="D264" s="6" t="s">
         <v>1148</v>
-      </c>
-      <c r="D264" s="6" t="s">
-        <v>1154</v>
       </c>
     </row>
     <row r="265" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A265" s="6" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="B265" s="7" t="s">
-        <v>1156</v>
+        <v>1150</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>1158</v>
+        <v>1152</v>
       </c>
       <c r="D265" s="4" t="s">
-        <v>1161</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="266" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A266" s="6" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="B266" s="7" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C266" s="6" t="s">
+        <v>1153</v>
+      </c>
+      <c r="D266" s="4" t="s">
         <v>1156</v>
-      </c>
-      <c r="C266" s="6" t="s">
-        <v>1159</v>
-      </c>
-      <c r="D266" s="4" t="s">
-        <v>1162</v>
       </c>
     </row>
     <row r="267" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A267" s="6" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B267" s="7" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C267" s="6" t="s">
+        <v>1154</v>
+      </c>
+      <c r="D267" s="4" t="s">
         <v>1157</v>
-      </c>
-      <c r="B267" s="7" t="s">
-        <v>1156</v>
-      </c>
-      <c r="C267" s="6" t="s">
-        <v>1160</v>
-      </c>
-      <c r="D267" s="4" t="s">
-        <v>1163</v>
       </c>
     </row>
     <row r="268" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A268" s="6" t="s">
-        <v>1157</v>
+        <v>1151</v>
       </c>
       <c r="B268" s="7" t="s">
-        <v>1156</v>
+        <v>1150</v>
       </c>
       <c r="C268" s="6" t="s">
         <v>498</v>
       </c>
       <c r="D268" s="4" t="s">
-        <v>1164</v>
+        <v>1158</v>
       </c>
     </row>
     <row r="269" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A269" s="6" t="s">
-        <v>1165</v>
+        <v>1159</v>
       </c>
       <c r="B269" s="4" t="s">
-        <v>1166</v>
+        <v>1160</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>1167</v>
+        <v>1161</v>
       </c>
       <c r="D269" s="4" t="s">
-        <v>1168</v>
+        <v>1162</v>
       </c>
     </row>
     <row r="270" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A270" s="6" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B270" s="4" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C270" s="6" t="s">
+        <v>1163</v>
+      </c>
+      <c r="D270" s="4" t="s">
         <v>1165</v>
-      </c>
-      <c r="B270" s="4" t="s">
-        <v>1166</v>
-      </c>
-      <c r="C270" s="6" t="s">
-        <v>1169</v>
-      </c>
-      <c r="D270" s="4" t="s">
-        <v>1171</v>
       </c>
     </row>
     <row r="271" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A271" s="6" t="s">
-        <v>1165</v>
+        <v>1159</v>
       </c>
       <c r="B271" s="4" t="s">
+        <v>1160</v>
+      </c>
+      <c r="C271" s="6" t="s">
+        <v>1164</v>
+      </c>
+      <c r="D271" s="4" t="s">
         <v>1166</v>
-      </c>
-      <c r="C271" s="6" t="s">
-        <v>1170</v>
-      </c>
-      <c r="D271" s="4" t="s">
-        <v>1172</v>
       </c>
     </row>
     <row r="272" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A272" s="6" t="s">
-        <v>1165</v>
+        <v>1159</v>
       </c>
       <c r="B272" s="4" t="s">
-        <v>1166</v>
+        <v>1160</v>
       </c>
       <c r="C272" s="6" t="s">
-        <v>1173</v>
+        <v>1167</v>
       </c>
       <c r="D272" s="4" t="s">
-        <v>1174</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="273" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A273" s="6" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
       <c r="B273" s="4" t="s">
-        <v>1175</v>
+        <v>1169</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>1177</v>
+        <v>1171</v>
       </c>
       <c r="D273" s="4" t="s">
-        <v>1178</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="274" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A274" s="6" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
       <c r="B274" s="4" t="s">
-        <v>1175</v>
+        <v>1169</v>
       </c>
       <c r="C274" s="6" t="s">
-        <v>1179</v>
+        <v>1173</v>
       </c>
       <c r="D274" s="4" t="s">
-        <v>1180</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="275" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A275" s="6" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B275" s="4" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C275" s="6" t="s">
+        <v>1175</v>
+      </c>
+      <c r="D275" s="4" t="s">
         <v>1176</v>
-      </c>
-      <c r="B275" s="4" t="s">
-        <v>1175</v>
-      </c>
-      <c r="C275" s="6" t="s">
-        <v>1181</v>
-      </c>
-      <c r="D275" s="4" t="s">
-        <v>1182</v>
       </c>
     </row>
     <row r="276" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A276" s="6" t="s">
-        <v>1176</v>
+        <v>1170</v>
       </c>
       <c r="B276" s="4" t="s">
-        <v>1175</v>
+        <v>1169</v>
       </c>
       <c r="C276" s="6" t="s">
-        <v>1183</v>
+        <v>1177</v>
       </c>
       <c r="D276" s="4" t="s">
-        <v>1184</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="277" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A277" s="6" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="B277" s="4" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="C277" s="6" t="s">
         <v>715</v>
       </c>
       <c r="D277" s="4" t="s">
-        <v>1189</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="278" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A278" s="6" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="B278" s="4" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="C278" s="6" t="s">
-        <v>1187</v>
+        <v>1181</v>
       </c>
       <c r="D278" s="4" t="s">
-        <v>1189</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="279" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A279" s="6" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="B279" s="4" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="C279" s="6" t="s">
-        <v>1188</v>
+        <v>1182</v>
       </c>
       <c r="D279" s="4" t="s">
-        <v>1189</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="280" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A280" s="6" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="B280" s="4" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="C280" s="6" t="s">
         <v>499</v>
       </c>
       <c r="D280" s="5" t="s">
-        <v>1197</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="281" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A281" s="6" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="B281" s="4" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="C281" s="6" t="s">
-        <v>1190</v>
+        <v>1184</v>
       </c>
       <c r="D281" s="5" t="s">
-        <v>1198</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="282" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A282" s="6" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="B282" s="4" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="C282" s="6" t="s">
         <v>576</v>
       </c>
       <c r="D282" s="5" t="s">
-        <v>1199</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="283" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A283" s="6" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="B283" s="4" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C283" s="6" t="s">
         <v>1185</v>
       </c>
-      <c r="C283" s="6" t="s">
-        <v>1191</v>
-      </c>
       <c r="D283" s="5" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="284" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A284" s="6" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B284" s="4" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C284" s="6" t="s">
         <v>1186</v>
       </c>
-      <c r="B284" s="4" t="s">
-        <v>1185</v>
-      </c>
-      <c r="C284" s="6" t="s">
-        <v>1192</v>
-      </c>
       <c r="D284" s="5" t="s">
-        <v>1193</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="285" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A285" s="6" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="B285" s="4" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="C285" s="6" t="s">
-        <v>1194</v>
+        <v>1188</v>
       </c>
       <c r="D285" s="5" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="286" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A286" s="6" t="s">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="B286" s="4" t="s">
-        <v>1185</v>
+        <v>1179</v>
       </c>
       <c r="C286" s="6" t="s">
-        <v>1195</v>
+        <v>1189</v>
       </c>
       <c r="D286" s="5" t="s">
-        <v>1196</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="287" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A287" s="6" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="B287" s="4" t="s">
-        <v>1202</v>
+        <v>1196</v>
       </c>
       <c r="C287" s="6" t="s">
-        <v>1201</v>
+        <v>1195</v>
       </c>
       <c r="D287" s="4" t="s">
-        <v>1203</v>
+        <v>1197</v>
       </c>
     </row>
     <row r="288" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A288" s="6" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="B288" s="4" t="s">
-        <v>1202</v>
+        <v>1196</v>
       </c>
       <c r="C288" s="6" t="s">
         <v>555</v>
       </c>
       <c r="D288" s="4" t="s">
-        <v>1204</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="289" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A289" s="6" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="B289" s="4" t="s">
-        <v>1202</v>
+        <v>1196</v>
       </c>
       <c r="C289" s="6" t="s">
         <v>508</v>
       </c>
       <c r="D289" s="4" t="s">
-        <v>1206</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="290" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A290" s="6" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="B290" s="4" t="s">
-        <v>1202</v>
+        <v>1196</v>
       </c>
       <c r="C290" s="6" t="s">
         <v>498</v>
       </c>
       <c r="D290" s="4" t="s">
-        <v>1207</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="291" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A291" s="6" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="B291" s="4" t="s">
-        <v>1202</v>
+        <v>1196</v>
       </c>
       <c r="C291" s="6" t="s">
         <v>576</v>
       </c>
       <c r="D291" s="4" t="s">
-        <v>1208</v>
+        <v>1202</v>
       </c>
     </row>
     <row r="292" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A292" s="6" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="B292" s="4" t="s">
-        <v>1202</v>
+        <v>1196</v>
       </c>
       <c r="C292" s="6" t="s">
         <v>403</v>
       </c>
       <c r="D292" s="4" t="s">
-        <v>1209</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="293" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A293" s="6" t="s">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="B293" s="4" t="s">
-        <v>1202</v>
+        <v>1196</v>
       </c>
       <c r="C293" s="6" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="D293" s="4" t="s">
-        <v>1205</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="294" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A294" s="6" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="B294" s="4" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C294" s="6" t="s">
+        <v>1206</v>
+      </c>
+      <c r="D294" s="5" t="s">
         <v>1211</v>
-      </c>
-      <c r="C294" s="6" t="s">
-        <v>1212</v>
-      </c>
-      <c r="D294" s="5" t="s">
-        <v>1217</v>
       </c>
     </row>
     <row r="295" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A295" s="6" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="B295" s="4" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="C295" s="6" t="s">
         <v>556</v>
       </c>
       <c r="D295" s="5" t="s">
-        <v>1218</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="296" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A296" s="6" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="B296" s="4" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="C296" s="6" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D296" s="5" t="s">
         <v>1213</v>
-      </c>
-      <c r="D296" s="5" t="s">
-        <v>1219</v>
       </c>
     </row>
     <row r="297" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A297" s="6" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="B297" s="4" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="C297" s="6" t="s">
         <v>714</v>
       </c>
       <c r="D297" s="5" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="298" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A298" s="6" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="B298" s="4" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="C298" s="6" t="s">
-        <v>1214</v>
+        <v>1208</v>
       </c>
       <c r="D298" s="5" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="299" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A299" s="6" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="B299" s="4" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="C299" s="6" t="s">
-        <v>1215</v>
+        <v>1209</v>
       </c>
       <c r="D299" s="5" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="300" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A300" s="6" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B300" s="4" t="s">
+        <v>1205</v>
+      </c>
+      <c r="C300" s="6" t="s">
         <v>1210</v>
       </c>
-      <c r="B300" s="4" t="s">
-        <v>1211</v>
-      </c>
-      <c r="C300" s="6" t="s">
-        <v>1216</v>
-      </c>
       <c r="D300" s="5" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="301" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A301" s="6" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="B301" s="4" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>1188</v>
+        <v>1182</v>
       </c>
       <c r="D301" s="5" t="s">
-        <v>1219</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="302" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A302" s="6" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="B302" s="4" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="C302" s="6" t="s">
-        <v>1220</v>
+        <v>1214</v>
       </c>
       <c r="D302" s="4" t="s">
-        <v>1221</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="303" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A303" s="6" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="B303" s="4" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="C303" s="6" t="s">
         <v>555</v>
       </c>
       <c r="D303" s="5" t="s">
-        <v>1223</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="304" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A304" s="6" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="B304" s="4" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="C304" s="6" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="D304" s="5" t="s">
-        <v>1226</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="305" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A305" s="6" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="B305" s="4" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="C305" s="6" t="s">
         <v>498</v>
       </c>
       <c r="D305" s="5" t="s">
-        <v>1224</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="306" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A306" s="6" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="B306" s="4" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="C306" s="6" t="s">
-        <v>1222</v>
+        <v>1216</v>
       </c>
       <c r="D306" s="5" t="s">
-        <v>1225</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="307" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A307" s="6" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="B307" s="4" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="C307" s="6" t="s">
         <v>508</v>
       </c>
       <c r="D307" s="5" t="s">
-        <v>1227</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="308" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A308" s="6" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="B308" s="4" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="C308" s="6" t="s">
         <v>403</v>
       </c>
       <c r="D308" s="5" t="s">
-        <v>1232</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="309" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A309" s="6" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="B309" s="4" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="C309" s="6" t="s">
         <v>368</v>
       </c>
       <c r="D309" s="5" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="310" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A310" s="6" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="C310" s="6" t="s">
-        <v>1228</v>
+        <v>1222</v>
       </c>
       <c r="D310" s="5" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="311" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A311" s="6" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="C311" s="6" t="s">
-        <v>1148</v>
+        <v>1142</v>
       </c>
       <c r="D311" s="5" t="s">
-        <v>1231</v>
+        <v>1225</v>
       </c>
     </row>
     <row r="312" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A312" s="6" t="s">
-        <v>1210</v>
+        <v>1204</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>1211</v>
+        <v>1205</v>
       </c>
       <c r="C312" s="6" t="s">
-        <v>1229</v>
+        <v>1223</v>
       </c>
       <c r="D312" s="5" t="s">
-        <v>1230</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="313" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A313" s="6" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>1233</v>
+        <v>1227</v>
       </c>
       <c r="C313" s="6" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="D313" s="4" t="s">
-        <v>1238</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="314" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A314" s="6" t="s">
-        <v>1234</v>
+        <v>1228</v>
       </c>
       <c r="B314" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C314" s="6" t="s">
+        <v>1230</v>
+      </c>
+      <c r="D314" s="4" t="s">
         <v>1233</v>
-      </c>
-      <c r="C314" s="6" t="s">
-        <v>1236</v>
-      </c>
-      <c r="D314" s="4" t="s">
-        <v>1239</v>
       </c>
     </row>
     <row r="315" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A315" s="6" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B315" s="4" t="s">
+        <v>1227</v>
+      </c>
+      <c r="C315" s="6" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D315" s="4" t="s">
         <v>1234</v>
-      </c>
-      <c r="B315" s="4" t="s">
-        <v>1233</v>
-      </c>
-      <c r="C315" s="6" t="s">
-        <v>1237</v>
-      </c>
-      <c r="D315" s="4" t="s">
-        <v>1240</v>
       </c>
     </row>
     <row r="316" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A316" s="6" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="B316" s="7" t="s">
-        <v>1241</v>
+        <v>1235</v>
       </c>
       <c r="C316" s="17" t="s">
         <v>403</v>
       </c>
       <c r="D316" s="17" t="s">
-        <v>1245</v>
+        <v>1239</v>
       </c>
     </row>
     <row r="317" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A317" s="6" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="B317" s="7" t="s">
-        <v>1242</v>
+        <v>1236</v>
       </c>
       <c r="C317" s="17" t="s">
         <v>556</v>
       </c>
       <c r="D317" s="17" t="s">
-        <v>1246</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="318" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A318" s="6" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="B318" s="7" t="s">
-        <v>1242</v>
+        <v>1236</v>
       </c>
       <c r="C318" s="17" t="s">
-        <v>1244</v>
+        <v>1238</v>
       </c>
       <c r="D318" s="17" t="s">
-        <v>1246</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="319" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A319" s="6" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B319" s="7" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C319" s="17" t="s">
+        <v>1241</v>
+      </c>
+      <c r="D319" s="17" t="s">
         <v>1243</v>
-      </c>
-      <c r="B319" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="C319" s="17" t="s">
-        <v>1247</v>
-      </c>
-      <c r="D319" s="17" t="s">
-        <v>1249</v>
       </c>
     </row>
     <row r="320" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A320" s="6" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B320" s="7" t="s">
+        <v>1236</v>
+      </c>
+      <c r="C320" s="17" t="s">
+        <v>1242</v>
+      </c>
+      <c r="D320" s="17" t="s">
         <v>1243</v>
-      </c>
-      <c r="B320" s="7" t="s">
-        <v>1242</v>
-      </c>
-      <c r="C320" s="17" t="s">
-        <v>1248</v>
-      </c>
-      <c r="D320" s="17" t="s">
-        <v>1249</v>
       </c>
     </row>
     <row r="321" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A321" s="6" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="B321" s="7" t="s">
-        <v>1242</v>
+        <v>1236</v>
       </c>
       <c r="C321" s="17" t="s">
         <v>580</v>
       </c>
       <c r="D321" s="18" t="s">
-        <v>1254</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="322" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A322" s="6" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="B322" s="7" t="s">
-        <v>1242</v>
+        <v>1236</v>
       </c>
       <c r="C322" s="17" t="s">
-        <v>1250</v>
+        <v>1244</v>
       </c>
       <c r="D322" s="18" t="s">
-        <v>1253</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="323" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A323" s="6" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="B323" s="7" t="s">
-        <v>1242</v>
+        <v>1236</v>
       </c>
       <c r="C323" s="17" t="s">
-        <v>1251</v>
+        <v>1245</v>
       </c>
       <c r="D323" s="18" t="s">
-        <v>1253</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="324" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A324" s="6" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="B324" s="7" t="s">
-        <v>1242</v>
+        <v>1236</v>
       </c>
       <c r="C324" s="17" t="s">
-        <v>1252</v>
+        <v>1246</v>
       </c>
       <c r="D324" s="18" t="s">
-        <v>1253</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="325" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A325" s="6" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="B325" s="7" t="s">
-        <v>1242</v>
+        <v>1236</v>
       </c>
       <c r="C325" s="17" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="D325" s="18" t="s">
-        <v>1255</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="326" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A326" s="6" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="B326" s="7" t="s">
-        <v>1242</v>
+        <v>1236</v>
       </c>
       <c r="C326" s="17" t="s">
         <v>508</v>
       </c>
       <c r="D326" s="18" t="s">
-        <v>1261</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="327" spans="1:4" ht="84" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A327" s="6" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="B327" s="7" t="s">
-        <v>1242</v>
+        <v>1236</v>
       </c>
       <c r="C327" s="19" t="s">
-        <v>1256</v>
+        <v>1250</v>
       </c>
       <c r="D327" s="20" t="s">
-        <v>1257</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="328" spans="1:4" ht="84" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A328" s="6" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="B328" s="7" t="s">
-        <v>1242</v>
+        <v>1236</v>
       </c>
       <c r="C328" s="19" t="s">
-        <v>1258</v>
+        <v>1252</v>
       </c>
       <c r="D328" s="20" t="s">
-        <v>1259</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="329" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A329" s="6" t="s">
-        <v>1243</v>
+        <v>1237</v>
       </c>
       <c r="B329" s="7" t="s">
-        <v>1242</v>
+        <v>1236</v>
       </c>
       <c r="C329" s="21" t="s">
         <v>576</v>
       </c>
       <c r="D329" s="22" t="s">
-        <v>1260</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="330" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A330" s="6" t="s">
-        <v>1263</v>
+        <v>1257</v>
       </c>
       <c r="B330" s="7" t="s">
-        <v>1262</v>
+        <v>1256</v>
       </c>
       <c r="C330" s="10" t="s">
-        <v>1264</v>
+        <v>1258</v>
       </c>
       <c r="D330" s="4" t="s">
-        <v>1265</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="331" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A331" s="6" t="s">
-        <v>1263</v>
+        <v>1257</v>
       </c>
       <c r="B331" s="7" t="s">
-        <v>1262</v>
+        <v>1256</v>
       </c>
       <c r="C331" s="10" t="s">
-        <v>1266</v>
+        <v>1260</v>
       </c>
       <c r="D331" s="4" t="s">
-        <v>1271</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="332" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A332" s="6" t="s">
-        <v>1263</v>
+        <v>1257</v>
       </c>
       <c r="B332" s="7" t="s">
-        <v>1262</v>
+        <v>1256</v>
       </c>
       <c r="C332" s="10" t="s">
-        <v>1267</v>
+        <v>1261</v>
       </c>
       <c r="D332" s="4" t="s">
-        <v>1272</v>
+        <v>1266</v>
       </c>
     </row>
     <row r="333" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A333" s="6" t="s">
-        <v>1263</v>
+        <v>1257</v>
       </c>
       <c r="B333" s="7" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C333" s="10" t="s">
         <v>1262</v>
       </c>
-      <c r="C333" s="10" t="s">
-        <v>1268</v>
-      </c>
       <c r="D333" s="4" t="s">
-        <v>1273</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="334" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A334" s="6" t="s">
-        <v>1263</v>
+        <v>1257</v>
       </c>
       <c r="B334" s="7" t="s">
-        <v>1262</v>
+        <v>1256</v>
       </c>
       <c r="C334" s="10" t="s">
-        <v>1235</v>
+        <v>1229</v>
       </c>
       <c r="D334" s="4" t="s">
-        <v>1274</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="335" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A335" s="6" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B335" s="7" t="s">
+        <v>1256</v>
+      </c>
+      <c r="C335" s="10" t="s">
         <v>1263</v>
       </c>
-      <c r="B335" s="7" t="s">
-        <v>1262</v>
-      </c>
-      <c r="C335" s="10" t="s">
+      <c r="D335" s="4" t="s">
         <v>1269</v>
-      </c>
-      <c r="D335" s="4" t="s">
-        <v>1275</v>
       </c>
     </row>
     <row r="336" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A336" s="6" t="s">
-        <v>1263</v>
+        <v>1257</v>
       </c>
       <c r="B336" s="7" t="s">
-        <v>1262</v>
+        <v>1256</v>
       </c>
       <c r="C336" s="10" t="s">
+        <v>1264</v>
+      </c>
+      <c r="D336" s="4" t="s">
         <v>1270</v>
-      </c>
-      <c r="D336" s="4" t="s">
-        <v>1276</v>
       </c>
     </row>
     <row r="337" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A337" s="6" t="s">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>1277</v>
+        <v>1271</v>
       </c>
       <c r="C337" s="10" t="s">
         <v>556</v>
       </c>
       <c r="D337" s="5" t="s">
-        <v>1284</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="338" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A338" s="6" t="s">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>1277</v>
+        <v>1271</v>
       </c>
       <c r="C338" s="10" t="s">
         <v>556</v>
       </c>
       <c r="D338" s="5" t="s">
-        <v>1284</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="339" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A339" s="6" t="s">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>1277</v>
+        <v>1271</v>
       </c>
       <c r="C339" s="10" t="s">
-        <v>1214</v>
+        <v>1208</v>
       </c>
       <c r="D339" s="5" t="s">
-        <v>1285</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="340" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A340" s="6" t="s">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>1277</v>
+        <v>1271</v>
       </c>
       <c r="C340" s="10" t="s">
         <v>508</v>
       </c>
       <c r="D340" s="5" t="s">
-        <v>1286</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="341" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A341" s="6" t="s">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>1277</v>
+        <v>1271</v>
       </c>
       <c r="C341" s="10" t="s">
         <v>555</v>
       </c>
       <c r="D341" s="5" t="s">
-        <v>1287</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="342" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A342" s="6" t="s">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>1277</v>
+        <v>1271</v>
       </c>
       <c r="C342" s="10" t="s">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="D342" s="5" t="s">
-        <v>1288</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="343" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A343" s="6" t="s">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>1277</v>
+        <v>1271</v>
       </c>
       <c r="C343" s="10" t="s">
-        <v>1279</v>
+        <v>1273</v>
       </c>
       <c r="D343" s="5" t="s">
-        <v>1289</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="344" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A344" s="6" t="s">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>1277</v>
+        <v>1271</v>
       </c>
       <c r="C344" s="10" t="s">
         <v>576</v>
       </c>
       <c r="D344" s="5" t="s">
-        <v>1283</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="345" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A345" s="6" t="s">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>1277</v>
+        <v>1271</v>
       </c>
       <c r="C345" s="10" t="s">
         <v>498</v>
       </c>
       <c r="D345" s="5" t="s">
-        <v>1282</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="346" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A346" s="6" t="s">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>1277</v>
+        <v>1271</v>
       </c>
       <c r="C346" s="6" t="s">
-        <v>1280</v>
+        <v>1274</v>
       </c>
       <c r="D346" s="4" t="s">
-        <v>1281</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="347" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A347" s="6" t="s">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>1277</v>
+        <v>1271</v>
       </c>
       <c r="C347" s="6" t="s">
         <v>569</v>
       </c>
       <c r="D347" s="5" t="s">
-        <v>1292</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="348" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A348" s="6" t="s">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>1277</v>
+        <v>1271</v>
       </c>
       <c r="C348" s="6" t="s">
-        <v>1290</v>
+        <v>1284</v>
       </c>
       <c r="D348" s="5" t="s">
-        <v>1292</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="349" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A349" s="6" t="s">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>1277</v>
+        <v>1271</v>
       </c>
       <c r="C349" s="6" t="s">
-        <v>1291</v>
+        <v>1285</v>
       </c>
       <c r="D349" s="5" t="s">
-        <v>1292</v>
+        <v>1286</v>
       </c>
     </row>
     <row r="350" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A350" s="6" t="s">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>1277</v>
+        <v>1271</v>
       </c>
       <c r="C350" s="6" t="s">
         <v>570</v>
       </c>
       <c r="D350" s="4" t="s">
-        <v>1293</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="351" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A351" s="6" t="s">
-        <v>1278</v>
+        <v>1272</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>1277</v>
+        <v>1271</v>
       </c>
       <c r="C351" s="6" t="s">
         <v>513</v>
       </c>
       <c r="D351" s="4" t="s">
-        <v>1294</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="352" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A352" s="6" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B352" s="4" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C352" s="5" t="s">
+        <v>1291</v>
+      </c>
+      <c r="D352" s="4" t="s">
         <v>1296</v>
-      </c>
-      <c r="B352" s="4" t="s">
-        <v>1295</v>
-      </c>
-      <c r="C352" s="5" t="s">
-        <v>1297</v>
-      </c>
-      <c r="D352" s="4" t="s">
-        <v>1302</v>
       </c>
     </row>
     <row r="353" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A353" s="6" t="s">
-        <v>1296</v>
+        <v>1290</v>
       </c>
       <c r="B353" s="4" t="s">
+        <v>1289</v>
+      </c>
+      <c r="C353" s="5" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D353" s="4" t="s">
         <v>1295</v>
-      </c>
-      <c r="C353" s="5" t="s">
-        <v>1298</v>
-      </c>
-      <c r="D353" s="4" t="s">
-        <v>1301</v>
       </c>
     </row>
     <row r="354" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A354" s="6" t="s">
-        <v>1296</v>
+        <v>1290</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>1295</v>
+        <v>1289</v>
       </c>
       <c r="C354" s="5" t="s">
-        <v>1299</v>
+        <v>1293</v>
       </c>
       <c r="D354" s="4" t="s">
-        <v>1300</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="355" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A355" s="6" t="s">
-        <v>1303</v>
+        <v>1297</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>1304</v>
+        <v>1298</v>
       </c>
       <c r="C355" s="6" t="s">
-        <v>1305</v>
+        <v>1299</v>
       </c>
       <c r="D355" s="5" t="s">
-        <v>1306</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="356" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A356" s="6" t="s">
-        <v>1303</v>
+        <v>1297</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>1304</v>
+        <v>1298</v>
       </c>
       <c r="C356" s="6" t="s">
+        <v>1301</v>
+      </c>
+      <c r="D356" t="s">
         <v>1307</v>
-      </c>
-      <c r="D356" t="s">
-        <v>1313</v>
       </c>
     </row>
     <row r="357" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A357" s="6" t="s">
-        <v>1303</v>
+        <v>1297</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>1304</v>
+        <v>1298</v>
       </c>
       <c r="C357" s="6" t="s">
+        <v>1302</v>
+      </c>
+      <c r="D357" t="s">
         <v>1308</v>
-      </c>
-      <c r="D357" t="s">
-        <v>1314</v>
       </c>
     </row>
     <row r="358" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A358" s="6" t="s">
+        <v>1297</v>
+      </c>
+      <c r="B358" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C358" s="6" t="s">
         <v>1303</v>
       </c>
-      <c r="B358" s="4" t="s">
-        <v>1304</v>
-      </c>
-      <c r="C358" s="6" t="s">
+      <c r="D358" t="s">
         <v>1309</v>
-      </c>
-      <c r="D358" t="s">
-        <v>1315</v>
       </c>
     </row>
     <row r="359" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A359" s="6" t="s">
-        <v>1303</v>
+        <v>1297</v>
       </c>
       <c r="B359" s="4" t="s">
+        <v>1298</v>
+      </c>
+      <c r="C359" s="6" t="s">
         <v>1304</v>
       </c>
-      <c r="C359" s="6" t="s">
+      <c r="D359" t="s">
         <v>1310</v>
-      </c>
-      <c r="D359" t="s">
-        <v>1316</v>
       </c>
     </row>
     <row r="360" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A360" s="6" t="s">
-        <v>1303</v>
+        <v>1297</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>1304</v>
+        <v>1298</v>
       </c>
       <c r="C360" s="6" t="s">
+        <v>1305</v>
+      </c>
+      <c r="D360" t="s">
         <v>1311</v>
-      </c>
-      <c r="D360" t="s">
-        <v>1317</v>
       </c>
     </row>
     <row r="361" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A361" s="6" t="s">
-        <v>1303</v>
+        <v>1297</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>1304</v>
+        <v>1298</v>
       </c>
       <c r="C361" s="6" t="s">
+        <v>1306</v>
+      </c>
+      <c r="D361" t="s">
         <v>1312</v>
-      </c>
-      <c r="D361" t="s">
-        <v>1318</v>
       </c>
     </row>
     <row r="362" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A362" s="6" t="s">
-        <v>1303</v>
+        <v>1297</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>1304</v>
+        <v>1298</v>
       </c>
       <c r="C362" s="6" t="s">
+        <v>1313</v>
+      </c>
+      <c r="D362" s="4" t="s">
         <v>1319</v>
-      </c>
-      <c r="D362" s="4" t="s">
-        <v>1325</v>
       </c>
     </row>
     <row r="363" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A363" s="6" t="s">
-        <v>1303</v>
+        <v>1297</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>1304</v>
+        <v>1298</v>
       </c>
       <c r="C363" s="6" t="s">
+        <v>1314</v>
+      </c>
+      <c r="D363" s="4" t="s">
         <v>1320</v>
-      </c>
-      <c r="D363" s="4" t="s">
-        <v>1326</v>
       </c>
     </row>
     <row r="364" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A364" s="6" t="s">
-        <v>1303</v>
+        <v>1297</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>1304</v>
+        <v>1298</v>
       </c>
       <c r="C364" s="6" t="s">
-        <v>1324</v>
+        <v>1318</v>
       </c>
       <c r="D364" s="4" t="s">
-        <v>1327</v>
+        <v>1321</v>
       </c>
     </row>
     <row r="365" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A365" s="6" t="s">
-        <v>1303</v>
+        <v>1297</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>1304</v>
+        <v>1298</v>
       </c>
       <c r="C365" s="6" t="s">
-        <v>1321</v>
+        <v>1315</v>
       </c>
       <c r="D365" s="4" t="s">
-        <v>1328</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="366" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A366" s="6" t="s">
-        <v>1303</v>
+        <v>1297</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>1304</v>
+        <v>1298</v>
       </c>
       <c r="C366" s="6" t="s">
-        <v>1322</v>
+        <v>1316</v>
       </c>
       <c r="D366" s="4" t="s">
-        <v>1329</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="367" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A367" s="6" t="s">
-        <v>1303</v>
+        <v>1297</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>1304</v>
+        <v>1298</v>
       </c>
       <c r="C367" s="6" t="s">
-        <v>1323</v>
+        <v>1317</v>
       </c>
       <c r="D367" s="4" t="s">
-        <v>1330</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="368" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A368" s="6" t="s">
-        <v>1303</v>
+        <v>1297</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>1304</v>
+        <v>1298</v>
       </c>
       <c r="C368" s="6" t="s">
-        <v>1331</v>
+        <v>1325</v>
       </c>
       <c r="D368" s="5" t="s">
-        <v>1333</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="369" spans="1:4" ht="84" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A369" s="6" t="s">
-        <v>1303</v>
+        <v>1297</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>1304</v>
+        <v>1298</v>
       </c>
       <c r="C369" s="6" t="s">
-        <v>1332</v>
+        <v>1326</v>
       </c>
       <c r="D369" s="5" t="s">
-        <v>1334</v>
+        <v>1328</v>
       </c>
     </row>
   </sheetData>
